--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="264">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -568,6 +568,15 @@
     <t>['12', '68']</t>
   </si>
   <si>
+    <t>['28', '59', '77', '90+2']</t>
+  </si>
+  <si>
+    <t>['41', '45+1', '82', '90+1']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -791,6 +800,12 @@
   </si>
   <si>
     <t>['86', '90+8']</t>
+  </si>
+  <si>
+    <t>['51', '90+6']</t>
+  </si>
+  <si>
+    <t>['51', '73', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1489,7 +1504,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ2">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1614,7 +1629,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1692,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AQ3">
         <v>1.76</v>
@@ -1898,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ4">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2519,7 +2534,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2644,7 +2659,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2722,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ8">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3056,7 +3071,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3137,7 +3152,7 @@
         <v>0.95</v>
       </c>
       <c r="AQ10">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR10">
         <v>0.82</v>
@@ -3262,7 +3277,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3549,7 +3564,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ12">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR12">
         <v>0.8</v>
@@ -3674,7 +3689,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3752,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ13">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3880,7 +3895,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3958,10 +3973,10 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AQ14">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AR14">
         <v>1.15</v>
@@ -4167,7 +4182,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ15">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
@@ -4292,7 +4307,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4370,10 +4385,10 @@
         <v>0.5</v>
       </c>
       <c r="AP16">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ16">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR16">
         <v>1.64</v>
@@ -4498,7 +4513,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4579,7 +4594,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ17">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AR17">
         <v>1.16</v>
@@ -4910,7 +4925,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4988,10 +5003,10 @@
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ19">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR19">
         <v>1.43</v>
@@ -5116,7 +5131,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5400,10 +5415,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AQ21">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR21">
         <v>1.02</v>
@@ -5528,7 +5543,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6021,7 +6036,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ24">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR24">
         <v>1.21</v>
@@ -6224,7 +6239,7 @@
         <v>2.33</v>
       </c>
       <c r="AP25">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ25">
         <v>1.24</v>
@@ -6433,7 +6448,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ26">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR26">
         <v>1.69</v>
@@ -6558,7 +6573,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6636,10 +6651,10 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ27">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR27">
         <v>1.27</v>
@@ -6764,7 +6779,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6842,7 +6857,7 @@
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ28">
         <v>1.76</v>
@@ -6970,7 +6985,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7048,7 +7063,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ29">
         <v>0.95</v>
@@ -7176,7 +7191,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7382,7 +7397,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7666,10 +7681,10 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ32">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR32">
         <v>1.04</v>
@@ -7794,7 +7809,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7875,7 +7890,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ33">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR33">
         <v>1.57</v>
@@ -8000,7 +8015,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8078,10 +8093,10 @@
         <v>1.25</v>
       </c>
       <c r="AP34">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AQ34">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR34">
         <v>0.87</v>
@@ -8206,7 +8221,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8287,7 +8302,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ35">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AR35">
         <v>0.9</v>
@@ -8490,7 +8505,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ36">
         <v>1.24</v>
@@ -8699,7 +8714,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ37">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR37">
         <v>0.98</v>
@@ -8824,7 +8839,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -9030,7 +9045,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9108,7 +9123,7 @@
         <v>1.6</v>
       </c>
       <c r="AP39">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ39">
         <v>1.76</v>
@@ -9317,7 +9332,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ40">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AR40">
         <v>1.66</v>
@@ -9442,7 +9457,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9520,10 +9535,10 @@
         <v>1.8</v>
       </c>
       <c r="AP41">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ41">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AR41">
         <v>1.48</v>
@@ -9726,10 +9741,10 @@
         <v>0.8</v>
       </c>
       <c r="AP42">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ42">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR42">
         <v>1.44</v>
@@ -10060,7 +10075,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10138,10 +10153,10 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ44">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR44">
         <v>1.44</v>
@@ -10266,7 +10281,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10472,7 +10487,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10550,7 +10565,7 @@
         <v>1.67</v>
       </c>
       <c r="AP46">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ46">
         <v>2.1</v>
@@ -10678,7 +10693,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10756,7 +10771,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ47">
         <v>1.24</v>
@@ -10965,7 +10980,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ48">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR48">
         <v>1.54</v>
@@ -11090,7 +11105,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11168,7 +11183,7 @@
         <v>2.17</v>
       </c>
       <c r="AP49">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ49">
         <v>1.43</v>
@@ -11374,7 +11389,7 @@
         <v>0.17</v>
       </c>
       <c r="AP50">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AQ50">
         <v>0.95</v>
@@ -11502,7 +11517,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11583,7 +11598,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ51">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR51">
         <v>1.19</v>
@@ -11789,7 +11804,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ52">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR52">
         <v>1.57</v>
@@ -12201,7 +12216,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ54">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AR54">
         <v>1.02</v>
@@ -12326,7 +12341,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12407,7 +12422,7 @@
         <v>0.95</v>
       </c>
       <c r="AQ55">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR55">
         <v>1.18</v>
@@ -12610,7 +12625,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ56">
         <v>1.76</v>
@@ -12738,7 +12753,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12816,10 +12831,10 @@
         <v>1.29</v>
       </c>
       <c r="AP57">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ57">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR57">
         <v>1.41</v>
@@ -12944,7 +12959,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -13025,7 +13040,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ58">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AR58">
         <v>1.28</v>
@@ -13150,7 +13165,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13228,10 +13243,10 @@
         <v>0.88</v>
       </c>
       <c r="AP59">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AQ59">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR59">
         <v>1.07</v>
@@ -13434,7 +13449,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ60">
         <v>0.95</v>
@@ -13562,7 +13577,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13640,7 +13655,7 @@
         <v>2.38</v>
       </c>
       <c r="AP61">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ61">
         <v>2.43</v>
@@ -13768,7 +13783,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13974,7 +13989,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14052,7 +14067,7 @@
         <v>1.88</v>
       </c>
       <c r="AP63">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ63">
         <v>1.76</v>
@@ -14180,7 +14195,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14258,7 +14273,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ64">
         <v>1.05</v>
@@ -14386,7 +14401,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14592,7 +14607,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14670,7 +14685,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ66">
         <v>1.76</v>
@@ -14879,7 +14894,7 @@
         <v>0.95</v>
       </c>
       <c r="AQ67">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AR67">
         <v>1.27</v>
@@ -15004,7 +15019,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15082,7 +15097,7 @@
         <v>1.89</v>
       </c>
       <c r="AP68">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ68">
         <v>2.1</v>
@@ -15291,7 +15306,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ69">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR69">
         <v>1.49</v>
@@ -15494,10 +15509,10 @@
         <v>1.22</v>
       </c>
       <c r="AP70">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ70">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR70">
         <v>1.5</v>
@@ -15622,7 +15637,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15703,7 +15718,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ71">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR71">
         <v>1.36</v>
@@ -15906,7 +15921,7 @@
         <v>0.9</v>
       </c>
       <c r="AP72">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ72">
         <v>1.05</v>
@@ -16034,7 +16049,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16112,10 +16127,10 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ73">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AR73">
         <v>1.4</v>
@@ -16240,7 +16255,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16318,7 +16333,7 @@
         <v>2.5</v>
       </c>
       <c r="AP74">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ74">
         <v>2.43</v>
@@ -16446,7 +16461,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16652,7 +16667,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16858,7 +16873,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -16936,10 +16951,10 @@
         <v>1.8</v>
       </c>
       <c r="AP77">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ77">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR77">
         <v>1.32</v>
@@ -17145,7 +17160,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ78">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR78">
         <v>1.74</v>
@@ -17270,7 +17285,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17348,10 +17363,10 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ79">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR79">
         <v>1.41</v>
@@ -17554,7 +17569,7 @@
         <v>0.82</v>
       </c>
       <c r="AP80">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ80">
         <v>1.05</v>
@@ -17760,7 +17775,7 @@
         <v>1.45</v>
       </c>
       <c r="AP81">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AQ81">
         <v>1.24</v>
@@ -17888,7 +17903,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17966,7 +17981,7 @@
         <v>1.91</v>
       </c>
       <c r="AP82">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ82">
         <v>2.1</v>
@@ -18094,7 +18109,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18381,7 +18396,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ84">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR84">
         <v>1.26</v>
@@ -18506,7 +18521,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18584,7 +18599,7 @@
         <v>1.91</v>
       </c>
       <c r="AP85">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ85">
         <v>1.43</v>
@@ -18712,7 +18727,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18996,7 +19011,7 @@
         <v>0.67</v>
       </c>
       <c r="AP87">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ87">
         <v>0.95</v>
@@ -19205,7 +19220,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ88">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR88">
         <v>1.13</v>
@@ -19330,7 +19345,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19408,10 +19423,10 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ89">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19536,7 +19551,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19614,10 +19629,10 @@
         <v>1.75</v>
       </c>
       <c r="AP90">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ90">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AR90">
         <v>1.58</v>
@@ -19948,7 +19963,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20029,7 +20044,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ92">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR92">
         <v>1.79</v>
@@ -20154,7 +20169,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20235,7 +20250,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ93">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR93">
         <v>1.28</v>
@@ -20360,7 +20375,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20566,7 +20581,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20644,10 +20659,10 @@
         <v>1.08</v>
       </c>
       <c r="AP95">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ95">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AR95">
         <v>1.31</v>
@@ -21056,10 +21071,10 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ97">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR97">
         <v>1.59</v>
@@ -21184,7 +21199,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21265,7 +21280,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ98">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AR98">
         <v>1.78</v>
@@ -21390,7 +21405,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21468,7 +21483,7 @@
         <v>2.62</v>
       </c>
       <c r="AP99">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AQ99">
         <v>2.43</v>
@@ -21596,7 +21611,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21802,7 +21817,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -21880,10 +21895,10 @@
         <v>1.29</v>
       </c>
       <c r="AP101">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ101">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR101">
         <v>1.31</v>
@@ -22086,7 +22101,7 @@
         <v>0.64</v>
       </c>
       <c r="AP102">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ102">
         <v>1.05</v>
@@ -22214,7 +22229,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22292,7 +22307,7 @@
         <v>0.86</v>
       </c>
       <c r="AP103">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ103">
         <v>0.95</v>
@@ -22420,7 +22435,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22707,7 +22722,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ105">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AR105">
         <v>1.57</v>
@@ -22910,10 +22925,10 @@
         <v>0.36</v>
       </c>
       <c r="AP106">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ106">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR106">
         <v>1.44</v>
@@ -23038,7 +23053,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23116,10 +23131,10 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ107">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR107">
         <v>1.57</v>
@@ -23244,7 +23259,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23322,7 +23337,7 @@
         <v>1.87</v>
       </c>
       <c r="AP108">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ108">
         <v>1.43</v>
@@ -23528,7 +23543,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ109">
         <v>1.24</v>
@@ -23737,7 +23752,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ110">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR110">
         <v>1.26</v>
@@ -24146,10 +24161,10 @@
         <v>1.13</v>
       </c>
       <c r="AP112">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ112">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AR112">
         <v>1.45</v>
@@ -24274,7 +24289,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24686,7 +24701,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -24764,7 +24779,7 @@
         <v>1.75</v>
       </c>
       <c r="AP115">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AQ115">
         <v>1.43</v>
@@ -24973,7 +24988,7 @@
         <v>0.95</v>
       </c>
       <c r="AQ116">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AR116">
         <v>1.16</v>
@@ -25098,7 +25113,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25179,7 +25194,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ117">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR117">
         <v>1.18</v>
@@ -25382,10 +25397,10 @@
         <v>0.75</v>
       </c>
       <c r="AP118">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ118">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -25510,7 +25525,7 @@
         <v>92</v>
       </c>
       <c r="P119" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q119">
         <v>4.4</v>
@@ -25588,7 +25603,7 @@
         <v>1.94</v>
       </c>
       <c r="AP119">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ119">
         <v>2.1</v>
@@ -25797,7 +25812,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ120">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR120">
         <v>1.33</v>
@@ -25922,7 +25937,7 @@
         <v>163</v>
       </c>
       <c r="P121" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q121">
         <v>2.93</v>
@@ -26000,7 +26015,7 @@
         <v>1.65</v>
       </c>
       <c r="AP121">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ121">
         <v>1.43</v>
@@ -26206,10 +26221,10 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ122">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -26415,7 +26430,7 @@
         <v>0.95</v>
       </c>
       <c r="AQ123">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR123">
         <v>1.12</v>
@@ -26746,7 +26761,7 @@
         <v>166</v>
       </c>
       <c r="P125" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -26827,7 +26842,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ125">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR125">
         <v>1.76</v>
@@ -26952,7 +26967,7 @@
         <v>167</v>
       </c>
       <c r="P126" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27030,7 +27045,7 @@
         <v>1.76</v>
       </c>
       <c r="AP126">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ126">
         <v>1.76</v>
@@ -27158,7 +27173,7 @@
         <v>168</v>
       </c>
       <c r="P127" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27236,7 +27251,7 @@
         <v>2.59</v>
       </c>
       <c r="AP127">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ127">
         <v>2.43</v>
@@ -27364,7 +27379,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27442,7 +27457,7 @@
         <v>1.94</v>
       </c>
       <c r="AP128">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ128">
         <v>2.1</v>
@@ -27570,7 +27585,7 @@
         <v>170</v>
       </c>
       <c r="P129" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q129">
         <v>4.33</v>
@@ -27776,7 +27791,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q130">
         <v>4.2</v>
@@ -27854,7 +27869,7 @@
         <v>1.61</v>
       </c>
       <c r="AP130">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ130">
         <v>1.43</v>
@@ -28060,7 +28075,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP131">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ131">
         <v>0.95</v>
@@ -28269,7 +28284,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ132">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AR132">
         <v>1.19</v>
@@ -28472,10 +28487,10 @@
         <v>1.67</v>
       </c>
       <c r="AP133">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ133">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR133">
         <v>1.45</v>
@@ -28681,7 +28696,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ134">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR134">
         <v>1.19</v>
@@ -28887,7 +28902,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ135">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR135">
         <v>1.78</v>
@@ -29012,7 +29027,7 @@
         <v>175</v>
       </c>
       <c r="P136" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q136">
         <v>3.2</v>
@@ -29090,7 +29105,7 @@
         <v>0.84</v>
       </c>
       <c r="AP136">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AQ136">
         <v>1.05</v>
@@ -29299,7 +29314,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ137">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AR137">
         <v>1.3</v>
@@ -29502,7 +29517,7 @@
         <v>1.16</v>
       </c>
       <c r="AP138">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ138">
         <v>1.24</v>
@@ -29630,7 +29645,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -29711,7 +29726,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ139">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR139">
         <v>1.47</v>
@@ -29914,10 +29929,10 @@
         <v>1.26</v>
       </c>
       <c r="AP140">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ140">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR140">
         <v>1.51</v>
@@ -30042,7 +30057,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30248,7 +30263,7 @@
         <v>179</v>
       </c>
       <c r="P142" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30454,7 +30469,7 @@
         <v>180</v>
       </c>
       <c r="P143" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30532,7 +30547,7 @@
         <v>0.95</v>
       </c>
       <c r="AP143">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ143">
         <v>0.95</v>
@@ -30947,7 +30962,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ145">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR145">
         <v>1.17</v>
@@ -31072,7 +31087,7 @@
         <v>182</v>
       </c>
       <c r="P146" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q146">
         <v>2.9</v>
@@ -31150,10 +31165,10 @@
         <v>1.25</v>
       </c>
       <c r="AP146">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AQ146">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR146">
         <v>1.48</v>
@@ -31356,10 +31371,10 @@
         <v>0.65</v>
       </c>
       <c r="AP147">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ147">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AR147">
         <v>1.32</v>
@@ -31484,7 +31499,7 @@
         <v>85</v>
       </c>
       <c r="P148" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q148">
         <v>5.5</v>
@@ -31562,7 +31577,7 @@
         <v>2.4</v>
       </c>
       <c r="AP148">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AQ148">
         <v>2.43</v>
@@ -31641,6 +31656,830 @@
       </c>
       <c r="BP148">
         <v>1.06</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7813968</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45864.29166666666</v>
+      </c>
+      <c r="F149">
+        <v>22</v>
+      </c>
+      <c r="G149" t="s">
+        <v>72</v>
+      </c>
+      <c r="H149" t="s">
+        <v>76</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
+      <c r="L149">
+        <v>4</v>
+      </c>
+      <c r="M149">
+        <v>2</v>
+      </c>
+      <c r="N149">
+        <v>6</v>
+      </c>
+      <c r="O149" t="s">
+        <v>184</v>
+      </c>
+      <c r="P149" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q149">
+        <v>3.25</v>
+      </c>
+      <c r="R149">
+        <v>2.1</v>
+      </c>
+      <c r="S149">
+        <v>3.1</v>
+      </c>
+      <c r="T149">
+        <v>1.4</v>
+      </c>
+      <c r="U149">
+        <v>2.85</v>
+      </c>
+      <c r="V149">
+        <v>3.03</v>
+      </c>
+      <c r="W149">
+        <v>1.36</v>
+      </c>
+      <c r="X149">
+        <v>7.3</v>
+      </c>
+      <c r="Y149">
+        <v>1.03</v>
+      </c>
+      <c r="Z149">
+        <v>2.33</v>
+      </c>
+      <c r="AA149">
+        <v>3.15</v>
+      </c>
+      <c r="AB149">
+        <v>2.69</v>
+      </c>
+      <c r="AC149">
+        <v>1.03</v>
+      </c>
+      <c r="AD149">
+        <v>9</v>
+      </c>
+      <c r="AE149">
+        <v>1.29</v>
+      </c>
+      <c r="AF149">
+        <v>3.3</v>
+      </c>
+      <c r="AG149">
+        <v>1.96</v>
+      </c>
+      <c r="AH149">
+        <v>1.74</v>
+      </c>
+      <c r="AI149">
+        <v>1.73</v>
+      </c>
+      <c r="AJ149">
+        <v>2</v>
+      </c>
+      <c r="AK149">
+        <v>1.44</v>
+      </c>
+      <c r="AL149">
+        <v>1.28</v>
+      </c>
+      <c r="AM149">
+        <v>1.43</v>
+      </c>
+      <c r="AN149">
+        <v>1.48</v>
+      </c>
+      <c r="AO149">
+        <v>1.81</v>
+      </c>
+      <c r="AP149">
+        <v>1.55</v>
+      </c>
+      <c r="AQ149">
+        <v>1.73</v>
+      </c>
+      <c r="AR149">
+        <v>1.45</v>
+      </c>
+      <c r="AS149">
+        <v>1.5</v>
+      </c>
+      <c r="AT149">
+        <v>2.95</v>
+      </c>
+      <c r="AU149">
+        <v>9</v>
+      </c>
+      <c r="AV149">
+        <v>10</v>
+      </c>
+      <c r="AW149">
+        <v>5</v>
+      </c>
+      <c r="AX149">
+        <v>3</v>
+      </c>
+      <c r="AY149">
+        <v>14</v>
+      </c>
+      <c r="AZ149">
+        <v>13</v>
+      </c>
+      <c r="BA149">
+        <v>2</v>
+      </c>
+      <c r="BB149">
+        <v>3</v>
+      </c>
+      <c r="BC149">
+        <v>5</v>
+      </c>
+      <c r="BD149">
+        <v>0</v>
+      </c>
+      <c r="BE149">
+        <v>0</v>
+      </c>
+      <c r="BF149">
+        <v>0</v>
+      </c>
+      <c r="BG149">
+        <v>1.54</v>
+      </c>
+      <c r="BH149">
+        <v>2.28</v>
+      </c>
+      <c r="BI149">
+        <v>2</v>
+      </c>
+      <c r="BJ149">
+        <v>1.8</v>
+      </c>
+      <c r="BK149">
+        <v>2.53</v>
+      </c>
+      <c r="BL149">
+        <v>1.43</v>
+      </c>
+      <c r="BM149">
+        <v>3.54</v>
+      </c>
+      <c r="BN149">
+        <v>1.21</v>
+      </c>
+      <c r="BO149">
+        <v>5.35</v>
+      </c>
+      <c r="BP149">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7813969</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45864.29166666666</v>
+      </c>
+      <c r="F150">
+        <v>22</v>
+      </c>
+      <c r="G150" t="s">
+        <v>71</v>
+      </c>
+      <c r="H150" t="s">
+        <v>80</v>
+      </c>
+      <c r="I150">
+        <v>2</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>2</v>
+      </c>
+      <c r="L150">
+        <v>4</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>4</v>
+      </c>
+      <c r="O150" t="s">
+        <v>185</v>
+      </c>
+      <c r="P150" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q150">
+        <v>3.1</v>
+      </c>
+      <c r="R150">
+        <v>2.1</v>
+      </c>
+      <c r="S150">
+        <v>3.1</v>
+      </c>
+      <c r="T150">
+        <v>1.36</v>
+      </c>
+      <c r="U150">
+        <v>3.07</v>
+      </c>
+      <c r="V150">
+        <v>2.8</v>
+      </c>
+      <c r="W150">
+        <v>1.41</v>
+      </c>
+      <c r="X150">
+        <v>7.2</v>
+      </c>
+      <c r="Y150">
+        <v>1.03</v>
+      </c>
+      <c r="Z150">
+        <v>2.44</v>
+      </c>
+      <c r="AA150">
+        <v>3.21</v>
+      </c>
+      <c r="AB150">
+        <v>2.51</v>
+      </c>
+      <c r="AC150">
+        <v>1.02</v>
+      </c>
+      <c r="AD150">
+        <v>10</v>
+      </c>
+      <c r="AE150">
+        <v>1.25</v>
+      </c>
+      <c r="AF150">
+        <v>3.6</v>
+      </c>
+      <c r="AG150">
+        <v>1.83</v>
+      </c>
+      <c r="AH150">
+        <v>1.87</v>
+      </c>
+      <c r="AI150">
+        <v>1.67</v>
+      </c>
+      <c r="AJ150">
+        <v>2.1</v>
+      </c>
+      <c r="AK150">
+        <v>1.41</v>
+      </c>
+      <c r="AL150">
+        <v>1.27</v>
+      </c>
+      <c r="AM150">
+        <v>1.48</v>
+      </c>
+      <c r="AN150">
+        <v>0.62</v>
+      </c>
+      <c r="AO150">
+        <v>0.86</v>
+      </c>
+      <c r="AP150">
+        <v>0.73</v>
+      </c>
+      <c r="AQ150">
+        <v>0.82</v>
+      </c>
+      <c r="AR150">
+        <v>1.18</v>
+      </c>
+      <c r="AS150">
+        <v>1.35</v>
+      </c>
+      <c r="AT150">
+        <v>2.53</v>
+      </c>
+      <c r="AU150">
+        <v>9</v>
+      </c>
+      <c r="AV150">
+        <v>4</v>
+      </c>
+      <c r="AW150">
+        <v>12</v>
+      </c>
+      <c r="AX150">
+        <v>6</v>
+      </c>
+      <c r="AY150">
+        <v>21</v>
+      </c>
+      <c r="AZ150">
+        <v>10</v>
+      </c>
+      <c r="BA150">
+        <v>8</v>
+      </c>
+      <c r="BB150">
+        <v>1</v>
+      </c>
+      <c r="BC150">
+        <v>9</v>
+      </c>
+      <c r="BD150">
+        <v>0</v>
+      </c>
+      <c r="BE150">
+        <v>0</v>
+      </c>
+      <c r="BF150">
+        <v>0</v>
+      </c>
+      <c r="BG150">
+        <v>1.45</v>
+      </c>
+      <c r="BH150">
+        <v>2.48</v>
+      </c>
+      <c r="BI150">
+        <v>1.85</v>
+      </c>
+      <c r="BJ150">
+        <v>1.95</v>
+      </c>
+      <c r="BK150">
+        <v>2.32</v>
+      </c>
+      <c r="BL150">
+        <v>1.52</v>
+      </c>
+      <c r="BM150">
+        <v>3.15</v>
+      </c>
+      <c r="BN150">
+        <v>1.27</v>
+      </c>
+      <c r="BO150">
+        <v>4.62</v>
+      </c>
+      <c r="BP150">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7813970</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45864.29166666666</v>
+      </c>
+      <c r="F151">
+        <v>22</v>
+      </c>
+      <c r="G151" t="s">
+        <v>82</v>
+      </c>
+      <c r="H151" t="s">
+        <v>78</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>3</v>
+      </c>
+      <c r="N151">
+        <v>3</v>
+      </c>
+      <c r="O151" t="s">
+        <v>85</v>
+      </c>
+      <c r="P151" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q151">
+        <v>4</v>
+      </c>
+      <c r="R151">
+        <v>2</v>
+      </c>
+      <c r="S151">
+        <v>2.7</v>
+      </c>
+      <c r="T151">
+        <v>1.44</v>
+      </c>
+      <c r="U151">
+        <v>2.71</v>
+      </c>
+      <c r="V151">
+        <v>3.24</v>
+      </c>
+      <c r="W151">
+        <v>1.32</v>
+      </c>
+      <c r="X151">
+        <v>9</v>
+      </c>
+      <c r="Y151">
+        <v>1</v>
+      </c>
+      <c r="Z151">
+        <v>3.1</v>
+      </c>
+      <c r="AA151">
+        <v>3.2</v>
+      </c>
+      <c r="AB151">
+        <v>2.15</v>
+      </c>
+      <c r="AC151">
+        <v>1.05</v>
+      </c>
+      <c r="AD151">
+        <v>8</v>
+      </c>
+      <c r="AE151">
+        <v>1.36</v>
+      </c>
+      <c r="AF151">
+        <v>2.88</v>
+      </c>
+      <c r="AG151">
+        <v>2.2</v>
+      </c>
+      <c r="AH151">
+        <v>1.6</v>
+      </c>
+      <c r="AI151">
+        <v>2</v>
+      </c>
+      <c r="AJ151">
+        <v>1.8</v>
+      </c>
+      <c r="AK151">
+        <v>1.6</v>
+      </c>
+      <c r="AL151">
+        <v>1.3</v>
+      </c>
+      <c r="AM151">
+        <v>1.3</v>
+      </c>
+      <c r="AN151">
+        <v>0.95</v>
+      </c>
+      <c r="AO151">
+        <v>1.24</v>
+      </c>
+      <c r="AP151">
+        <v>0.91</v>
+      </c>
+      <c r="AQ151">
+        <v>1.32</v>
+      </c>
+      <c r="AR151">
+        <v>1.31</v>
+      </c>
+      <c r="AS151">
+        <v>1.44</v>
+      </c>
+      <c r="AT151">
+        <v>2.75</v>
+      </c>
+      <c r="AU151">
+        <v>6</v>
+      </c>
+      <c r="AV151">
+        <v>11</v>
+      </c>
+      <c r="AW151">
+        <v>5</v>
+      </c>
+      <c r="AX151">
+        <v>3</v>
+      </c>
+      <c r="AY151">
+        <v>11</v>
+      </c>
+      <c r="AZ151">
+        <v>14</v>
+      </c>
+      <c r="BA151">
+        <v>4</v>
+      </c>
+      <c r="BB151">
+        <v>6</v>
+      </c>
+      <c r="BC151">
+        <v>10</v>
+      </c>
+      <c r="BD151">
+        <v>0</v>
+      </c>
+      <c r="BE151">
+        <v>0</v>
+      </c>
+      <c r="BF151">
+        <v>0</v>
+      </c>
+      <c r="BG151">
+        <v>1.67</v>
+      </c>
+      <c r="BH151">
+        <v>2.08</v>
+      </c>
+      <c r="BI151">
+        <v>2.12</v>
+      </c>
+      <c r="BJ151">
+        <v>1.64</v>
+      </c>
+      <c r="BK151">
+        <v>2.86</v>
+      </c>
+      <c r="BL151">
+        <v>1.34</v>
+      </c>
+      <c r="BM151">
+        <v>4.15</v>
+      </c>
+      <c r="BN151">
+        <v>1.15</v>
+      </c>
+      <c r="BO151">
+        <v>6.52</v>
+      </c>
+      <c r="BP151">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7813971</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45864.29166666666</v>
+      </c>
+      <c r="F152">
+        <v>22</v>
+      </c>
+      <c r="G152" t="s">
+        <v>81</v>
+      </c>
+      <c r="H152" t="s">
+        <v>77</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>1</v>
+      </c>
+      <c r="M152">
+        <v>1</v>
+      </c>
+      <c r="N152">
+        <v>2</v>
+      </c>
+      <c r="O152" t="s">
+        <v>186</v>
+      </c>
+      <c r="P152" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q152">
+        <v>2.3</v>
+      </c>
+      <c r="R152">
+        <v>2.1</v>
+      </c>
+      <c r="S152">
+        <v>4.5</v>
+      </c>
+      <c r="T152">
+        <v>1.38</v>
+      </c>
+      <c r="U152">
+        <v>2.95</v>
+      </c>
+      <c r="V152">
+        <v>2.93</v>
+      </c>
+      <c r="W152">
+        <v>1.38</v>
+      </c>
+      <c r="X152">
+        <v>6.9</v>
+      </c>
+      <c r="Y152">
+        <v>1.04</v>
+      </c>
+      <c r="Z152">
+        <v>1.65</v>
+      </c>
+      <c r="AA152">
+        <v>3.58</v>
+      </c>
+      <c r="AB152">
+        <v>4.3</v>
+      </c>
+      <c r="AC152">
+        <v>1.03</v>
+      </c>
+      <c r="AD152">
+        <v>9</v>
+      </c>
+      <c r="AE152">
+        <v>1.29</v>
+      </c>
+      <c r="AF152">
+        <v>3.3</v>
+      </c>
+      <c r="AG152">
+        <v>1.9</v>
+      </c>
+      <c r="AH152">
+        <v>1.8</v>
+      </c>
+      <c r="AI152">
+        <v>1.91</v>
+      </c>
+      <c r="AJ152">
+        <v>1.8</v>
+      </c>
+      <c r="AK152">
+        <v>1.15</v>
+      </c>
+      <c r="AL152">
+        <v>1.23</v>
+      </c>
+      <c r="AM152">
+        <v>2.03</v>
+      </c>
+      <c r="AN152">
+        <v>1.19</v>
+      </c>
+      <c r="AO152">
+        <v>1.05</v>
+      </c>
+      <c r="AP152">
+        <v>1.18</v>
+      </c>
+      <c r="AQ152">
+        <v>1.05</v>
+      </c>
+      <c r="AR152">
+        <v>1.56</v>
+      </c>
+      <c r="AS152">
+        <v>1.16</v>
+      </c>
+      <c r="AT152">
+        <v>2.72</v>
+      </c>
+      <c r="AU152">
+        <v>4</v>
+      </c>
+      <c r="AV152">
+        <v>3</v>
+      </c>
+      <c r="AW152">
+        <v>6</v>
+      </c>
+      <c r="AX152">
+        <v>2</v>
+      </c>
+      <c r="AY152">
+        <v>10</v>
+      </c>
+      <c r="AZ152">
+        <v>5</v>
+      </c>
+      <c r="BA152">
+        <v>8</v>
+      </c>
+      <c r="BB152">
+        <v>1</v>
+      </c>
+      <c r="BC152">
+        <v>9</v>
+      </c>
+      <c r="BD152">
+        <v>0</v>
+      </c>
+      <c r="BE152">
+        <v>0</v>
+      </c>
+      <c r="BF152">
+        <v>0</v>
+      </c>
+      <c r="BG152">
+        <v>1.54</v>
+      </c>
+      <c r="BH152">
+        <v>2.28</v>
+      </c>
+      <c r="BI152">
+        <v>2</v>
+      </c>
+      <c r="BJ152">
+        <v>1.8</v>
+      </c>
+      <c r="BK152">
+        <v>2.53</v>
+      </c>
+      <c r="BL152">
+        <v>1.43</v>
+      </c>
+      <c r="BM152">
+        <v>3.54</v>
+      </c>
+      <c r="BN152">
+        <v>1.21</v>
+      </c>
+      <c r="BO152">
+        <v>5.35</v>
+      </c>
+      <c r="BP152">
+        <v>1.07</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="269">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -577,6 +577,12 @@
     <t>['54']</t>
   </si>
   <si>
+    <t>['59', '77']</t>
+  </si>
+  <si>
+    <t>['34', '45+3', '52', '90+3']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -806,6 +812,15 @@
   </si>
   <si>
     <t>['51', '73', '90+3']</t>
+  </si>
+  <si>
+    <t>['69', '83']</t>
+  </si>
+  <si>
+    <t>['14', '59']</t>
+  </si>
+  <si>
+    <t>['54', '62']</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP152"/>
+  <dimension ref="A1:BP155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1501,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ2">
         <v>0.82</v>
@@ -1629,7 +1644,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1710,7 +1725,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ3">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2119,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ5">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2325,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ6">
         <v>1.05</v>
@@ -2531,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
         <v>1.18</v>
@@ -2659,7 +2674,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2943,10 +2958,10 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ9">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -3071,7 +3086,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3149,7 +3164,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ10">
         <v>1.32</v>
@@ -3277,7 +3292,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3355,10 +3370,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3689,7 +3704,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3895,7 +3910,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -4179,7 +4194,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ15">
         <v>0.91</v>
@@ -4307,7 +4322,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4513,7 +4528,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4797,10 +4812,10 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ18">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR18">
         <v>1.29</v>
@@ -4925,7 +4940,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -5131,7 +5146,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5209,10 +5224,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR20">
         <v>1.06</v>
@@ -5543,7 +5558,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5621,10 +5636,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ22">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
@@ -5827,10 +5842,10 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ23">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR23">
         <v>1.7</v>
@@ -6242,7 +6257,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ25">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR25">
         <v>1.64</v>
@@ -6445,7 +6460,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>1.18</v>
@@ -6573,7 +6588,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6779,7 +6794,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6860,7 +6875,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ28">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR28">
         <v>1.05</v>
@@ -6985,7 +7000,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7066,7 +7081,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ29">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR29">
         <v>1.37</v>
@@ -7191,7 +7206,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7269,7 +7284,7 @@
         <v>1.25</v>
       </c>
       <c r="AP30">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ30">
         <v>1.05</v>
@@ -7397,7 +7412,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7475,10 +7490,10 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR31">
         <v>1.56</v>
@@ -7809,7 +7824,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7887,7 +7902,7 @@
         <v>1.75</v>
       </c>
       <c r="AP33">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ33">
         <v>1.55</v>
@@ -8015,7 +8030,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8221,7 +8236,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8299,7 +8314,7 @@
         <v>2.25</v>
       </c>
       <c r="AP35">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ35">
         <v>1.73</v>
@@ -8508,7 +8523,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ36">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR36">
         <v>1.34</v>
@@ -8711,7 +8726,7 @@
         <v>0.6</v>
       </c>
       <c r="AP37">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37">
         <v>0.73</v>
@@ -8839,7 +8854,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8920,7 +8935,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ38">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AR38">
         <v>1.37</v>
@@ -9045,7 +9060,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9126,7 +9141,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ39">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR39">
         <v>1.38</v>
@@ -9329,7 +9344,7 @@
         <v>1.6</v>
       </c>
       <c r="AP40">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
         <v>0.82</v>
@@ -9457,7 +9472,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9947,10 +9962,10 @@
         <v>0.2</v>
       </c>
       <c r="AP43">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ43">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR43">
         <v>0.96</v>
@@ -10075,7 +10090,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10281,7 +10296,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10362,7 +10377,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ45">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR45">
         <v>1.34</v>
@@ -10487,7 +10502,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10568,7 +10583,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ46">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR46">
         <v>1.42</v>
@@ -10693,7 +10708,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10774,7 +10789,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ47">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR47">
         <v>1.33</v>
@@ -10977,7 +10992,7 @@
         <v>0.67</v>
       </c>
       <c r="AP48">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ48">
         <v>0.91</v>
@@ -11105,7 +11120,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11186,7 +11201,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ49">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR49">
         <v>1.4</v>
@@ -11392,7 +11407,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ50">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR50">
         <v>0.9399999999999999</v>
@@ -11517,7 +11532,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11595,7 +11610,7 @@
         <v>0.57</v>
       </c>
       <c r="AP51">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ51">
         <v>0.91</v>
@@ -11801,7 +11816,7 @@
         <v>0.43</v>
       </c>
       <c r="AP52">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ52">
         <v>0.73</v>
@@ -12007,7 +12022,7 @@
         <v>0.86</v>
       </c>
       <c r="AP53">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
         <v>1.05</v>
@@ -12213,7 +12228,7 @@
         <v>1.86</v>
       </c>
       <c r="AP54">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ54">
         <v>1.73</v>
@@ -12341,7 +12356,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12419,7 +12434,7 @@
         <v>1.29</v>
       </c>
       <c r="AP55">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ55">
         <v>1.55</v>
@@ -12628,7 +12643,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ56">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -12753,7 +12768,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12959,7 +12974,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -13037,7 +13052,7 @@
         <v>1.38</v>
       </c>
       <c r="AP58">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
         <v>0.82</v>
@@ -13165,7 +13180,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13452,7 +13467,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ60">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR60">
         <v>1.58</v>
@@ -13577,7 +13592,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13658,7 +13673,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ61">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AR61">
         <v>1.46</v>
@@ -13783,7 +13798,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13861,10 +13876,10 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR62">
         <v>1.72</v>
@@ -13989,7 +14004,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14070,7 +14085,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ63">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR63">
         <v>1.43</v>
@@ -14195,7 +14210,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14401,7 +14416,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14479,10 +14494,10 @@
         <v>1.89</v>
       </c>
       <c r="AP65">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ65">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
         <v>1.05</v>
@@ -14607,7 +14622,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14688,7 +14703,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ66">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR66">
         <v>1.5</v>
@@ -14891,7 +14906,7 @@
         <v>1.22</v>
       </c>
       <c r="AP67">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ67">
         <v>0.82</v>
@@ -15019,7 +15034,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15100,7 +15115,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ68">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR68">
         <v>1.25</v>
@@ -15303,7 +15318,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ69">
         <v>1.32</v>
@@ -15637,7 +15652,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -16049,7 +16064,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16255,7 +16270,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16336,7 +16351,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ74">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AR74">
         <v>1.57</v>
@@ -16461,7 +16476,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16539,10 +16554,10 @@
         <v>0.7</v>
       </c>
       <c r="AP75">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ75">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR75">
         <v>1.34</v>
@@ -16667,7 +16682,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16745,10 +16760,10 @@
         <v>1.6</v>
       </c>
       <c r="AP76">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ76">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR76">
         <v>1.29</v>
@@ -16873,7 +16888,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17157,7 +17172,7 @@
         <v>0.3</v>
       </c>
       <c r="AP78">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
         <v>0.73</v>
@@ -17285,7 +17300,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17778,7 +17793,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ81">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR81">
         <v>1.16</v>
@@ -17903,7 +17918,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17984,7 +17999,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ82">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR82">
         <v>1.47</v>
@@ -18109,7 +18124,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18187,10 +18202,10 @@
         <v>2.55</v>
       </c>
       <c r="AP83">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ83">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AR83">
         <v>1.25</v>
@@ -18393,7 +18408,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ84">
         <v>0.91</v>
@@ -18521,7 +18536,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18602,7 +18617,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ85">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR85">
         <v>1.45</v>
@@ -18727,7 +18742,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18808,7 +18823,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ86">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR86">
         <v>1.26</v>
@@ -19014,7 +19029,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ87">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR87">
         <v>1.32</v>
@@ -19217,7 +19232,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ88">
         <v>1.55</v>
@@ -19345,7 +19360,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19551,7 +19566,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19835,10 +19850,10 @@
         <v>2.08</v>
       </c>
       <c r="AP91">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ91">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR91">
         <v>1.49</v>
@@ -19963,7 +19978,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20041,7 +20056,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>1.32</v>
@@ -20169,7 +20184,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20247,7 +20262,7 @@
         <v>1.69</v>
       </c>
       <c r="AP93">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ93">
         <v>1.55</v>
@@ -20375,7 +20390,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20453,7 +20468,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP94">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ94">
         <v>1.05</v>
@@ -20581,7 +20596,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20865,10 +20880,10 @@
         <v>1.38</v>
       </c>
       <c r="AP96">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ96">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR96">
         <v>1.23</v>
@@ -21199,7 +21214,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21277,7 +21292,7 @@
         <v>1.69</v>
       </c>
       <c r="AP98">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ98">
         <v>1.73</v>
@@ -21405,7 +21420,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21486,7 +21501,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ99">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AR99">
         <v>1.23</v>
@@ -21611,7 +21626,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21689,10 +21704,10 @@
         <v>2</v>
       </c>
       <c r="AP100">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ100">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR100">
         <v>1.13</v>
@@ -21817,7 +21832,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -22229,7 +22244,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22310,7 +22325,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ103">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR103">
         <v>1.45</v>
@@ -22435,7 +22450,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22513,10 +22528,10 @@
         <v>1.93</v>
       </c>
       <c r="AP104">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ104">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR104">
         <v>1.27</v>
@@ -22719,7 +22734,7 @@
         <v>1.57</v>
       </c>
       <c r="AP105">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ105">
         <v>1.73</v>
@@ -23053,7 +23068,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23259,7 +23274,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23340,7 +23355,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ108">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR108">
         <v>1.45</v>
@@ -23546,7 +23561,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ109">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR109">
         <v>1.29</v>
@@ -23749,7 +23764,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ110">
         <v>1.55</v>
@@ -23958,7 +23973,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ111">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR111">
         <v>1.29</v>
@@ -24289,7 +24304,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24367,10 +24382,10 @@
         <v>2.53</v>
       </c>
       <c r="AP113">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ113">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AR113">
         <v>1.78</v>
@@ -24573,7 +24588,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP114">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ114">
         <v>1.05</v>
@@ -24701,7 +24716,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -24782,7 +24797,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ115">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR115">
         <v>1.17</v>
@@ -24985,7 +25000,7 @@
         <v>1.56</v>
       </c>
       <c r="AP116">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ116">
         <v>1.73</v>
@@ -25113,7 +25128,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25191,7 +25206,7 @@
         <v>1.31</v>
       </c>
       <c r="AP117">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ117">
         <v>1.18</v>
@@ -25525,7 +25540,7 @@
         <v>92</v>
       </c>
       <c r="P119" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q119">
         <v>4.4</v>
@@ -25606,7 +25621,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ119">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR119">
         <v>1.42</v>
@@ -25809,7 +25824,7 @@
         <v>1.19</v>
       </c>
       <c r="AP120">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ120">
         <v>1.32</v>
@@ -25937,7 +25952,7 @@
         <v>163</v>
       </c>
       <c r="P121" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q121">
         <v>2.93</v>
@@ -26018,7 +26033,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ121">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR121">
         <v>1.58</v>
@@ -26427,7 +26442,7 @@
         <v>0.65</v>
       </c>
       <c r="AP123">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ123">
         <v>0.73</v>
@@ -26636,7 +26651,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ124">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR124">
         <v>1.21</v>
@@ -26761,7 +26776,7 @@
         <v>166</v>
       </c>
       <c r="P125" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -26839,7 +26854,7 @@
         <v>1.71</v>
       </c>
       <c r="AP125">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ125">
         <v>1.55</v>
@@ -26967,7 +26982,7 @@
         <v>167</v>
       </c>
       <c r="P126" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27048,7 +27063,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ126">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR126">
         <v>1.3</v>
@@ -27173,7 +27188,7 @@
         <v>168</v>
       </c>
       <c r="P127" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27254,7 +27269,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ127">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AR127">
         <v>1.46</v>
@@ -27379,7 +27394,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27460,7 +27475,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ128">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR128">
         <v>1.55</v>
@@ -27585,7 +27600,7 @@
         <v>170</v>
       </c>
       <c r="P129" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q129">
         <v>4.33</v>
@@ -27663,10 +27678,10 @@
         <v>2.5</v>
       </c>
       <c r="AP129">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ129">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AR129">
         <v>1.32</v>
@@ -27791,7 +27806,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q130">
         <v>4.2</v>
@@ -27872,7 +27887,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ130">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR130">
         <v>1.32</v>
@@ -28078,7 +28093,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ131">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR131">
         <v>1.39</v>
@@ -28693,7 +28708,7 @@
         <v>0.67</v>
       </c>
       <c r="AP134">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ134">
         <v>0.73</v>
@@ -28899,7 +28914,7 @@
         <v>0.89</v>
       </c>
       <c r="AP135">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ135">
         <v>0.91</v>
@@ -29027,7 +29042,7 @@
         <v>175</v>
       </c>
       <c r="P136" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q136">
         <v>3.2</v>
@@ -29311,7 +29326,7 @@
         <v>0.95</v>
       </c>
       <c r="AP137">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ137">
         <v>0.82</v>
@@ -29520,7 +29535,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ138">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR138">
         <v>1.45</v>
@@ -29645,7 +29660,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -29723,7 +29738,7 @@
         <v>1.32</v>
       </c>
       <c r="AP139">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AQ139">
         <v>1.18</v>
@@ -30057,7 +30072,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30135,10 +30150,10 @@
         <v>1.53</v>
       </c>
       <c r="AP141">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AQ141">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR141">
         <v>1.09</v>
@@ -30263,7 +30278,7 @@
         <v>179</v>
       </c>
       <c r="P142" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30341,10 +30356,10 @@
         <v>2.05</v>
       </c>
       <c r="AP142">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ142">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR142">
         <v>1.32</v>
@@ -30469,7 +30484,7 @@
         <v>180</v>
       </c>
       <c r="P143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30550,7 +30565,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ143">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AR143">
         <v>1.44</v>
@@ -30753,10 +30768,10 @@
         <v>1.15</v>
       </c>
       <c r="AP144">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ144">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR144">
         <v>1.36</v>
@@ -31087,7 +31102,7 @@
         <v>182</v>
       </c>
       <c r="P146" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q146">
         <v>2.9</v>
@@ -31499,7 +31514,7 @@
         <v>85</v>
       </c>
       <c r="P148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q148">
         <v>5.5</v>
@@ -31580,7 +31595,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ148">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AR148">
         <v>1.37</v>
@@ -31705,7 +31720,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q149">
         <v>3.25</v>
@@ -32117,7 +32132,7 @@
         <v>85</v>
       </c>
       <c r="P151" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q151">
         <v>4</v>
@@ -32480,6 +32495,624 @@
       </c>
       <c r="BP152">
         <v>1.07</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7813974</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45865.29166666666</v>
+      </c>
+      <c r="F153">
+        <v>22</v>
+      </c>
+      <c r="G153" t="s">
+        <v>74</v>
+      </c>
+      <c r="H153" t="s">
+        <v>83</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>2</v>
+      </c>
+      <c r="M153">
+        <v>2</v>
+      </c>
+      <c r="N153">
+        <v>4</v>
+      </c>
+      <c r="O153" t="s">
+        <v>187</v>
+      </c>
+      <c r="P153" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q153">
+        <v>3.25</v>
+      </c>
+      <c r="R153">
+        <v>2.1</v>
+      </c>
+      <c r="S153">
+        <v>3.1</v>
+      </c>
+      <c r="T153">
+        <v>1.4</v>
+      </c>
+      <c r="U153">
+        <v>2.8</v>
+      </c>
+      <c r="V153">
+        <v>3</v>
+      </c>
+      <c r="W153">
+        <v>1.36</v>
+      </c>
+      <c r="X153">
+        <v>8</v>
+      </c>
+      <c r="Y153">
+        <v>1.08</v>
+      </c>
+      <c r="Z153">
+        <v>2.57</v>
+      </c>
+      <c r="AA153">
+        <v>3.1</v>
+      </c>
+      <c r="AB153">
+        <v>2.45</v>
+      </c>
+      <c r="AC153">
+        <v>1</v>
+      </c>
+      <c r="AD153">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE153">
+        <v>1.28</v>
+      </c>
+      <c r="AF153">
+        <v>3.08</v>
+      </c>
+      <c r="AG153">
+        <v>1.95</v>
+      </c>
+      <c r="AH153">
+        <v>1.75</v>
+      </c>
+      <c r="AI153">
+        <v>1.83</v>
+      </c>
+      <c r="AJ153">
+        <v>1.91</v>
+      </c>
+      <c r="AK153">
+        <v>1.53</v>
+      </c>
+      <c r="AL153">
+        <v>1.35</v>
+      </c>
+      <c r="AM153">
+        <v>1.4</v>
+      </c>
+      <c r="AN153">
+        <v>1.24</v>
+      </c>
+      <c r="AO153">
+        <v>1.76</v>
+      </c>
+      <c r="AP153">
+        <v>1.23</v>
+      </c>
+      <c r="AQ153">
+        <v>1.73</v>
+      </c>
+      <c r="AR153">
+        <v>1.14</v>
+      </c>
+      <c r="AS153">
+        <v>1.35</v>
+      </c>
+      <c r="AT153">
+        <v>2.49</v>
+      </c>
+      <c r="AU153">
+        <v>5</v>
+      </c>
+      <c r="AV153">
+        <v>5</v>
+      </c>
+      <c r="AW153">
+        <v>5</v>
+      </c>
+      <c r="AX153">
+        <v>3</v>
+      </c>
+      <c r="AY153">
+        <v>10</v>
+      </c>
+      <c r="AZ153">
+        <v>8</v>
+      </c>
+      <c r="BA153">
+        <v>8</v>
+      </c>
+      <c r="BB153">
+        <v>6</v>
+      </c>
+      <c r="BC153">
+        <v>14</v>
+      </c>
+      <c r="BD153">
+        <v>1.91</v>
+      </c>
+      <c r="BE153">
+        <v>6</v>
+      </c>
+      <c r="BF153">
+        <v>2.34</v>
+      </c>
+      <c r="BG153">
+        <v>1.42</v>
+      </c>
+      <c r="BH153">
+        <v>2.55</v>
+      </c>
+      <c r="BI153">
+        <v>1.8</v>
+      </c>
+      <c r="BJ153">
+        <v>2</v>
+      </c>
+      <c r="BK153">
+        <v>2.25</v>
+      </c>
+      <c r="BL153">
+        <v>1.56</v>
+      </c>
+      <c r="BM153">
+        <v>3.04</v>
+      </c>
+      <c r="BN153">
+        <v>1.29</v>
+      </c>
+      <c r="BO153">
+        <v>4.4</v>
+      </c>
+      <c r="BP153">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7813973</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45865.29166666666</v>
+      </c>
+      <c r="F154">
+        <v>22</v>
+      </c>
+      <c r="G154" t="s">
+        <v>79</v>
+      </c>
+      <c r="H154" t="s">
+        <v>75</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>1</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>2</v>
+      </c>
+      <c r="N154">
+        <v>2</v>
+      </c>
+      <c r="O154" t="s">
+        <v>85</v>
+      </c>
+      <c r="P154" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q154">
+        <v>2.25</v>
+      </c>
+      <c r="R154">
+        <v>2.4</v>
+      </c>
+      <c r="S154">
+        <v>4.33</v>
+      </c>
+      <c r="T154">
+        <v>1.3</v>
+      </c>
+      <c r="U154">
+        <v>3.4</v>
+      </c>
+      <c r="V154">
+        <v>2.4</v>
+      </c>
+      <c r="W154">
+        <v>1.53</v>
+      </c>
+      <c r="X154">
+        <v>5.5</v>
+      </c>
+      <c r="Y154">
+        <v>1.12</v>
+      </c>
+      <c r="Z154">
+        <v>1.67</v>
+      </c>
+      <c r="AA154">
+        <v>3.8</v>
+      </c>
+      <c r="AB154">
+        <v>3.87</v>
+      </c>
+      <c r="AC154">
+        <v>1.01</v>
+      </c>
+      <c r="AD154">
+        <v>13</v>
+      </c>
+      <c r="AE154">
+        <v>1.17</v>
+      </c>
+      <c r="AF154">
+        <v>4.05</v>
+      </c>
+      <c r="AG154">
+        <v>1.6</v>
+      </c>
+      <c r="AH154">
+        <v>2.1</v>
+      </c>
+      <c r="AI154">
+        <v>1.62</v>
+      </c>
+      <c r="AJ154">
+        <v>2.25</v>
+      </c>
+      <c r="AK154">
+        <v>1.22</v>
+      </c>
+      <c r="AL154">
+        <v>1.25</v>
+      </c>
+      <c r="AM154">
+        <v>2.05</v>
+      </c>
+      <c r="AN154">
+        <v>2.1</v>
+      </c>
+      <c r="AO154">
+        <v>1.43</v>
+      </c>
+      <c r="AP154">
+        <v>2</v>
+      </c>
+      <c r="AQ154">
+        <v>1.5</v>
+      </c>
+      <c r="AR154">
+        <v>1.72</v>
+      </c>
+      <c r="AS154">
+        <v>1.38</v>
+      </c>
+      <c r="AT154">
+        <v>3.1</v>
+      </c>
+      <c r="AU154">
+        <v>4</v>
+      </c>
+      <c r="AV154">
+        <v>4</v>
+      </c>
+      <c r="AW154">
+        <v>9</v>
+      </c>
+      <c r="AX154">
+        <v>2</v>
+      </c>
+      <c r="AY154">
+        <v>13</v>
+      </c>
+      <c r="AZ154">
+        <v>6</v>
+      </c>
+      <c r="BA154">
+        <v>8</v>
+      </c>
+      <c r="BB154">
+        <v>4</v>
+      </c>
+      <c r="BC154">
+        <v>12</v>
+      </c>
+      <c r="BD154">
+        <v>1.61</v>
+      </c>
+      <c r="BE154">
+        <v>6.3</v>
+      </c>
+      <c r="BF154">
+        <v>2.96</v>
+      </c>
+      <c r="BG154">
+        <v>1.39</v>
+      </c>
+      <c r="BH154">
+        <v>2.65</v>
+      </c>
+      <c r="BI154">
+        <v>1.72</v>
+      </c>
+      <c r="BJ154">
+        <v>2</v>
+      </c>
+      <c r="BK154">
+        <v>2.18</v>
+      </c>
+      <c r="BL154">
+        <v>1.6</v>
+      </c>
+      <c r="BM154">
+        <v>2.9</v>
+      </c>
+      <c r="BN154">
+        <v>1.32</v>
+      </c>
+      <c r="BO154">
+        <v>4.16</v>
+      </c>
+      <c r="BP154">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7813972</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45865.29166666666</v>
+      </c>
+      <c r="F155">
+        <v>22</v>
+      </c>
+      <c r="G155" t="s">
+        <v>70</v>
+      </c>
+      <c r="H155" t="s">
+        <v>73</v>
+      </c>
+      <c r="I155">
+        <v>2</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>2</v>
+      </c>
+      <c r="L155">
+        <v>4</v>
+      </c>
+      <c r="M155">
+        <v>2</v>
+      </c>
+      <c r="N155">
+        <v>6</v>
+      </c>
+      <c r="O155" t="s">
+        <v>188</v>
+      </c>
+      <c r="P155" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q155">
+        <v>1.8</v>
+      </c>
+      <c r="R155">
+        <v>2.3</v>
+      </c>
+      <c r="S155">
+        <v>9</v>
+      </c>
+      <c r="T155">
+        <v>1.36</v>
+      </c>
+      <c r="U155">
+        <v>3</v>
+      </c>
+      <c r="V155">
+        <v>2.62</v>
+      </c>
+      <c r="W155">
+        <v>1.44</v>
+      </c>
+      <c r="X155">
+        <v>7</v>
+      </c>
+      <c r="Y155">
+        <v>1.08</v>
+      </c>
+      <c r="Z155">
+        <v>1.28</v>
+      </c>
+      <c r="AA155">
+        <v>4.6</v>
+      </c>
+      <c r="AB155">
+        <v>8</v>
+      </c>
+      <c r="AC155">
+        <v>1.01</v>
+      </c>
+      <c r="AD155">
+        <v>11</v>
+      </c>
+      <c r="AE155">
+        <v>1.22</v>
+      </c>
+      <c r="AF155">
+        <v>3.5</v>
+      </c>
+      <c r="AG155">
+        <v>1.88</v>
+      </c>
+      <c r="AH155">
+        <v>1.82</v>
+      </c>
+      <c r="AI155">
+        <v>2.15</v>
+      </c>
+      <c r="AJ155">
+        <v>1.65</v>
+      </c>
+      <c r="AK155">
+        <v>1.06</v>
+      </c>
+      <c r="AL155">
+        <v>1.18</v>
+      </c>
+      <c r="AM155">
+        <v>3.3</v>
+      </c>
+      <c r="AN155">
+        <v>2.43</v>
+      </c>
+      <c r="AO155">
+        <v>0.95</v>
+      </c>
+      <c r="AP155">
+        <v>2.45</v>
+      </c>
+      <c r="AQ155">
+        <v>0.91</v>
+      </c>
+      <c r="AR155">
+        <v>1.45</v>
+      </c>
+      <c r="AS155">
+        <v>1.09</v>
+      </c>
+      <c r="AT155">
+        <v>2.54</v>
+      </c>
+      <c r="AU155">
+        <v>6</v>
+      </c>
+      <c r="AV155">
+        <v>4</v>
+      </c>
+      <c r="AW155">
+        <v>7</v>
+      </c>
+      <c r="AX155">
+        <v>6</v>
+      </c>
+      <c r="AY155">
+        <v>13</v>
+      </c>
+      <c r="AZ155">
+        <v>10</v>
+      </c>
+      <c r="BA155">
+        <v>2</v>
+      </c>
+      <c r="BB155">
+        <v>2</v>
+      </c>
+      <c r="BC155">
+        <v>4</v>
+      </c>
+      <c r="BD155">
+        <v>1.25</v>
+      </c>
+      <c r="BE155">
+        <v>8.9</v>
+      </c>
+      <c r="BF155">
+        <v>4.85</v>
+      </c>
+      <c r="BG155">
+        <v>1.64</v>
+      </c>
+      <c r="BH155">
+        <v>2.12</v>
+      </c>
+      <c r="BI155">
+        <v>2.08</v>
+      </c>
+      <c r="BJ155">
+        <v>1.67</v>
+      </c>
+      <c r="BK155">
+        <v>2.77</v>
+      </c>
+      <c r="BL155">
+        <v>1.36</v>
+      </c>
+      <c r="BM155">
+        <v>3.99</v>
+      </c>
+      <c r="BN155">
+        <v>1.16</v>
+      </c>
+      <c r="BO155">
+        <v>6.21</v>
+      </c>
+      <c r="BP155">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP92"/>
+  <dimension ref="A1:BP94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
@@ -1786,7 +1786,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.15</v>
@@ -2873,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR11" t="n">
         <v>1.04</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.15</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.08</v>
@@ -3966,7 +3966,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR16" t="n">
         <v>1.64</v>
@@ -4181,7 +4181,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.08</v>
@@ -4402,7 +4402,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR18" t="n">
         <v>1.29</v>
@@ -4835,7 +4835,7 @@
         <v>1.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.92</v>
@@ -5492,7 +5492,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR23" t="n">
         <v>1.7</v>
@@ -5707,7 +5707,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.92</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.31</v>
@@ -6582,7 +6582,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR28" t="n">
         <v>1.05</v>
@@ -7018,7 +7018,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR30" t="n">
         <v>1.13</v>
@@ -7236,7 +7236,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR31" t="n">
         <v>1.56</v>
@@ -7672,7 +7672,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR33" t="n">
         <v>1.57</v>
@@ -8105,7 +8105,7 @@
         <v>2.25</v>
       </c>
       <c r="AP35" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.69</v>
@@ -8541,7 +8541,7 @@
         <v>0.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.31</v>
@@ -8759,7 +8759,7 @@
         <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ38" t="n">
         <v>2.62</v>
@@ -8977,10 +8977,10 @@
         <v>1.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR39" t="n">
         <v>1.38</v>
@@ -10285,10 +10285,10 @@
         <v>1.83</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR45" t="n">
         <v>1.34</v>
@@ -11157,10 +11157,10 @@
         <v>2.17</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR49" t="n">
         <v>1.4</v>
@@ -11593,7 +11593,7 @@
         <v>0.57</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.92</v>
@@ -12032,7 +12032,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR53" t="n">
         <v>1.7</v>
@@ -12468,7 +12468,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR55" t="n">
         <v>1.18</v>
@@ -12686,7 +12686,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR56" t="n">
         <v>1.46</v>
@@ -13119,7 +13119,7 @@
         <v>1.38</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.08</v>
@@ -14212,7 +14212,7 @@
         <v>1</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR63" t="n">
         <v>1.43</v>
@@ -14427,10 +14427,10 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR64" t="n">
         <v>1.41</v>
@@ -14648,7 +14648,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR65" t="n">
         <v>1.05</v>
@@ -14866,7 +14866,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR66" t="n">
         <v>1.5</v>
@@ -15735,7 +15735,7 @@
         <v>1.22</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.15</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.31</v>
@@ -16174,7 +16174,7 @@
         <v>1</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR72" t="n">
         <v>1.44</v>
@@ -16825,7 +16825,7 @@
         <v>0.7</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.6899999999999999</v>
@@ -17043,7 +17043,7 @@
         <v>1.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.38</v>
@@ -17264,7 +17264,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR77" t="n">
         <v>1.32</v>
@@ -17918,7 +17918,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR80" t="n">
         <v>1.46</v>
@@ -18351,7 +18351,7 @@
         <v>1.91</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.92</v>
@@ -18787,7 +18787,7 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.92</v>
@@ -19008,7 +19008,7 @@
         <v>1</v>
       </c>
       <c r="AQ85" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR85" t="n">
         <v>1.45</v>
@@ -19223,10 +19223,10 @@
         <v>2</v>
       </c>
       <c r="AP86" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ86" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AR86" t="n">
         <v>1.26</v>
@@ -19662,7 +19662,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR88" t="n">
         <v>1.13</v>
@@ -20316,7 +20316,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR91" t="n">
         <v>1.49</v>
@@ -20609,6 +20609,442 @@
         <v>0</v>
       </c>
       <c r="BP92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>7813913</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>45808.1875</v>
+      </c>
+      <c r="F93" t="n">
+        <v>14</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Busan I'Park</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" t="n">
+        <v>4</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>['43', '65', '71', '76']</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S93" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U93" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V93" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W93" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X93" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI93" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>7813912</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>45808.1875</v>
+      </c>
+      <c r="F94" t="n">
+        <v>14</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Jeonnam Dragons</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Hwaseong</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3</v>
+      </c>
+      <c r="L94" t="n">
+        <v>3</v>
+      </c>
+      <c r="M94" t="n">
+        <v>2</v>
+      </c>
+      <c r="N94" t="n">
+        <v>5</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>['5', '35', '78']</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>['10', '71']</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R94" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S94" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U94" t="n">
+        <v>3</v>
+      </c>
+      <c r="V94" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W94" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X94" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP94" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>3</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR9" t="n">
         <v>2.58</v>
@@ -2655,10 +2655,10 @@
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR10" t="n">
         <v>0.82</v>
@@ -2873,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR11" t="n">
         <v>1.04</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR12" t="n">
         <v>0.8</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AR13" t="n">
         <v>1.4</v>
@@ -3527,10 +3527,10 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR14" t="n">
         <v>1.15</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
         <v>0.82</v>
@@ -3963,10 +3963,10 @@
         <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR16" t="n">
         <v>1.64</v>
@@ -4181,10 +4181,10 @@
         <v>1.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AR17" t="n">
         <v>1.16</v>
@@ -4399,10 +4399,10 @@
         <v>2</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR18" t="n">
         <v>1.29</v>
@@ -4617,10 +4617,10 @@
         <v>0.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
         <v>1.43</v>
@@ -4835,10 +4835,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR20" t="n">
         <v>1.06</v>
@@ -5053,10 +5053,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR21" t="n">
         <v>1.02</v>
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AR22" t="n">
         <v>0.92</v>
@@ -5489,10 +5489,10 @@
         <v>2.33</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR23" t="n">
         <v>1.7</v>
@@ -5707,10 +5707,10 @@
         <v>1.33</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
         <v>1.21</v>
@@ -5925,10 +5925,10 @@
         <v>2.33</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR25" t="n">
         <v>1.64</v>
@@ -6143,10 +6143,10 @@
         <v>0.33</v>
       </c>
       <c r="AP26" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR26" t="n">
         <v>1.69</v>
@@ -6361,10 +6361,10 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR27" t="n">
         <v>1.27</v>
@@ -6579,10 +6579,10 @@
         <v>2.33</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR28" t="n">
         <v>1.05</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR29" t="n">
         <v>1.37</v>
@@ -7015,10 +7015,10 @@
         <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR30" t="n">
         <v>1.13</v>
@@ -7233,10 +7233,10 @@
         <v>2</v>
       </c>
       <c r="AP31" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR31" t="n">
         <v>1.56</v>
@@ -7451,10 +7451,10 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
         <v>1.04</v>
@@ -7669,10 +7669,10 @@
         <v>1.75</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR33" t="n">
         <v>1.57</v>
@@ -7887,10 +7887,10 @@
         <v>1.25</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR34" t="n">
         <v>0.87</v>
@@ -8105,10 +8105,10 @@
         <v>2.25</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR35" t="n">
         <v>0.9</v>
@@ -8323,10 +8323,10 @@
         <v>2</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR36" t="n">
         <v>1.34</v>
@@ -8541,10 +8541,10 @@
         <v>0.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR37" t="n">
         <v>0.98</v>
@@ -8759,10 +8759,10 @@
         <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AR38" t="n">
         <v>1.37</v>
@@ -8977,10 +8977,10 @@
         <v>1.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR39" t="n">
         <v>1.38</v>
@@ -9195,10 +9195,10 @@
         <v>1.6</v>
       </c>
       <c r="AP40" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AR40" t="n">
         <v>1.66</v>
@@ -9413,10 +9413,10 @@
         <v>1.8</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR41" t="n">
         <v>1.48</v>
@@ -9631,10 +9631,10 @@
         <v>0.8</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR42" t="n">
         <v>1.44</v>
@@ -9849,10 +9849,10 @@
         <v>0.2</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR43" t="n">
         <v>0.96</v>
@@ -10067,10 +10067,10 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR44" t="n">
         <v>1.44</v>
@@ -10285,10 +10285,10 @@
         <v>1.83</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR45" t="n">
         <v>1.34</v>
@@ -10503,10 +10503,10 @@
         <v>1.67</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR46" t="n">
         <v>1.42</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR47" t="n">
         <v>1.33</v>
@@ -10939,10 +10939,10 @@
         <v>0.67</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR48" t="n">
         <v>1.54</v>
@@ -11157,10 +11157,10 @@
         <v>2.17</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR49" t="n">
         <v>1.4</v>
@@ -11375,10 +11375,10 @@
         <v>0.17</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR50" t="n">
         <v>0.9399999999999999</v>
@@ -11593,10 +11593,10 @@
         <v>0.57</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR51" t="n">
         <v>1.19</v>
@@ -11811,10 +11811,10 @@
         <v>0.43</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR52" t="n">
         <v>1.57</v>
@@ -12029,10 +12029,10 @@
         <v>0.86</v>
       </c>
       <c r="AP53" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR53" t="n">
         <v>1.7</v>
@@ -12247,10 +12247,10 @@
         <v>1.86</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR54" t="n">
         <v>1.02</v>
@@ -12465,10 +12465,10 @@
         <v>1.29</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR55" t="n">
         <v>1.18</v>
@@ -12683,10 +12683,10 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR56" t="n">
         <v>1.46</v>
@@ -12901,10 +12901,10 @@
         <v>1.29</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR57" t="n">
         <v>1.41</v>
@@ -13119,10 +13119,10 @@
         <v>1.38</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AR58" t="n">
         <v>1.28</v>
@@ -13337,10 +13337,10 @@
         <v>0.88</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR59" t="n">
         <v>1.07</v>
@@ -13555,10 +13555,10 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR60" t="n">
         <v>1.58</v>
@@ -13773,10 +13773,10 @@
         <v>2.38</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AR61" t="n">
         <v>1.46</v>
@@ -13991,10 +13991,10 @@
         <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR62" t="n">
         <v>1.72</v>
@@ -14209,10 +14209,10 @@
         <v>1.88</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR63" t="n">
         <v>1.43</v>
@@ -14427,10 +14427,10 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR64" t="n">
         <v>1.41</v>
@@ -14645,10 +14645,10 @@
         <v>1.89</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR65" t="n">
         <v>1.05</v>
@@ -14863,10 +14863,10 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR66" t="n">
         <v>1.5</v>
@@ -15081,10 +15081,10 @@
         <v>1.22</v>
       </c>
       <c r="AP67" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AQ67" t="n">
         <v>0.91</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>0.82</v>
       </c>
       <c r="AR67" t="n">
         <v>1.27</v>
@@ -15299,10 +15299,10 @@
         <v>1.89</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR68" t="n">
         <v>1.25</v>
@@ -15517,10 +15517,10 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR69" t="n">
         <v>1.49</v>
@@ -15735,10 +15735,10 @@
         <v>1.22</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR70" t="n">
         <v>1.5</v>
@@ -15953,10 +15953,10 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR71" t="n">
         <v>1.36</v>
@@ -16171,10 +16171,10 @@
         <v>0.9</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR72" t="n">
         <v>1.44</v>
@@ -16389,10 +16389,10 @@
         <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR73" t="n">
         <v>1.4</v>
@@ -16607,10 +16607,10 @@
         <v>2.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AR74" t="n">
         <v>1.57</v>
@@ -16825,10 +16825,10 @@
         <v>0.7</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR75" t="n">
         <v>1.34</v>
@@ -17043,10 +17043,10 @@
         <v>1.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR76" t="n">
         <v>1.29</v>
@@ -17261,10 +17261,10 @@
         <v>1.8</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR77" t="n">
         <v>1.32</v>
@@ -17479,10 +17479,10 @@
         <v>0.3</v>
       </c>
       <c r="AP78" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR78" t="n">
         <v>1.74</v>
@@ -17697,10 +17697,10 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR79" t="n">
         <v>1.41</v>
@@ -17915,10 +17915,10 @@
         <v>0.82</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR80" t="n">
         <v>1.46</v>
@@ -18133,10 +18133,10 @@
         <v>1.45</v>
       </c>
       <c r="AP81" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR81" t="n">
         <v>1.16</v>
@@ -18351,10 +18351,10 @@
         <v>1.91</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ82" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR82" t="n">
         <v>1.47</v>
@@ -18569,10 +18569,10 @@
         <v>2.55</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AR83" t="n">
         <v>1.25</v>
@@ -18787,10 +18787,10 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR84" t="n">
         <v>1.26</v>
@@ -19005,10 +19005,10 @@
         <v>1.91</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR85" t="n">
         <v>1.45</v>
@@ -19223,10 +19223,10 @@
         <v>2</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR86" t="n">
         <v>1.26</v>
@@ -19441,10 +19441,10 @@
         <v>0.67</v>
       </c>
       <c r="AP87" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR87" t="n">
         <v>1.32</v>
@@ -19659,10 +19659,10 @@
         <v>1.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR88" t="n">
         <v>1.13</v>
@@ -19877,10 +19877,10 @@
         <v>0.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR89" t="n">
         <v>1.48</v>
@@ -20095,10 +20095,10 @@
         <v>1.75</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR90" t="n">
         <v>1.58</v>
@@ -20313,10 +20313,10 @@
         <v>2.08</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR91" t="n">
         <v>1.49</v>
@@ -20531,10 +20531,10 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR92" t="n">
         <v>1.79</v>
@@ -20749,10 +20749,10 @@
         <v>1.69</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR93" t="n">
         <v>1.28</v>
@@ -20967,10 +20967,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR94" t="n">
         <v>1.27</v>
@@ -21185,10 +21185,10 @@
         <v>1.08</v>
       </c>
       <c r="AP95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ95" t="n">
         <v>0.91</v>
-      </c>
-      <c r="AQ95" t="n">
-        <v>0.82</v>
       </c>
       <c r="AR95" t="n">
         <v>1.31</v>
@@ -21403,10 +21403,10 @@
         <v>1.38</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR96" t="n">
         <v>1.23</v>
@@ -21621,10 +21621,10 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR97" t="n">
         <v>1.59</v>
@@ -21839,10 +21839,10 @@
         <v>1.69</v>
       </c>
       <c r="AP98" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR98" t="n">
         <v>1.78</v>
@@ -22057,10 +22057,10 @@
         <v>2.62</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AR99" t="n">
         <v>1.23</v>
@@ -22275,10 +22275,10 @@
         <v>2</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ100" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR100" t="n">
         <v>1.13</v>
@@ -22493,10 +22493,10 @@
         <v>1.29</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR101" t="n">
         <v>1.31</v>
@@ -22711,10 +22711,10 @@
         <v>0.64</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR102" t="n">
         <v>1.5</v>
@@ -22929,10 +22929,10 @@
         <v>0.86</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR103" t="n">
         <v>1.45</v>
@@ -23147,10 +23147,10 @@
         <v>1.93</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR104" t="n">
         <v>1.27</v>
@@ -23365,10 +23365,10 @@
         <v>1.57</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR105" t="n">
         <v>1.57</v>
@@ -23583,10 +23583,10 @@
         <v>0.36</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR106" t="n">
         <v>1.44</v>
@@ -23801,10 +23801,10 @@
         <v>0.33</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR107" t="n">
         <v>1.57</v>
@@ -24019,10 +24019,10 @@
         <v>1.87</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR108" t="n">
         <v>1.45</v>
@@ -24237,10 +24237,10 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR109" t="n">
         <v>1.29</v>
@@ -24455,10 +24455,10 @@
         <v>1.67</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR110" t="n">
         <v>1.26</v>
@@ -24673,10 +24673,10 @@
         <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR111" t="n">
         <v>1.29</v>
@@ -24891,10 +24891,10 @@
         <v>1.13</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AR112" t="n">
         <v>1.45</v>
@@ -25109,10 +25109,10 @@
         <v>2.53</v>
       </c>
       <c r="AP113" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ113" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AR113" t="n">
         <v>1.78</v>
@@ -25327,10 +25327,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR114" t="n">
         <v>1.51</v>
@@ -25545,10 +25545,10 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR115" t="n">
         <v>1.17</v>
@@ -25763,10 +25763,10 @@
         <v>1.56</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR116" t="n">
         <v>1.16</v>
@@ -25981,10 +25981,10 @@
         <v>1.31</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR117" t="n">
         <v>1.18</v>
@@ -26199,10 +26199,10 @@
         <v>0.75</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR118" t="n">
         <v>1.48</v>
@@ -26417,10 +26417,10 @@
         <v>1.94</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ119" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR119" t="n">
         <v>1.42</v>
@@ -26635,10 +26635,10 @@
         <v>1.19</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR120" t="n">
         <v>1.33</v>
@@ -26853,10 +26853,10 @@
         <v>1.65</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR121" t="n">
         <v>1.58</v>
@@ -27071,10 +27071,10 @@
         <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AR122" t="n">
         <v>1.46</v>
@@ -27289,10 +27289,10 @@
         <v>0.65</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR123" t="n">
         <v>1.12</v>
@@ -27507,10 +27507,10 @@
         <v>1.24</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR124" t="n">
         <v>1.21</v>
@@ -27725,10 +27725,10 @@
         <v>1.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR125" t="n">
         <v>1.76</v>
@@ -27943,10 +27943,10 @@
         <v>1.76</v>
       </c>
       <c r="AP126" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR126" t="n">
         <v>1.3</v>
@@ -28161,10 +28161,10 @@
         <v>2.59</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AR127" t="n">
         <v>1.46</v>
@@ -28379,10 +28379,10 @@
         <v>1.94</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ128" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR128" t="n">
         <v>1.55</v>
@@ -28597,10 +28597,10 @@
         <v>2.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AR129" t="n">
         <v>1.32</v>
@@ -28815,10 +28815,10 @@
         <v>1.61</v>
       </c>
       <c r="AP130" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR130" t="n">
         <v>1.32</v>
@@ -29033,10 +29033,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP131" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR131" t="n">
         <v>1.39</v>
@@ -29251,10 +29251,10 @@
         <v>1.72</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR132" t="n">
         <v>1.19</v>
@@ -29469,10 +29469,10 @@
         <v>1.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR133" t="n">
         <v>1.45</v>
@@ -29687,10 +29687,10 @@
         <v>0.67</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR134" t="n">
         <v>1.19</v>
@@ -29905,10 +29905,10 @@
         <v>0.89</v>
       </c>
       <c r="AP135" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AR135" t="n">
         <v>1.78</v>
@@ -30123,10 +30123,10 @@
         <v>0.84</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR136" t="n">
         <v>1.14</v>
@@ -30341,10 +30341,10 @@
         <v>0.95</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AR137" t="n">
         <v>1.3</v>
@@ -30559,10 +30559,10 @@
         <v>1.16</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR138" t="n">
         <v>1.45</v>
@@ -30777,10 +30777,10 @@
         <v>1.32</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR139" t="n">
         <v>1.47</v>
@@ -30995,10 +30995,10 @@
         <v>1.26</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR140" t="n">
         <v>1.51</v>
@@ -31213,10 +31213,10 @@
         <v>1.53</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR141" t="n">
         <v>1.09</v>
@@ -31431,10 +31431,10 @@
         <v>2.05</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AQ142" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR142" t="n">
         <v>1.32</v>
@@ -31649,10 +31649,10 @@
         <v>0.95</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR143" t="n">
         <v>1.44</v>
@@ -31867,10 +31867,10 @@
         <v>1.15</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AR144" t="n">
         <v>1.36</v>
@@ -32085,10 +32085,10 @@
         <v>1.55</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR145" t="n">
         <v>1.17</v>
@@ -32303,10 +32303,10 @@
         <v>1.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR146" t="n">
         <v>1.48</v>
@@ -32521,10 +32521,10 @@
         <v>0.65</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AR147" t="n">
         <v>1.32</v>
@@ -32739,10 +32739,10 @@
         <v>2.4</v>
       </c>
       <c r="AP148" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AQ148" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AR148" t="n">
         <v>1.37</v>
@@ -32957,10 +32957,10 @@
         <v>1.81</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR149" t="n">
         <v>1.45</v>
@@ -33175,10 +33175,10 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AR150" t="n">
         <v>1.18</v>
@@ -33393,10 +33393,10 @@
         <v>1.24</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR151" t="n">
         <v>1.31</v>
@@ -33611,10 +33611,10 @@
         <v>1.05</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AR152" t="n">
         <v>1.56</v>
@@ -33829,10 +33829,10 @@
         <v>1.76</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR153" t="n">
         <v>1.14</v>
@@ -34047,10 +34047,10 @@
         <v>1.43</v>
       </c>
       <c r="AP154" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR154" t="n">
         <v>1.72</v>
@@ -34265,10 +34265,10 @@
         <v>0.95</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AR155" t="n">
         <v>1.45</v>
@@ -34344,6 +34344,1532 @@
       </c>
       <c r="BP155" t="n">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>7813975</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>45871.29166666666</v>
+      </c>
+      <c r="F156" t="n">
+        <v>23</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Seongnam</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>2</v>
+      </c>
+      <c r="K156" t="n">
+        <v>2</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" t="n">
+        <v>3</v>
+      </c>
+      <c r="N156" t="n">
+        <v>5</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>['73', '90+6']</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>['2', '42', '86']</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R156" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S156" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U156" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V156" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W156" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X156" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>7813976</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>45871.29166666666</v>
+      </c>
+      <c r="F157" t="n">
+        <v>23</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S157" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U157" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V157" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X157" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>7813977</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>45871.29166666666</v>
+      </c>
+      <c r="F158" t="n">
+        <v>23</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Jeonnam Dragons</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Asan Mugunghwa</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>2</v>
+      </c>
+      <c r="M158" t="n">
+        <v>2</v>
+      </c>
+      <c r="N158" t="n">
+        <v>4</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>['84', '90+5']</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>['79', '86']</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R158" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S158" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U158" t="n">
+        <v>3</v>
+      </c>
+      <c r="V158" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W158" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X158" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>7813978</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>45871.29166666666</v>
+      </c>
+      <c r="F159" t="n">
+        <v>23</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Hwaseong</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1</v>
+      </c>
+      <c r="K159" t="n">
+        <v>1</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>4</v>
+      </c>
+      <c r="R159" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S159" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V159" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X159" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>7813979</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>45871.29166666666</v>
+      </c>
+      <c r="F160" t="n">
+        <v>23</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Cheongju</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1</v>
+      </c>
+      <c r="K160" t="n">
+        <v>2</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>2</v>
+      </c>
+      <c r="N160" t="n">
+        <v>3</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>['30', '86']</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V160" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X160" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>7813980</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>45871.29166666666</v>
+      </c>
+      <c r="F161" t="n">
+        <v>23</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Gyeongnam</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Busan I'Park</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S161" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V161" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X161" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>7813981</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>45871.29166666666</v>
+      </c>
+      <c r="F162" t="n">
+        <v>23</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Suwon Bluewings</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>2</v>
+      </c>
+      <c r="K162" t="n">
+        <v>2</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>2</v>
+      </c>
+      <c r="N162" t="n">
+        <v>3</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>['3', '38']</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S162" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U162" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V162" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X162" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
         <v>9</v>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
         <v>6</v>
@@ -1156,10 +1156,10 @@
         <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
         <v>1</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW4" t="n">
         <v>4</v>
@@ -1374,10 +1374,10 @@
         <v>5</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA4" t="n">
         <v>7</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
@@ -1592,10 +1592,10 @@
         <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW6" t="n">
         <v>3</v>
@@ -1810,10 +1810,10 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA6" t="n">
         <v>2</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW7" t="n">
         <v>2</v>
@@ -2028,10 +2028,10 @@
         <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA7" t="n">
         <v>6</v>
@@ -2234,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW8" t="n">
         <v>4</v>
@@ -2246,10 +2246,10 @@
         <v>5</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -2443,19 +2443,19 @@
         <v>2.04</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.28</v>
+        <v>5.02</v>
       </c>
       <c r="AU9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV9" t="n">
         <v>3</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4</v>
       </c>
       <c r="AW9" t="n">
         <v>8</v>
@@ -2464,10 +2464,10 @@
         <v>3</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA9" t="n">
         <v>5</v>
@@ -2661,19 +2661,19 @@
         <v>1.39</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
         <v>8</v>
@@ -2682,10 +2682,10 @@
         <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
         <v>2</v>
@@ -2879,19 +2879,19 @@
         <v>1.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="AU11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW11" t="n">
         <v>4</v>
@@ -2900,10 +2900,10 @@
         <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA11" t="n">
         <v>2</v>
@@ -3097,19 +3097,19 @@
         <v>1.17</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW12" t="n">
         <v>5</v>
@@ -3118,10 +3118,10 @@
         <v>7</v>
       </c>
       <c r="AY12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>12</v>
       </c>
       <c r="BA12" t="n">
         <v>6</v>
@@ -3315,19 +3315,19 @@
         <v>0.91</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AU13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW13" t="n">
         <v>6</v>
@@ -3336,10 +3336,10 @@
         <v>7</v>
       </c>
       <c r="AY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>11</v>
       </c>
       <c r="BA13" t="n">
         <v>10</v>
@@ -3533,19 +3533,19 @@
         <v>1.65</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.76</v>
+        <v>2.49</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
@@ -3554,10 +3554,10 @@
         <v>5</v>
       </c>
       <c r="AY14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>4</v>
@@ -3751,19 +3751,19 @@
         <v>1</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="AU15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW15" t="n">
         <v>3</v>
@@ -3772,10 +3772,10 @@
         <v>4</v>
       </c>
       <c r="AY15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
         <v>3</v>
@@ -3969,19 +3969,19 @@
         <v>1.48</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.06</v>
+        <v>2.79</v>
       </c>
       <c r="AU16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
         <v>3</v>
@@ -3990,10 +3990,10 @@
         <v>4</v>
       </c>
       <c r="AY16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
         <v>5</v>
@@ -4187,19 +4187,19 @@
         <v>0.91</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AU17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW17" t="n">
         <v>6</v>
@@ -4208,10 +4208,10 @@
         <v>8</v>
       </c>
       <c r="AY17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>11</v>
       </c>
       <c r="BA17" t="n">
         <v>4</v>
@@ -4405,19 +4405,19 @@
         <v>1.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="AU18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW18" t="n">
         <v>8</v>
@@ -4426,10 +4426,10 @@
         <v>1</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA18" t="n">
         <v>1</v>
@@ -4623,19 +4623,19 @@
         <v>1</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AU19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
         <v>6</v>
@@ -4644,10 +4644,10 @@
         <v>2</v>
       </c>
       <c r="AY19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA19" t="n">
         <v>5</v>
@@ -4841,19 +4841,19 @@
         <v>2.04</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="AU20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
         <v>1</v>
@@ -4862,10 +4862,10 @@
         <v>5</v>
       </c>
       <c r="AY20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA20" t="n">
         <v>4</v>
@@ -5059,19 +5059,19 @@
         <v>1.17</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="AU21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW21" t="n">
         <v>1</v>
@@ -5080,10 +5080,10 @@
         <v>7</v>
       </c>
       <c r="AY21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
         <v>3</v>
@@ -5277,19 +5277,19 @@
         <v>2.39</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AU22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW22" t="n">
         <v>3</v>
@@ -5298,10 +5298,10 @@
         <v>3</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA22" t="n">
         <v>3</v>
@@ -5495,16 +5495,16 @@
         <v>1.48</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AU23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
@@ -5513,13 +5513,13 @@
         <v>9</v>
       </c>
       <c r="AX23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA23" t="n">
         <v>6</v>
@@ -5713,19 +5713,19 @@
         <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AU24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW24" t="n">
         <v>6</v>
@@ -5734,10 +5734,10 @@
         <v>9</v>
       </c>
       <c r="AY24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>15</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>16</v>
       </c>
       <c r="BA24" t="n">
         <v>9</v>
@@ -5931,19 +5931,19 @@
         <v>1.3</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW25" t="n">
         <v>5</v>
@@ -5952,10 +5952,10 @@
         <v>3</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA25" t="n">
         <v>5</v>
@@ -6149,19 +6149,19 @@
         <v>1.17</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AU26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW26" t="n">
         <v>4</v>
@@ -6170,10 +6170,10 @@
         <v>5</v>
       </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>7</v>
@@ -6367,19 +6367,19 @@
         <v>0.7</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AU27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW27" t="n">
         <v>7</v>
@@ -6388,10 +6388,10 @@
         <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA27" t="n">
         <v>6</v>
@@ -6585,19 +6585,19 @@
         <v>1.7</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AU28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW28" t="n">
         <v>4</v>
@@ -6606,10 +6606,10 @@
         <v>3</v>
       </c>
       <c r="AY28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>8</v>
       </c>
       <c r="BA28" t="n">
         <v>3</v>
@@ -6803,19 +6803,19 @@
         <v>0.87</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
         <v>8</v>
@@ -6824,10 +6824,10 @@
         <v>3</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA29" t="n">
         <v>8</v>
@@ -7021,19 +7021,19 @@
         <v>1</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="AU30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -7042,10 +7042,10 @@
         <v>3</v>
       </c>
       <c r="AY30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA30" t="n">
         <v>6</v>
@@ -7239,19 +7239,19 @@
         <v>1.7</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.82</v>
+        <v>2.54</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW31" t="n">
         <v>9</v>
@@ -7260,10 +7260,10 @@
         <v>7</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
         <v>4</v>
@@ -7457,19 +7457,19 @@
         <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AU32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW32" t="n">
         <v>13</v>
@@ -7478,10 +7478,10 @@
         <v>4</v>
       </c>
       <c r="AY32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA32" t="n">
         <v>5</v>
@@ -7675,19 +7675,19 @@
         <v>1.48</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="AU33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW33" t="n">
         <v>10</v>
@@ -7696,10 +7696,10 @@
         <v>6</v>
       </c>
       <c r="AY33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA33" t="n">
         <v>3</v>
@@ -7893,19 +7893,19 @@
         <v>1.39</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AU34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV34" t="n">
         <v>3</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>4</v>
       </c>
       <c r="AW34" t="n">
         <v>4</v>
@@ -7914,10 +7914,10 @@
         <v>8</v>
       </c>
       <c r="AY34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA34" t="n">
         <v>4</v>
@@ -8111,19 +8111,19 @@
         <v>1.65</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="AU35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW35" t="n">
         <v>4</v>
@@ -8132,10 +8132,10 @@
         <v>1</v>
       </c>
       <c r="AY35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA35" t="n">
         <v>2</v>
@@ -8329,19 +8329,19 @@
         <v>1.3</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AU36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW36" t="n">
         <v>4</v>
@@ -8350,10 +8350,10 @@
         <v>3</v>
       </c>
       <c r="AY36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA36" t="n">
         <v>11</v>
@@ -8547,19 +8547,19 @@
         <v>0.7</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AU37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW37" t="n">
         <v>5</v>
@@ -8568,10 +8568,10 @@
         <v>8</v>
       </c>
       <c r="AY37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA37" t="n">
         <v>4</v>
@@ -8765,19 +8765,19 @@
         <v>2.39</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AU38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW38" t="n">
         <v>4</v>
@@ -8786,10 +8786,10 @@
         <v>4</v>
       </c>
       <c r="AY38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA38" t="n">
         <v>4</v>
@@ -8983,19 +8983,19 @@
         <v>1.7</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW39" t="n">
         <v>6</v>
@@ -9004,10 +9004,10 @@
         <v>7</v>
       </c>
       <c r="AY39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA39" t="n">
         <v>7</v>
@@ -9201,19 +9201,19 @@
         <v>0.91</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.98</v>
+        <v>2.73</v>
       </c>
       <c r="AU40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW40" t="n">
         <v>8</v>
@@ -9222,10 +9222,10 @@
         <v>8</v>
       </c>
       <c r="AY40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA40" t="n">
         <v>6</v>
@@ -9419,19 +9419,19 @@
         <v>1.65</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW41" t="n">
         <v>3</v>
@@ -9440,10 +9440,10 @@
         <v>7</v>
       </c>
       <c r="AY41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ41" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA41" t="n">
         <v>2</v>
@@ -9637,19 +9637,19 @@
         <v>1</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AU42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW42" t="n">
         <v>5</v>
@@ -9658,10 +9658,10 @@
         <v>6</v>
       </c>
       <c r="AY42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA42" t="n">
         <v>2</v>
@@ -9855,19 +9855,19 @@
         <v>0.87</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AU43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW43" t="n">
         <v>5</v>
@@ -9876,10 +9876,10 @@
         <v>4</v>
       </c>
       <c r="AY43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA43" t="n">
         <v>2</v>
@@ -10073,19 +10073,19 @@
         <v>1.17</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AU44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW44" t="n">
         <v>9</v>
@@ -10094,10 +10094,10 @@
         <v>7</v>
       </c>
       <c r="AY44" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA44" t="n">
         <v>3</v>
@@ -10291,19 +10291,19 @@
         <v>1.7</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AU45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW45" t="n">
         <v>4</v>
@@ -10312,10 +10312,10 @@
         <v>4</v>
       </c>
       <c r="AY45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA45" t="n">
         <v>5</v>
@@ -10509,19 +10509,19 @@
         <v>2.04</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AU46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW46" t="n">
         <v>6</v>
@@ -10530,10 +10530,10 @@
         <v>9</v>
       </c>
       <c r="AY46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA46" t="n">
         <v>4</v>
@@ -10727,19 +10727,19 @@
         <v>1.3</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AU47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW47" t="n">
         <v>11</v>
@@ -10748,10 +10748,10 @@
         <v>4</v>
       </c>
       <c r="AY47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA47" t="n">
         <v>7</v>
@@ -10945,19 +10945,19 @@
         <v>1</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW48" t="n">
         <v>9</v>
@@ -10966,10 +10966,10 @@
         <v>7</v>
       </c>
       <c r="AY48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA48" t="n">
         <v>9</v>
@@ -11163,19 +11163,19 @@
         <v>1.48</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.07</v>
+        <v>0.95</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.47</v>
+        <v>2.22</v>
       </c>
       <c r="AU49" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV49" t="n">
         <v>9</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>10</v>
       </c>
       <c r="AW49" t="n">
         <v>4</v>
@@ -11184,10 +11184,10 @@
         <v>5</v>
       </c>
       <c r="AY49" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA49" t="n">
         <v>3</v>
@@ -11381,19 +11381,19 @@
         <v>0.87</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AU50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW50" t="n">
         <v>6</v>
@@ -11402,10 +11402,10 @@
         <v>6</v>
       </c>
       <c r="AY50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA50" t="n">
         <v>4</v>
@@ -11599,19 +11599,19 @@
         <v>1</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="AU51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW51" t="n">
         <v>14</v>
@@ -11620,10 +11620,10 @@
         <v>3</v>
       </c>
       <c r="AY51" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA51" t="n">
         <v>5</v>
@@ -11817,19 +11817,19 @@
         <v>0.7</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="AU52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW52" t="n">
         <v>4</v>
@@ -11838,10 +11838,10 @@
         <v>9</v>
       </c>
       <c r="AY52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA52" t="n">
         <v>4</v>
@@ -12035,19 +12035,19 @@
         <v>1</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="AU53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW53" t="n">
         <v>9</v>
@@ -12056,10 +12056,10 @@
         <v>4</v>
       </c>
       <c r="AY53" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA53" t="n">
         <v>5</v>
@@ -12253,19 +12253,19 @@
         <v>1.65</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.46</v>
+        <v>2.19</v>
       </c>
       <c r="AU54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW54" t="n">
         <v>4</v>
@@ -12274,10 +12274,10 @@
         <v>5</v>
       </c>
       <c r="AY54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA54" t="n">
         <v>8</v>
@@ -12471,19 +12471,19 @@
         <v>1.48</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="AU55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW55" t="n">
         <v>9</v>
@@ -12492,10 +12492,10 @@
         <v>4</v>
       </c>
       <c r="AY55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA55" t="n">
         <v>0</v>
@@ -12689,19 +12689,19 @@
         <v>1.7</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AU56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW56" t="n">
         <v>12</v>
@@ -12710,10 +12710,10 @@
         <v>6</v>
       </c>
       <c r="AY56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA56" t="n">
         <v>13</v>
@@ -12907,19 +12907,19 @@
         <v>1.39</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="AU57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW57" t="n">
         <v>3</v>
@@ -12928,10 +12928,10 @@
         <v>4</v>
       </c>
       <c r="AY57" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA57" t="n">
         <v>3</v>
@@ -13125,19 +13125,19 @@
         <v>0.91</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AT58" t="n">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
       <c r="AU58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW58" t="n">
         <v>6</v>
@@ -13146,10 +13146,10 @@
         <v>3</v>
       </c>
       <c r="AY58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA58" t="n">
         <v>4</v>
@@ -13343,19 +13343,19 @@
         <v>1</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AU59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW59" t="n">
         <v>11</v>
@@ -13364,10 +13364,10 @@
         <v>4</v>
       </c>
       <c r="AY59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA59" t="n">
         <v>8</v>
@@ -13561,19 +13561,19 @@
         <v>0.87</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT60" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="AU60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW60" t="n">
         <v>7</v>
@@ -13582,10 +13582,10 @@
         <v>12</v>
       </c>
       <c r="AY60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA60" t="n">
         <v>4</v>
@@ -13779,19 +13779,19 @@
         <v>2.39</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AT61" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="AU61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW61" t="n">
         <v>9</v>
@@ -13800,10 +13800,10 @@
         <v>3</v>
       </c>
       <c r="AY61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA61" t="n">
         <v>8</v>
@@ -13997,19 +13997,19 @@
         <v>1.3</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW62" t="n">
         <v>3</v>
@@ -14018,10 +14018,10 @@
         <v>2</v>
       </c>
       <c r="AY62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA62" t="n">
         <v>8</v>
@@ -14215,19 +14215,19 @@
         <v>1.7</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.71</v>
+        <v>2.44</v>
       </c>
       <c r="AU63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW63" t="n">
         <v>11</v>
@@ -14236,10 +14236,10 @@
         <v>3</v>
       </c>
       <c r="AY63" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA63" t="n">
         <v>6</v>
@@ -14433,19 +14433,19 @@
         <v>1</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT64" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU64" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW64" t="n">
         <v>3</v>
@@ -14454,10 +14454,10 @@
         <v>2</v>
       </c>
       <c r="AY64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA64" t="n">
         <v>2</v>
@@ -14651,19 +14651,19 @@
         <v>1.48</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AT65" t="n">
-        <v>2.34</v>
+        <v>2.09</v>
       </c>
       <c r="AU65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV65" t="n">
         <v>3</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>4</v>
       </c>
       <c r="AW65" t="n">
         <v>2</v>
@@ -14672,10 +14672,10 @@
         <v>9</v>
       </c>
       <c r="AY65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ65" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA65" t="n">
         <v>6</v>
@@ -14869,19 +14869,19 @@
         <v>1.7</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT66" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AU66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW66" t="n">
         <v>6</v>
@@ -14890,10 +14890,10 @@
         <v>12</v>
       </c>
       <c r="AY66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ66" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA66" t="n">
         <v>0</v>
@@ -15087,19 +15087,19 @@
         <v>0.91</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AT67" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AU67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW67" t="n">
         <v>7</v>
@@ -15108,10 +15108,10 @@
         <v>7</v>
       </c>
       <c r="AY67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ67" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA67" t="n">
         <v>2</v>
@@ -15305,19 +15305,19 @@
         <v>2.04</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="AU68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW68" t="n">
         <v>8</v>
@@ -15326,10 +15326,10 @@
         <v>7</v>
       </c>
       <c r="AY68" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ68" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA68" t="n">
         <v>4</v>
@@ -15523,16 +15523,16 @@
         <v>1.39</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AT69" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AU69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV69" t="n">
         <v>0</v>
@@ -15541,13 +15541,13 @@
         <v>10</v>
       </c>
       <c r="AX69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY69" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA69" t="n">
         <v>3</v>
@@ -15741,19 +15741,19 @@
         <v>1.17</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="AU70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW70" t="n">
         <v>4</v>
@@ -15762,10 +15762,10 @@
         <v>6</v>
       </c>
       <c r="AY70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA70" t="n">
         <v>0</v>
@@ -15959,19 +15959,19 @@
         <v>0.7</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT71" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="AU71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW71" t="n">
         <v>5</v>
@@ -15980,10 +15980,10 @@
         <v>6</v>
       </c>
       <c r="AY71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA71" t="n">
         <v>5</v>
@@ -16177,16 +16177,16 @@
         <v>1</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT72" t="n">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="AU72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV72" t="n">
         <v>0</v>
@@ -16195,13 +16195,13 @@
         <v>10</v>
       </c>
       <c r="AX72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA72" t="n">
         <v>8</v>
@@ -16395,19 +16395,19 @@
         <v>1.65</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT73" t="n">
-        <v>2.86</v>
+        <v>2.61</v>
       </c>
       <c r="AU73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV73" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW73" t="n">
         <v>7</v>
@@ -16416,10 +16416,10 @@
         <v>4</v>
       </c>
       <c r="AY73" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA73" t="n">
         <v>3</v>
@@ -16613,19 +16613,19 @@
         <v>2.39</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AT74" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AU74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV74" t="n">
         <v>3</v>
-      </c>
-      <c r="AV74" t="n">
-        <v>4</v>
       </c>
       <c r="AW74" t="n">
         <v>3</v>
@@ -16634,10 +16634,10 @@
         <v>2</v>
       </c>
       <c r="AY74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA74" t="n">
         <v>2</v>
@@ -16831,19 +16831,19 @@
         <v>0.87</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT75" t="n">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="AU75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW75" t="n">
         <v>7</v>
@@ -16852,10 +16852,10 @@
         <v>6</v>
       </c>
       <c r="AY75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA75" t="n">
         <v>5</v>
@@ -17049,19 +17049,19 @@
         <v>1.3</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="AT76" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AU76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW76" t="n">
         <v>1</v>
@@ -17070,10 +17070,10 @@
         <v>5</v>
       </c>
       <c r="AY76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA76" t="n">
         <v>3</v>
@@ -17267,19 +17267,19 @@
         <v>1.48</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
       <c r="AU77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW77" t="n">
         <v>4</v>
@@ -17288,10 +17288,10 @@
         <v>7</v>
       </c>
       <c r="AY77" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ77" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA77" t="n">
         <v>2</v>
@@ -17485,19 +17485,19 @@
         <v>0.7</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT78" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="AU78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW78" t="n">
         <v>12</v>
@@ -17506,10 +17506,10 @@
         <v>8</v>
       </c>
       <c r="AY78" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ78" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA78" t="n">
         <v>4</v>
@@ -17703,19 +17703,19 @@
         <v>1.17</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AU79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV79" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW79" t="n">
         <v>15</v>
@@ -17724,10 +17724,10 @@
         <v>1</v>
       </c>
       <c r="AY79" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ79" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA79" t="n">
         <v>11</v>
@@ -17921,16 +17921,16 @@
         <v>1</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AT80" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AU80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV80" t="n">
         <v>0</v>
@@ -17939,13 +17939,13 @@
         <v>10</v>
       </c>
       <c r="AX80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY80" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA80" t="n">
         <v>9</v>
@@ -18139,19 +18139,19 @@
         <v>1.3</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="AU81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW81" t="n">
         <v>6</v>
@@ -18160,10 +18160,10 @@
         <v>10</v>
       </c>
       <c r="AY81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ81" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA81" t="n">
         <v>5</v>
@@ -18357,19 +18357,19 @@
         <v>2.04</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AT82" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AU82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW82" t="n">
         <v>2</v>
@@ -18378,10 +18378,10 @@
         <v>2</v>
       </c>
       <c r="AY82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ82" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA82" t="n">
         <v>6</v>
@@ -18575,31 +18575,31 @@
         <v>2.39</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AU83" t="n">
         <v>0</v>
       </c>
       <c r="AV83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX83" t="n">
         <v>6</v>
       </c>
       <c r="AY83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA83" t="n">
         <v>6</v>
@@ -18793,19 +18793,19 @@
         <v>1</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AT84" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="AU84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW84" t="n">
         <v>7</v>
@@ -18814,10 +18814,10 @@
         <v>6</v>
       </c>
       <c r="AY84" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ84" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA84" t="n">
         <v>3</v>
@@ -19011,19 +19011,19 @@
         <v>1.48</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="AU85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW85" t="n">
         <v>3</v>
@@ -19032,10 +19032,10 @@
         <v>4</v>
       </c>
       <c r="AY85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA85" t="n">
         <v>6</v>
@@ -19229,19 +19229,19 @@
         <v>1.48</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="AU86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW86" t="n">
         <v>11</v>
@@ -19250,10 +19250,10 @@
         <v>3</v>
       </c>
       <c r="AY86" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA86" t="n">
         <v>8</v>
@@ -19447,19 +19447,19 @@
         <v>0.87</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT87" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="AU87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW87" t="n">
         <v>5</v>
@@ -19468,10 +19468,10 @@
         <v>7</v>
       </c>
       <c r="AY87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA87" t="n">
         <v>5</v>
@@ -19665,16 +19665,16 @@
         <v>1.48</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AT88" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="AU88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV88" t="n">
         <v>0</v>
@@ -19683,13 +19683,13 @@
         <v>6</v>
       </c>
       <c r="AX88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA88" t="n">
         <v>5</v>
@@ -19883,19 +19883,19 @@
         <v>0.7</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT89" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="AU89" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV89" t="n">
         <v>7</v>
-      </c>
-      <c r="AV89" t="n">
-        <v>8</v>
       </c>
       <c r="AW89" t="n">
         <v>10</v>
@@ -19904,10 +19904,10 @@
         <v>9</v>
       </c>
       <c r="AY89" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ89" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA89" t="n">
         <v>5</v>
@@ -20101,19 +20101,19 @@
         <v>1.65</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AU90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW90" t="n">
         <v>12</v>
@@ -20122,10 +20122,10 @@
         <v>8</v>
       </c>
       <c r="AY90" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ90" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA90" t="n">
         <v>4</v>
@@ -20319,19 +20319,19 @@
         <v>1.7</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT91" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="AU91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW91" t="n">
         <v>16</v>
@@ -20340,10 +20340,10 @@
         <v>2</v>
       </c>
       <c r="AY91" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA91" t="n">
         <v>5</v>
@@ -20537,19 +20537,19 @@
         <v>1.39</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT92" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="AU92" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV92" t="n">
         <v>6</v>
-      </c>
-      <c r="AV92" t="n">
-        <v>7</v>
       </c>
       <c r="AW92" t="n">
         <v>6</v>
@@ -20558,10 +20558,10 @@
         <v>5</v>
       </c>
       <c r="AY92" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ92" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA92" t="n">
         <v>9</v>
@@ -20755,31 +20755,31 @@
         <v>1.48</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="AU93" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV93" t="n">
         <v>5</v>
       </c>
-      <c r="AV93" t="n">
+      <c r="AW93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY93" t="n">
         <v>6</v>
       </c>
-      <c r="AW93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY93" t="n">
+      <c r="AZ93" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ93" t="n">
-        <v>8</v>
       </c>
       <c r="BA93" t="n">
         <v>1</v>
@@ -20973,19 +20973,19 @@
         <v>1</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.58</v>
+        <v>2.33</v>
       </c>
       <c r="AU94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW94" t="n">
         <v>5</v>
@@ -20994,10 +20994,10 @@
         <v>5</v>
       </c>
       <c r="AY94" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA94" t="n">
         <v>4</v>
@@ -21191,31 +21191,31 @@
         <v>0.91</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="AU95" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW95" t="n">
         <v>5</v>
       </c>
-      <c r="AV95" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW95" t="n">
-        <v>3</v>
-      </c>
       <c r="AX95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY95" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ95" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ95" t="n">
-        <v>5</v>
       </c>
       <c r="BA95" t="n">
         <v>0</v>
@@ -21409,28 +21409,28 @@
         <v>1.3</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT96" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AU96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW96" t="n">
         <v>5</v>
       </c>
       <c r="AX96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ96" t="n">
         <v>11</v>
@@ -21627,28 +21627,28 @@
         <v>1.39</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.03</v>
+        <v>2.78</v>
       </c>
       <c r="AU97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW97" t="n">
         <v>5</v>
       </c>
       <c r="AX97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ97" t="n">
         <v>9</v>
@@ -21845,31 +21845,31 @@
         <v>1.65</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="AU98" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW98" t="n">
         <v>8</v>
       </c>
-      <c r="AV98" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW98" t="n">
-        <v>6</v>
-      </c>
       <c r="AX98" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AY98" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ98" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BA98" t="n">
         <v>3</v>
@@ -22063,19 +22063,19 @@
         <v>2.39</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AU99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW99" t="n">
         <v>2</v>
@@ -22084,10 +22084,10 @@
         <v>4</v>
       </c>
       <c r="AY99" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ99" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ99" t="n">
-        <v>9</v>
       </c>
       <c r="BA99" t="n">
         <v>4</v>
@@ -22281,31 +22281,31 @@
         <v>2.04</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="AU100" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX100" t="n">
         <v>5</v>
-      </c>
-      <c r="AV100" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW100" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX100" t="n">
-        <v>6</v>
       </c>
       <c r="AY100" t="n">
         <v>10</v>
       </c>
       <c r="AZ100" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA100" t="n">
         <v>4</v>
@@ -22499,31 +22499,31 @@
         <v>1.17</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU101" t="n">
         <v>0</v>
       </c>
       <c r="AV101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW101" t="n">
         <v>7</v>
       </c>
       <c r="AX101" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY101" t="n">
         <v>7</v>
       </c>
       <c r="AZ101" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA101" t="n">
         <v>6</v>
@@ -22717,31 +22717,31 @@
         <v>1</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AU102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX102" t="n">
         <v>2</v>
       </c>
       <c r="AY102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA102" t="n">
         <v>4</v>
@@ -22935,19 +22935,19 @@
         <v>0.87</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW103" t="n">
         <v>9</v>
@@ -22956,10 +22956,10 @@
         <v>0</v>
       </c>
       <c r="AY103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA103" t="n">
         <v>9</v>
@@ -23153,19 +23153,19 @@
         <v>1.48</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AU104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW104" t="n">
         <v>3</v>
@@ -23174,10 +23174,10 @@
         <v>4</v>
       </c>
       <c r="AY104" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ104" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ104" t="n">
-        <v>8</v>
       </c>
       <c r="BA104" t="n">
         <v>4</v>
@@ -23371,16 +23371,16 @@
         <v>1.65</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT105" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV105" t="n">
         <v>0</v>
@@ -23389,13 +23389,13 @@
         <v>6</v>
       </c>
       <c r="AX105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY105" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA105" t="n">
         <v>3</v>
@@ -23589,31 +23589,31 @@
         <v>0.7</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="AU106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW106" t="n">
         <v>11</v>
       </c>
       <c r="AX106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY106" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ106" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA106" t="n">
         <v>11</v>
@@ -23807,28 +23807,28 @@
         <v>0.7</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="AU107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW107" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY107" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ107" t="n">
         <v>8</v>
@@ -24025,31 +24025,31 @@
         <v>1.48</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AU108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW108" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX108" t="n">
         <v>8</v>
       </c>
       <c r="AY108" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA108" t="n">
         <v>5</v>
@@ -24243,28 +24243,28 @@
         <v>1.3</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="AU109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW109" t="n">
         <v>6</v>
       </c>
       <c r="AX109" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ109" t="n">
         <v>13</v>
@@ -24461,19 +24461,19 @@
         <v>1.48</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW110" t="n">
         <v>10</v>
@@ -24482,10 +24482,10 @@
         <v>10</v>
       </c>
       <c r="AY110" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ110" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA110" t="n">
         <v>6</v>
@@ -24679,25 +24679,25 @@
         <v>0.87</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="AU111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY111" t="n">
         <v>2</v>
@@ -24897,31 +24897,31 @@
         <v>0.91</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="AU112" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW112" t="n">
         <v>10</v>
       </c>
-      <c r="AV112" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW112" t="n">
+      <c r="AX112" t="n">
         <v>6</v>
       </c>
-      <c r="AX112" t="n">
-        <v>3</v>
-      </c>
       <c r="AY112" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AZ112" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA112" t="n">
         <v>9</v>
@@ -25115,19 +25115,19 @@
         <v>2.39</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AT113" t="n">
-        <v>3.34</v>
+        <v>3.07</v>
       </c>
       <c r="AU113" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW113" t="n">
         <v>5</v>
@@ -25136,10 +25136,10 @@
         <v>2</v>
       </c>
       <c r="AY113" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA113" t="n">
         <v>4</v>
@@ -25333,16 +25333,16 @@
         <v>1</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AU114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV114" t="n">
         <v>0</v>
@@ -25351,13 +25351,13 @@
         <v>5</v>
       </c>
       <c r="AX114" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ114" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA114" t="n">
         <v>2</v>
@@ -25551,25 +25551,25 @@
         <v>1.48</v>
       </c>
       <c r="AR115" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AS115" t="n">
         <v>1.17</v>
       </c>
-      <c r="AS115" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AT115" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="AU115" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV115" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX115" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY115" t="n">
         <v>12</v>
@@ -25769,31 +25769,31 @@
         <v>1.65</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.66</v>
+        <v>2.39</v>
       </c>
       <c r="AU116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW116" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AX116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY116" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AZ116" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA116" t="n">
         <v>3</v>
@@ -25987,31 +25987,31 @@
         <v>1.17</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="AU117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV117" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW117" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX117" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY117" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ117" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA117" t="n">
         <v>7</v>
@@ -26205,19 +26205,19 @@
         <v>1</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="AU118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV118" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW118" t="n">
         <v>3</v>
@@ -26226,10 +26226,10 @@
         <v>2</v>
       </c>
       <c r="AY118" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA118" t="n">
         <v>6</v>
@@ -26423,31 +26423,31 @@
         <v>2.04</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AU119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV119" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW119" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX119" t="n">
         <v>6</v>
       </c>
       <c r="AY119" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ119" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA119" t="n">
         <v>7</v>
@@ -26641,16 +26641,16 @@
         <v>1.39</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AU120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV120" t="n">
         <v>0</v>
@@ -26659,13 +26659,13 @@
         <v>4</v>
       </c>
       <c r="AX120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY120" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA120" t="n">
         <v>1</v>
@@ -26859,31 +26859,31 @@
         <v>1.48</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.93</v>
+        <v>2.71</v>
       </c>
       <c r="AU121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX121" t="n">
         <v>7</v>
       </c>
       <c r="AY121" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA121" t="n">
         <v>1</v>
@@ -27077,31 +27077,31 @@
         <v>0.91</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AU122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV122" t="n">
         <v>0</v>
       </c>
       <c r="AW122" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX122" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY122" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ122" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA122" t="n">
         <v>6</v>
@@ -27295,31 +27295,31 @@
         <v>0.7</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AU123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW123" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AX123" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY123" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AZ123" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA123" t="n">
         <v>1</v>
@@ -27513,19 +27513,19 @@
         <v>1.3</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AT124" t="n">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="AU124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW124" t="n">
         <v>4</v>
@@ -27534,10 +27534,10 @@
         <v>4</v>
       </c>
       <c r="AY124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ124" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA124" t="n">
         <v>3</v>
@@ -27731,31 +27731,31 @@
         <v>1.48</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT125" t="n">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="AU125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW125" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX125" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AY125" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ125" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BA125" t="n">
         <v>3</v>
@@ -27949,31 +27949,31 @@
         <v>1.7</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT126" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AU126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX126" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY126" t="n">
         <v>12</v>
       </c>
       <c r="AZ126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA126" t="n">
         <v>5</v>
@@ -28167,31 +28167,31 @@
         <v>2.39</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.96</v>
+        <v>2.71</v>
       </c>
       <c r="AU127" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX127" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY127" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ127" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA127" t="n">
         <v>0</v>
@@ -28385,31 +28385,31 @@
         <v>2.04</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.29</v>
+        <v>3.07</v>
       </c>
       <c r="AU128" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV128" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW128" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AX128" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AY128" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ128" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BA128" t="n">
         <v>7</v>
@@ -28603,31 +28603,31 @@
         <v>2.39</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
       <c r="AU129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX129" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY129" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ129" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA129" t="n">
         <v>2</v>
@@ -28821,19 +28821,19 @@
         <v>1.48</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="AU130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW130" t="n">
         <v>7</v>
@@ -28842,10 +28842,10 @@
         <v>8</v>
       </c>
       <c r="AY130" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ130" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA130" t="n">
         <v>1</v>
@@ -29039,31 +29039,31 @@
         <v>0.87</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="AU131" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ131" t="n">
         <v>6</v>
-      </c>
-      <c r="AV131" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW131" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY131" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ131" t="n">
-        <v>7</v>
       </c>
       <c r="BA131" t="n">
         <v>2</v>
@@ -29257,31 +29257,31 @@
         <v>1.65</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.72</v>
+        <v>2.47</v>
       </c>
       <c r="AU132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX132" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY132" t="n">
         <v>8</v>
       </c>
-      <c r="AY132" t="n">
-        <v>7</v>
-      </c>
       <c r="AZ132" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA132" t="n">
         <v>5</v>
@@ -29475,28 +29475,28 @@
         <v>1.48</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="AU133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV133" t="n">
         <v>0</v>
       </c>
       <c r="AW133" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX133" t="n">
         <v>6</v>
       </c>
       <c r="AY133" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ133" t="n">
         <v>6</v>
@@ -29693,31 +29693,31 @@
         <v>0.7</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="AU134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV134" t="n">
         <v>0</v>
       </c>
       <c r="AW134" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AX134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY134" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AZ134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA134" t="n">
         <v>6</v>
@@ -29911,16 +29911,16 @@
         <v>1</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AT135" t="n">
-        <v>3.13</v>
+        <v>2.86</v>
       </c>
       <c r="AU135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV135" t="n">
         <v>0</v>
@@ -29929,13 +29929,13 @@
         <v>4</v>
       </c>
       <c r="AX135" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY135" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ135" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ135" t="n">
-        <v>8</v>
       </c>
       <c r="BA135" t="n">
         <v>8</v>
@@ -30129,22 +30129,22 @@
         <v>1</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AU136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX136" t="n">
         <v>3</v>
@@ -30153,7 +30153,7 @@
         <v>15</v>
       </c>
       <c r="AZ136" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA136" t="n">
         <v>5</v>
@@ -30347,19 +30347,19 @@
         <v>0.91</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="AU137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW137" t="n">
         <v>7</v>
@@ -30368,10 +30368,10 @@
         <v>2</v>
       </c>
       <c r="AY137" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA137" t="n">
         <v>6</v>
@@ -30565,22 +30565,22 @@
         <v>1.3</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AU138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV138" t="n">
         <v>3</v>
       </c>
-      <c r="AV138" t="n">
-        <v>4</v>
-      </c>
       <c r="AW138" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX138" t="n">
         <v>3</v>
@@ -30589,7 +30589,7 @@
         <v>11</v>
       </c>
       <c r="AZ138" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA138" t="n">
         <v>6</v>
@@ -30783,31 +30783,31 @@
         <v>1.17</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AT139" t="n">
-        <v>3.06</v>
+        <v>2.82</v>
       </c>
       <c r="AU139" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW139" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX139" t="n">
         <v>4</v>
       </c>
       <c r="AY139" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA139" t="n">
         <v>4</v>
@@ -31001,31 +31001,31 @@
         <v>1.39</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT140" t="n">
-        <v>2.98</v>
+        <v>2.73</v>
       </c>
       <c r="AU140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX140" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY140" t="n">
         <v>6</v>
       </c>
       <c r="AZ140" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA140" t="n">
         <v>6</v>
@@ -31219,25 +31219,25 @@
         <v>1.48</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.43</v>
+        <v>2.24</v>
       </c>
       <c r="AU141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY141" t="n">
         <v>5</v>
@@ -31437,31 +31437,31 @@
         <v>2.04</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.06</v>
+        <v>2.79</v>
       </c>
       <c r="AU142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW142" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY142" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AZ142" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA142" t="n">
         <v>11</v>
@@ -31655,28 +31655,28 @@
         <v>0.87</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="AU143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX143" t="n">
         <v>6</v>
       </c>
-      <c r="AV143" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW143" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX143" t="n">
-        <v>5</v>
-      </c>
       <c r="AY143" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ143" t="n">
         <v>10</v>
@@ -31873,31 +31873,31 @@
         <v>1.3</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="AU144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW144" t="n">
         <v>7</v>
       </c>
       <c r="AX144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY144" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ144" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA144" t="n">
         <v>4</v>
@@ -32091,19 +32091,19 @@
         <v>1.48</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AU145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV145" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW145" t="n">
         <v>6</v>
@@ -32112,10 +32112,10 @@
         <v>7</v>
       </c>
       <c r="AY145" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ145" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA145" t="n">
         <v>3</v>
@@ -32309,31 +32309,31 @@
         <v>1.17</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AT146" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="AU146" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV146" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW146" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX146" t="n">
         <v>8</v>
       </c>
       <c r="AY146" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ146" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA146" t="n">
         <v>3</v>
@@ -32527,31 +32527,31 @@
         <v>0.7</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="AU147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW147" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX147" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY147" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ147" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA147" t="n">
         <v>5</v>
@@ -32745,31 +32745,31 @@
         <v>2.39</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AU148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW148" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX148" t="n">
         <v>6</v>
       </c>
-      <c r="AX148" t="n">
-        <v>2</v>
-      </c>
       <c r="AY148" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ148" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ148" t="n">
-        <v>5</v>
       </c>
       <c r="BA148" t="n">
         <v>2</v>
@@ -32963,31 +32963,31 @@
         <v>1.65</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="AU149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV149" t="n">
         <v>9</v>
-      </c>
-      <c r="AV149" t="n">
-        <v>10</v>
       </c>
       <c r="AW149" t="n">
         <v>5</v>
       </c>
       <c r="AX149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY149" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ149" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA149" t="n">
         <v>2</v>
@@ -33181,31 +33181,31 @@
         <v>0.91</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="AU150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW150" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX150" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY150" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ150" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA150" t="n">
         <v>8</v>
@@ -33399,31 +33399,31 @@
         <v>1.39</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AU151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW151" t="n">
         <v>6</v>
       </c>
-      <c r="AV151" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW151" t="n">
-        <v>5</v>
-      </c>
       <c r="AX151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY151" t="n">
         <v>11</v>
       </c>
       <c r="AZ151" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA151" t="n">
         <v>4</v>
@@ -33617,28 +33617,28 @@
         <v>1</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="AU152" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX152" t="n">
         <v>3</v>
       </c>
-      <c r="AW152" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX152" t="n">
-        <v>2</v>
-      </c>
       <c r="AY152" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ152" t="n">
         <v>5</v>
@@ -33835,31 +33835,31 @@
         <v>1.7</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="AU153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX153" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY153" t="n">
         <v>10</v>
       </c>
       <c r="AZ153" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA153" t="n">
         <v>8</v>
@@ -34053,31 +34053,31 @@
         <v>1.48</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AT154" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW154" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX154" t="n">
         <v>2</v>
       </c>
       <c r="AY154" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ154" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA154" t="n">
         <v>8</v>
@@ -34271,31 +34271,31 @@
         <v>0.87</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AU155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW155" t="n">
         <v>6</v>
       </c>
-      <c r="AV155" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW155" t="n">
-        <v>7</v>
-      </c>
       <c r="AX155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY155" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ155" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA155" t="n">
         <v>2</v>
@@ -34489,28 +34489,28 @@
         <v>1.3</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AT156" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="AU156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV156" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW156" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY156" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ156" t="n">
         <v>12</v>
@@ -34707,31 +34707,31 @@
         <v>2.39</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="AU157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV157" t="n">
         <v>0</v>
       </c>
       <c r="AW157" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY157" t="n">
         <v>9</v>
       </c>
-      <c r="AX157" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY157" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA157" t="n">
         <v>6</v>
@@ -34925,31 +34925,31 @@
         <v>1.17</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="AU158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW158" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX158" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY158" t="n">
         <v>7</v>
       </c>
       <c r="AZ158" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA158" t="n">
         <v>4</v>
@@ -35143,25 +35143,25 @@
         <v>1.39</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="AU159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX159" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY159" t="n">
         <v>6</v>
@@ -35361,19 +35361,19 @@
         <v>1</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="AU160" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV160" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW160" t="n">
         <v>5</v>
@@ -35382,10 +35382,10 @@
         <v>3</v>
       </c>
       <c r="AY160" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ160" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA160" t="n">
         <v>6</v>
@@ -35579,31 +35579,31 @@
         <v>1.48</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="AU161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW161" t="n">
         <v>0</v>
       </c>
       <c r="AX161" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AY161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ161" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BA161" t="n">
         <v>1</v>
@@ -35797,31 +35797,31 @@
         <v>2.04</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AT162" t="n">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="AU162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW162" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AX162" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AY162" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AZ162" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA162" t="n">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
@@ -2437,10 +2437,10 @@
         <v>3</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR9" t="n">
         <v>2.45</v>
@@ -2655,10 +2655,10 @@
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR10" t="n">
         <v>0.6899999999999999</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR13" t="n">
         <v>1.27</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ15" t="n">
         <v>1</v>
@@ -3966,7 +3966,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR16" t="n">
         <v>1.51</v>
@@ -4184,7 +4184,7 @@
         <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR17" t="n">
         <v>1.03</v>
@@ -4399,7 +4399,7 @@
         <v>2</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.7</v>
@@ -4617,7 +4617,7 @@
         <v>0.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ19" t="n">
         <v>1</v>
@@ -4838,7 +4838,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR20" t="n">
         <v>0.93</v>
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR22" t="n">
         <v>0.79</v>
@@ -5489,7 +5489,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.48</v>
@@ -5925,10 +5925,10 @@
         <v>2.33</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR25" t="n">
         <v>1.51</v>
@@ -6143,7 +6143,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.17</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.7</v>
@@ -6579,7 +6579,7 @@
         <v>2.33</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.7</v>
@@ -6800,7 +6800,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR29" t="n">
         <v>1.24</v>
@@ -7015,7 +7015,7 @@
         <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
@@ -7233,7 +7233,7 @@
         <v>2</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.7</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ32" t="n">
         <v>1</v>
@@ -7669,10 +7669,10 @@
         <v>1.75</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR33" t="n">
         <v>1.44</v>
@@ -7890,7 +7890,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR34" t="n">
         <v>0.73</v>
@@ -8326,7 +8326,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR36" t="n">
         <v>1.2</v>
@@ -8762,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR38" t="n">
         <v>1.24</v>
@@ -8977,7 +8977,7 @@
         <v>1.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.7</v>
@@ -9195,10 +9195,10 @@
         <v>1.6</v>
       </c>
       <c r="AP40" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR40" t="n">
         <v>1.53</v>
@@ -9413,7 +9413,7 @@
         <v>1.8</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.65</v>
@@ -9849,10 +9849,10 @@
         <v>0.2</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR43" t="n">
         <v>0.82</v>
@@ -10067,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.17</v>
@@ -10506,7 +10506,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR46" t="n">
         <v>1.29</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR47" t="n">
         <v>1.21</v>
@@ -10939,7 +10939,7 @@
         <v>0.67</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ48" t="n">
         <v>1</v>
@@ -11157,7 +11157,7 @@
         <v>2.17</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.48</v>
@@ -11378,7 +11378,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR50" t="n">
         <v>0.8100000000000001</v>
@@ -11811,7 +11811,7 @@
         <v>0.43</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.7</v>
@@ -12029,7 +12029,7 @@
         <v>0.86</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ53" t="n">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>1.86</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.65</v>
@@ -12465,10 +12465,10 @@
         <v>1.29</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR55" t="n">
         <v>1.05</v>
@@ -12901,10 +12901,10 @@
         <v>1.29</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR57" t="n">
         <v>1.29</v>
@@ -13122,7 +13122,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR58" t="n">
         <v>1.16</v>
@@ -13558,7 +13558,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR60" t="n">
         <v>1.45</v>
@@ -13776,7 +13776,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR61" t="n">
         <v>1.32</v>
@@ -13991,10 +13991,10 @@
         <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR62" t="n">
         <v>1.59</v>
@@ -14209,7 +14209,7 @@
         <v>1.88</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.7</v>
@@ -14427,7 +14427,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ64" t="n">
         <v>1</v>
@@ -14645,7 +14645,7 @@
         <v>1.89</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.48</v>
@@ -15081,10 +15081,10 @@
         <v>1.22</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR67" t="n">
         <v>1.14</v>
@@ -15302,7 +15302,7 @@
         <v>1</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR68" t="n">
         <v>1.12</v>
@@ -15517,10 +15517,10 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR69" t="n">
         <v>1.36</v>
@@ -15735,7 +15735,7 @@
         <v>1.22</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.17</v>
@@ -16171,7 +16171,7 @@
         <v>0.9</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ72" t="n">
         <v>1</v>
@@ -16389,7 +16389,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.65</v>
@@ -16610,7 +16610,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR74" t="n">
         <v>1.43</v>
@@ -16828,7 +16828,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR75" t="n">
         <v>1.21</v>
@@ -17046,7 +17046,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR76" t="n">
         <v>1.15</v>
@@ -17264,7 +17264,7 @@
         <v>1</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR77" t="n">
         <v>1.18</v>
@@ -17479,7 +17479,7 @@
         <v>0.3</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.7</v>
@@ -17697,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.17</v>
@@ -18136,7 +18136,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR81" t="n">
         <v>1.03</v>
@@ -18351,10 +18351,10 @@
         <v>1.91</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ82" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR82" t="n">
         <v>1.34</v>
@@ -18569,10 +18569,10 @@
         <v>2.55</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR83" t="n">
         <v>1.12</v>
@@ -19005,7 +19005,7 @@
         <v>1.91</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.48</v>
@@ -19444,7 +19444,7 @@
         <v>1</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR87" t="n">
         <v>1.18</v>
@@ -19659,10 +19659,10 @@
         <v>1.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR88" t="n">
         <v>0.99</v>
@@ -19877,7 +19877,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.7</v>
@@ -20313,7 +20313,7 @@
         <v>2.08</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.7</v>
@@ -20531,10 +20531,10 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR92" t="n">
         <v>1.65</v>
@@ -20752,7 +20752,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR93" t="n">
         <v>1.16</v>
@@ -21188,7 +21188,7 @@
         <v>1</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR95" t="n">
         <v>1.18</v>
@@ -21403,10 +21403,10 @@
         <v>1.38</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR96" t="n">
         <v>1.1</v>
@@ -21624,7 +21624,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR97" t="n">
         <v>1.46</v>
@@ -21839,7 +21839,7 @@
         <v>1.69</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.65</v>
@@ -22060,7 +22060,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR99" t="n">
         <v>1.09</v>
@@ -22275,10 +22275,10 @@
         <v>2</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ100" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR100" t="n">
         <v>1</v>
@@ -22711,7 +22711,7 @@
         <v>0.64</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ102" t="n">
         <v>1</v>
@@ -22929,10 +22929,10 @@
         <v>0.86</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR103" t="n">
         <v>1.32</v>
@@ -23365,7 +23365,7 @@
         <v>1.57</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.65</v>
@@ -23583,7 +23583,7 @@
         <v>0.36</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.7</v>
@@ -24240,7 +24240,7 @@
         <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR109" t="n">
         <v>1.17</v>
@@ -24458,7 +24458,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR110" t="n">
         <v>1.13</v>
@@ -24676,7 +24676,7 @@
         <v>1</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR111" t="n">
         <v>1.17</v>
@@ -24891,10 +24891,10 @@
         <v>1.13</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR112" t="n">
         <v>1.32</v>
@@ -25109,10 +25109,10 @@
         <v>2.53</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ113" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR113" t="n">
         <v>1.64</v>
@@ -25327,7 +25327,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ114" t="n">
         <v>1</v>
@@ -25763,7 +25763,7 @@
         <v>1.56</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.65</v>
@@ -25981,7 +25981,7 @@
         <v>1.31</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.17</v>
@@ -26199,7 +26199,7 @@
         <v>0.75</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ118" t="n">
         <v>1</v>
@@ -26417,10 +26417,10 @@
         <v>1.94</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ119" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR119" t="n">
         <v>1.32</v>
@@ -26638,7 +26638,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR120" t="n">
         <v>1.2</v>
@@ -27074,7 +27074,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR122" t="n">
         <v>1.34</v>
@@ -27289,7 +27289,7 @@
         <v>0.65</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.7</v>
@@ -27510,7 +27510,7 @@
         <v>1</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR124" t="n">
         <v>1.1</v>
@@ -27725,10 +27725,10 @@
         <v>1.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR125" t="n">
         <v>1.63</v>
@@ -28161,10 +28161,10 @@
         <v>2.59</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR127" t="n">
         <v>1.35</v>
@@ -28382,7 +28382,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ128" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR128" t="n">
         <v>1.45</v>
@@ -28600,7 +28600,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR129" t="n">
         <v>1.19</v>
@@ -29033,10 +29033,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP131" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR131" t="n">
         <v>1.28</v>
@@ -29469,10 +29469,10 @@
         <v>1.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR133" t="n">
         <v>1.34</v>
@@ -29687,7 +29687,7 @@
         <v>0.67</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.7</v>
@@ -29905,7 +29905,7 @@
         <v>0.89</v>
       </c>
       <c r="AP135" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ135" t="n">
         <v>1</v>
@@ -30344,7 +30344,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR137" t="n">
         <v>1.17</v>
@@ -30559,10 +30559,10 @@
         <v>1.16</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR138" t="n">
         <v>1.36</v>
@@ -30777,7 +30777,7 @@
         <v>1.32</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.17</v>
@@ -30998,7 +30998,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR140" t="n">
         <v>1.39</v>
@@ -31213,7 +31213,7 @@
         <v>1.53</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.48</v>
@@ -31434,7 +31434,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ142" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR142" t="n">
         <v>1.19</v>
@@ -31649,10 +31649,10 @@
         <v>0.95</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR143" t="n">
         <v>1.33</v>
@@ -31870,7 +31870,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR144" t="n">
         <v>1.24</v>
@@ -32088,7 +32088,7 @@
         <v>1</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR145" t="n">
         <v>1.06</v>
@@ -32739,10 +32739,10 @@
         <v>2.4</v>
       </c>
       <c r="AP148" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ148" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR148" t="n">
         <v>1.28</v>
@@ -32957,7 +32957,7 @@
         <v>1.81</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.65</v>
@@ -33178,7 +33178,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR150" t="n">
         <v>1.1</v>
@@ -33396,7 +33396,7 @@
         <v>1</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR151" t="n">
         <v>1.2</v>
@@ -33829,7 +33829,7 @@
         <v>1.76</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.7</v>
@@ -34047,7 +34047,7 @@
         <v>1.43</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.48</v>
@@ -34265,10 +34265,10 @@
         <v>0.95</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AR155" t="n">
         <v>1.34</v>
@@ -34486,7 +34486,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AR156" t="n">
         <v>1.39</v>
@@ -34704,7 +34704,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ157" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AR157" t="n">
         <v>1.23</v>
@@ -35140,7 +35140,7 @@
         <v>1</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR159" t="n">
         <v>1.02</v>
@@ -35355,7 +35355,7 @@
         <v>0.91</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ160" t="n">
         <v>1</v>
@@ -35573,10 +35573,10 @@
         <v>1.55</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR161" t="n">
         <v>1.25</v>
@@ -35794,7 +35794,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ162" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AR162" t="n">
         <v>1.15</v>
@@ -35870,6 +35870,878 @@
       </c>
       <c r="BP162" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>7813982</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>45878.29166666666</v>
+      </c>
+      <c r="F163" t="n">
+        <v>24</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Asan Mugunghwa</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Gyeongnam</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
+      <c r="K163" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" t="n">
+        <v>2</v>
+      </c>
+      <c r="M163" t="n">
+        <v>2</v>
+      </c>
+      <c r="N163" t="n">
+        <v>4</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>['56', '85']</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>['12', '90+8']</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S163" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U163" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X163" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>7813983</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>45878.29166666666</v>
+      </c>
+      <c r="F164" t="n">
+        <v>24</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Busan I'Park</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" t="n">
+        <v>1</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>2</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>['9', '69']</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S164" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U164" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V164" t="n">
+        <v>3</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X164" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>7813984</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>45878.29166666666</v>
+      </c>
+      <c r="F165" t="n">
+        <v>24</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Suwon Bluewings</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>1</v>
+      </c>
+      <c r="L165" t="n">
+        <v>3</v>
+      </c>
+      <c r="M165" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" t="n">
+        <v>4</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>['8', '58', '88']</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R165" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S165" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U165" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V165" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W165" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X165" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>7813985</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>45878.29166666666</v>
+      </c>
+      <c r="F166" t="n">
+        <v>24</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Seongnam</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" t="n">
+        <v>0</v>
+      </c>
+      <c r="X166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP166"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.17</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR11" t="n">
         <v>0.91</v>
@@ -3527,10 +3527,10 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -3748,7 +3748,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR15" t="n">
         <v>0.6899999999999999</v>
@@ -3963,7 +3963,7 @@
         <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.42</v>
@@ -4402,7 +4402,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR18" t="n">
         <v>1.16</v>
@@ -4620,7 +4620,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR19" t="n">
         <v>1.3</v>
@@ -4835,7 +4835,7 @@
         <v>1.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20" t="n">
         <v>2.08</v>
@@ -5053,7 +5053,7 @@
         <v>0.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.17</v>
@@ -5492,7 +5492,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR23" t="n">
         <v>1.57</v>
@@ -5710,7 +5710,7 @@
         <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR24" t="n">
         <v>1.08</v>
@@ -6364,7 +6364,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR27" t="n">
         <v>1.14</v>
@@ -6582,7 +6582,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR28" t="n">
         <v>0.9399999999999999</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.83</v>
@@ -7236,7 +7236,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR31" t="n">
         <v>1.42</v>
@@ -7454,7 +7454,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR32" t="n">
         <v>0.92</v>
@@ -7887,7 +7887,7 @@
         <v>1.25</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.38</v>
@@ -8105,10 +8105,10 @@
         <v>2.25</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR35" t="n">
         <v>0.78</v>
@@ -8541,10 +8541,10 @@
         <v>0.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR37" t="n">
         <v>0.86</v>
@@ -8980,7 +8980,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR39" t="n">
         <v>1.25</v>
@@ -9416,7 +9416,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR41" t="n">
         <v>1.35</v>
@@ -9634,7 +9634,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR42" t="n">
         <v>1.31</v>
@@ -10288,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR45" t="n">
         <v>1.2</v>
@@ -10503,7 +10503,7 @@
         <v>1.67</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ46" t="n">
         <v>2.08</v>
@@ -10942,7 +10942,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR48" t="n">
         <v>1.41</v>
@@ -11160,7 +11160,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR49" t="n">
         <v>1.27</v>
@@ -11375,7 +11375,7 @@
         <v>0.17</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.83</v>
@@ -11593,10 +11593,10 @@
         <v>0.57</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR51" t="n">
         <v>1.07</v>
@@ -11814,7 +11814,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR52" t="n">
         <v>1.44</v>
@@ -12250,7 +12250,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR54" t="n">
         <v>0.89</v>
@@ -12686,7 +12686,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -13119,7 +13119,7 @@
         <v>1.38</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.92</v>
@@ -13337,10 +13337,10 @@
         <v>0.88</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR59" t="n">
         <v>0.9399999999999999</v>
@@ -13773,7 +13773,7 @@
         <v>2.38</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.42</v>
@@ -14212,7 +14212,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR63" t="n">
         <v>1.29</v>
@@ -14648,7 +14648,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR65" t="n">
         <v>0.92</v>
@@ -14863,10 +14863,10 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR66" t="n">
         <v>1.37</v>
@@ -15299,7 +15299,7 @@
         <v>1.89</v>
       </c>
       <c r="AP68" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ68" t="n">
         <v>2.08</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR71" t="n">
         <v>1.23</v>
@@ -16392,7 +16392,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR73" t="n">
         <v>1.28</v>
@@ -16825,7 +16825,7 @@
         <v>0.7</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.83</v>
@@ -17043,7 +17043,7 @@
         <v>1.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.29</v>
@@ -17261,7 +17261,7 @@
         <v>1.8</v>
       </c>
       <c r="AP77" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.42</v>
@@ -17482,7 +17482,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR78" t="n">
         <v>1.6</v>
@@ -17915,7 +17915,7 @@
         <v>0.82</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ80" t="n">
         <v>1</v>
@@ -18133,7 +18133,7 @@
         <v>1.45</v>
       </c>
       <c r="AP81" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.29</v>
@@ -18787,10 +18787,10 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR84" t="n">
         <v>1.13</v>
@@ -19008,7 +19008,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR85" t="n">
         <v>1.32</v>
@@ -19226,7 +19226,7 @@
         <v>1</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR86" t="n">
         <v>1.13</v>
@@ -19441,7 +19441,7 @@
         <v>0.67</v>
       </c>
       <c r="AP87" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.83</v>
@@ -19880,7 +19880,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR89" t="n">
         <v>1.35</v>
@@ -20098,7 +20098,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR90" t="n">
         <v>1.44</v>
@@ -20316,7 +20316,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR91" t="n">
         <v>1.36</v>
@@ -20749,7 +20749,7 @@
         <v>1.69</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.42</v>
@@ -20967,7 +20967,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ94" t="n">
         <v>1</v>
@@ -21185,7 +21185,7 @@
         <v>1.08</v>
       </c>
       <c r="AP95" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.92</v>
@@ -21842,7 +21842,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR98" t="n">
         <v>1.65</v>
@@ -22057,7 +22057,7 @@
         <v>2.62</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ99" t="n">
         <v>2.42</v>
@@ -22493,7 +22493,7 @@
         <v>1.29</v>
       </c>
       <c r="AP101" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.17</v>
@@ -23147,10 +23147,10 @@
         <v>1.93</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR104" t="n">
         <v>1.14</v>
@@ -23368,7 +23368,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR105" t="n">
         <v>1.44</v>
@@ -23586,7 +23586,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR106" t="n">
         <v>1.32</v>
@@ -23804,7 +23804,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR107" t="n">
         <v>1.47</v>
@@ -24019,10 +24019,10 @@
         <v>1.87</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR108" t="n">
         <v>1.33</v>
@@ -24237,7 +24237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.29</v>
@@ -24455,7 +24455,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.42</v>
@@ -25545,10 +25545,10 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR115" t="n">
         <v>1.04</v>
@@ -25766,7 +25766,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR116" t="n">
         <v>1.03</v>
@@ -26202,7 +26202,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR118" t="n">
         <v>1.35</v>
@@ -26635,7 +26635,7 @@
         <v>1.19</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.38</v>
@@ -26856,7 +26856,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR121" t="n">
         <v>1.49</v>
@@ -27071,7 +27071,7 @@
         <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.92</v>
@@ -27292,7 +27292,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR123" t="n">
         <v>1.03</v>
@@ -27943,10 +27943,10 @@
         <v>1.76</v>
       </c>
       <c r="AP126" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR126" t="n">
         <v>1.17</v>
@@ -28597,7 +28597,7 @@
         <v>2.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ129" t="n">
         <v>2.42</v>
@@ -28815,10 +28815,10 @@
         <v>1.61</v>
       </c>
       <c r="AP130" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR130" t="n">
         <v>1.2</v>
@@ -29254,7 +29254,7 @@
         <v>1</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR132" t="n">
         <v>1.07</v>
@@ -29690,7 +29690,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR134" t="n">
         <v>1.08</v>
@@ -29908,7 +29908,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR135" t="n">
         <v>1.63</v>
@@ -30123,7 +30123,7 @@
         <v>0.84</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ136" t="n">
         <v>1</v>
@@ -30341,7 +30341,7 @@
         <v>0.95</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ137" t="n">
         <v>0.92</v>
@@ -30995,7 +30995,7 @@
         <v>1.26</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.38</v>
@@ -31216,7 +31216,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR141" t="n">
         <v>1.02</v>
@@ -31431,7 +31431,7 @@
         <v>2.05</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ142" t="n">
         <v>2.08</v>
@@ -31867,7 +31867,7 @@
         <v>1.15</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.29</v>
@@ -32303,7 +32303,7 @@
         <v>1.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.17</v>
@@ -32521,10 +32521,10 @@
         <v>0.65</v>
       </c>
       <c r="AP147" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AR147" t="n">
         <v>1.21</v>
@@ -32960,7 +32960,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR149" t="n">
         <v>1.36</v>
@@ -33175,7 +33175,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.92</v>
@@ -33393,7 +33393,7 @@
         <v>1.24</v>
       </c>
       <c r="AP151" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.38</v>
@@ -33832,7 +33832,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AR153" t="n">
         <v>1.05</v>
@@ -34050,7 +34050,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR154" t="n">
         <v>1.58</v>
@@ -34483,7 +34483,7 @@
         <v>1.23</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.29</v>
@@ -34701,7 +34701,7 @@
         <v>2.45</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AQ157" t="n">
         <v>2.42</v>
@@ -34919,7 +34919,7 @@
         <v>1.18</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.17</v>
@@ -35358,7 +35358,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AR160" t="n">
         <v>1.02</v>
@@ -35791,7 +35791,7 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="AQ162" t="n">
         <v>2.08</v>
@@ -36741,6 +36741,660 @@
         <v>0</v>
       </c>
       <c r="BP166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>7813986</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>45879.29166666666</v>
+      </c>
+      <c r="F167" t="n">
+        <v>24</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Hwaseong</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R167" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S167" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U167" t="n">
+        <v>3</v>
+      </c>
+      <c r="V167" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X167" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>7813987</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>45879.29166666666</v>
+      </c>
+      <c r="F168" t="n">
+        <v>24</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Jeonnam Dragons</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>3</v>
+      </c>
+      <c r="M168" t="n">
+        <v>4</v>
+      </c>
+      <c r="N168" t="n">
+        <v>7</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>['49', '51', '85']</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>['57', '65', '74', '90+9']</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R168" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S168" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U168" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V168" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W168" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X168" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>7813988</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>45879.29166666666</v>
+      </c>
+      <c r="F169" t="n">
+        <v>24</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Cheongju</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" t="n">
+        <v>0</v>
+      </c>
+      <c r="X169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP169" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>2.08</v>
@@ -2004,7 +2004,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.96</v>
@@ -2655,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.38</v>
@@ -2876,7 +2876,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR11" t="n">
         <v>0.91</v>
@@ -3094,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR12" t="n">
         <v>0.67</v>
@@ -3530,7 +3530,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -3963,7 +3963,7 @@
         <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.42</v>
@@ -4399,10 +4399,10 @@
         <v>2</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR18" t="n">
         <v>1.16</v>
@@ -5056,7 +5056,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR21" t="n">
         <v>0.89</v>
@@ -6146,7 +6146,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR26" t="n">
         <v>1.55</v>
@@ -6582,7 +6582,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR28" t="n">
         <v>0.9399999999999999</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR29" t="n">
         <v>1.24</v>
@@ -7015,7 +7015,7 @@
         <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
@@ -7236,7 +7236,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR31" t="n">
         <v>1.42</v>
@@ -8108,7 +8108,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR35" t="n">
         <v>0.78</v>
@@ -8323,7 +8323,7 @@
         <v>2</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.29</v>
@@ -8980,7 +8980,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR39" t="n">
         <v>1.25</v>
@@ -9416,7 +9416,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR41" t="n">
         <v>1.35</v>
@@ -9631,7 +9631,7 @@
         <v>0.8</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.96</v>
@@ -9852,7 +9852,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR43" t="n">
         <v>0.82</v>
@@ -10070,7 +10070,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR44" t="n">
         <v>1.31</v>
@@ -10288,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR45" t="n">
         <v>1.2</v>
@@ -10503,7 +10503,7 @@
         <v>1.67</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ46" t="n">
         <v>2.08</v>
@@ -11378,7 +11378,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR50" t="n">
         <v>0.8100000000000001</v>
@@ -12250,7 +12250,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR54" t="n">
         <v>0.89</v>
@@ -12465,7 +12465,7 @@
         <v>1.29</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.42</v>
@@ -12683,10 +12683,10 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -13555,10 +13555,10 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR60" t="n">
         <v>1.45</v>
@@ -13773,7 +13773,7 @@
         <v>2.38</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.42</v>
@@ -14212,7 +14212,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR63" t="n">
         <v>1.29</v>
@@ -14863,10 +14863,10 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR66" t="n">
         <v>1.37</v>
@@ -15081,7 +15081,7 @@
         <v>1.22</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.92</v>
@@ -15738,7 +15738,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR70" t="n">
         <v>1.36</v>
@@ -16392,7 +16392,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR73" t="n">
         <v>1.28</v>
@@ -16607,7 +16607,7 @@
         <v>2.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ74" t="n">
         <v>2.42</v>
@@ -16828,7 +16828,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR75" t="n">
         <v>1.21</v>
@@ -17043,7 +17043,7 @@
         <v>1.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.29</v>
@@ -17700,7 +17700,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR79" t="n">
         <v>1.28</v>
@@ -17915,7 +17915,7 @@
         <v>0.82</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ80" t="n">
         <v>1</v>
@@ -18569,7 +18569,7 @@
         <v>2.55</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ83" t="n">
         <v>2.42</v>
@@ -18787,7 +18787,7 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.96</v>
@@ -19444,7 +19444,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR87" t="n">
         <v>1.18</v>
@@ -20095,10 +20095,10 @@
         <v>1.75</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR90" t="n">
         <v>1.44</v>
@@ -20316,7 +20316,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR91" t="n">
         <v>1.36</v>
@@ -20967,7 +20967,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ94" t="n">
         <v>1</v>
@@ -21403,7 +21403,7 @@
         <v>1.38</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.29</v>
@@ -21621,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.38</v>
@@ -21842,7 +21842,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR98" t="n">
         <v>1.65</v>
@@ -22496,7 +22496,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR101" t="n">
         <v>1.18</v>
@@ -22932,7 +22932,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR103" t="n">
         <v>1.32</v>
@@ -23147,7 +23147,7 @@
         <v>1.93</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.46</v>
@@ -23368,7 +23368,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR105" t="n">
         <v>1.44</v>
@@ -23801,7 +23801,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.79</v>
@@ -24019,7 +24019,7 @@
         <v>1.87</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.46</v>
@@ -24455,7 +24455,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.42</v>
@@ -24676,7 +24676,7 @@
         <v>1</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR111" t="n">
         <v>1.17</v>
@@ -25763,10 +25763,10 @@
         <v>1.56</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR116" t="n">
         <v>1.03</v>
@@ -25984,7 +25984,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR117" t="n">
         <v>1.05</v>
@@ -26635,7 +26635,7 @@
         <v>1.19</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.38</v>
@@ -26853,7 +26853,7 @@
         <v>1.65</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.46</v>
@@ -27071,7 +27071,7 @@
         <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.92</v>
@@ -27289,7 +27289,7 @@
         <v>0.65</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.79</v>
@@ -27946,7 +27946,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR126" t="n">
         <v>1.17</v>
@@ -28379,7 +28379,7 @@
         <v>1.94</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ128" t="n">
         <v>2.08</v>
@@ -28597,7 +28597,7 @@
         <v>2.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ129" t="n">
         <v>2.42</v>
@@ -29036,7 +29036,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR131" t="n">
         <v>1.28</v>
@@ -29254,7 +29254,7 @@
         <v>1</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR132" t="n">
         <v>1.07</v>
@@ -30341,7 +30341,7 @@
         <v>0.95</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ137" t="n">
         <v>0.92</v>
@@ -30780,7 +30780,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR139" t="n">
         <v>1.34</v>
@@ -30995,7 +30995,7 @@
         <v>1.26</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.38</v>
@@ -31213,7 +31213,7 @@
         <v>1.53</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.46</v>
@@ -31431,7 +31431,7 @@
         <v>2.05</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ142" t="n">
         <v>2.08</v>
@@ -31652,7 +31652,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR143" t="n">
         <v>1.33</v>
@@ -32303,10 +32303,10 @@
         <v>1.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR146" t="n">
         <v>1.36</v>
@@ -32960,7 +32960,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR149" t="n">
         <v>1.36</v>
@@ -33611,7 +33611,7 @@
         <v>1.05</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ152" t="n">
         <v>1</v>
@@ -33832,7 +33832,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AR153" t="n">
         <v>1.05</v>
@@ -34268,7 +34268,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR155" t="n">
         <v>1.34</v>
@@ -34483,7 +34483,7 @@
         <v>1.23</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.29</v>
@@ -34919,10 +34919,10 @@
         <v>1.18</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR158" t="n">
         <v>1.23</v>
@@ -35355,7 +35355,7 @@
         <v>0.91</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.96</v>
@@ -36009,7 +36009,7 @@
         <v>0.91</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.92</v>
@@ -36448,7 +36448,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR165" t="n">
         <v>1.59</v>
@@ -37099,7 +37099,7 @@
         <v>0.7</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.79</v>
@@ -37320,7 +37320,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AR169" t="n">
         <v>1.21</v>
@@ -37396,6 +37396,442 @@
       </c>
       <c r="BP169" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>7813990</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>45884.29166666666</v>
+      </c>
+      <c r="F170" t="n">
+        <v>25</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Asan Mugunghwa</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>2</v>
+      </c>
+      <c r="K170" t="n">
+        <v>2</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>2</v>
+      </c>
+      <c r="N170" t="n">
+        <v>2</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>['10', '43']</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R170" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S170" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U170" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V170" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X170" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>7813989</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>45884.29166666666</v>
+      </c>
+      <c r="F171" t="n">
+        <v>25</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Jeonnam Dragons</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
+        <v>3</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>['85', '90+5']</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>3</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S171" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U171" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V171" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W171" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X171" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -37550,16 +37550,16 @@
         <v>2.49</v>
       </c>
       <c r="AU170" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX170" t="n">
         <v>4</v>
-      </c>
-      <c r="AX170" t="n">
-        <v>6</v>
       </c>
       <c r="AY170" t="n">
         <v>9</v>
@@ -37768,13 +37768,13 @@
         <v>2.65</v>
       </c>
       <c r="AU171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV171" t="n">
         <v>1</v>
       </c>
       <c r="AW171" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX171" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP171"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.92</v>
@@ -1350,7 +1350,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.24</v>
@@ -2437,10 +2437,10 @@
         <v>3</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR9" t="n">
         <v>2.45</v>
@@ -2658,7 +2658,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR10" t="n">
         <v>0.6899999999999999</v>
@@ -2873,7 +2873,7 @@
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.68</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.96</v>
@@ -4617,7 +4617,7 @@
         <v>0.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.96</v>
@@ -4835,10 +4835,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR20" t="n">
         <v>0.93</v>
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR22" t="n">
         <v>0.79</v>
@@ -5489,10 +5489,10 @@
         <v>2.33</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR23" t="n">
         <v>1.57</v>
@@ -5925,10 +5925,10 @@
         <v>2.33</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR25" t="n">
         <v>1.51</v>
@@ -6143,7 +6143,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.24</v>
@@ -7233,7 +7233,7 @@
         <v>2</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.68</v>
@@ -7669,7 +7669,7 @@
         <v>1.75</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.42</v>
@@ -7890,7 +7890,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR34" t="n">
         <v>0.73</v>
@@ -8105,7 +8105,7 @@
         <v>2.25</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.64</v>
@@ -8326,7 +8326,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR36" t="n">
         <v>1.2</v>
@@ -8541,7 +8541,7 @@
         <v>0.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.79</v>
@@ -8762,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR38" t="n">
         <v>1.24</v>
@@ -9195,7 +9195,7 @@
         <v>1.6</v>
       </c>
       <c r="AP40" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.92</v>
@@ -9413,7 +9413,7 @@
         <v>1.8</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.64</v>
@@ -9849,7 +9849,7 @@
         <v>0.2</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.8</v>
@@ -10067,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.24</v>
@@ -10506,7 +10506,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR46" t="n">
         <v>1.29</v>
@@ -10724,7 +10724,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR47" t="n">
         <v>1.21</v>
@@ -10939,7 +10939,7 @@
         <v>0.67</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.96</v>
@@ -11160,7 +11160,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR49" t="n">
         <v>1.27</v>
@@ -11593,7 +11593,7 @@
         <v>0.57</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.96</v>
@@ -11811,7 +11811,7 @@
         <v>0.43</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.79</v>
@@ -12029,7 +12029,7 @@
         <v>0.86</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ53" t="n">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>1.86</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.64</v>
@@ -12904,7 +12904,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR57" t="n">
         <v>1.29</v>
@@ -13119,7 +13119,7 @@
         <v>1.38</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.92</v>
@@ -13776,7 +13776,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR61" t="n">
         <v>1.32</v>
@@ -13991,10 +13991,10 @@
         <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR62" t="n">
         <v>1.59</v>
@@ -14209,7 +14209,7 @@
         <v>1.88</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.68</v>
@@ -14645,10 +14645,10 @@
         <v>1.89</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR65" t="n">
         <v>0.92</v>
@@ -15302,7 +15302,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR68" t="n">
         <v>1.12</v>
@@ -15517,10 +15517,10 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR69" t="n">
         <v>1.36</v>
@@ -16171,7 +16171,7 @@
         <v>0.9</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ72" t="n">
         <v>1</v>
@@ -16610,7 +16610,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR74" t="n">
         <v>1.43</v>
@@ -16825,7 +16825,7 @@
         <v>0.7</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.8</v>
@@ -17046,7 +17046,7 @@
         <v>1.68</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR76" t="n">
         <v>1.15</v>
@@ -17479,7 +17479,7 @@
         <v>0.3</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.79</v>
@@ -18136,7 +18136,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR81" t="n">
         <v>1.03</v>
@@ -18354,7 +18354,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ82" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR82" t="n">
         <v>1.34</v>
@@ -18572,7 +18572,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR83" t="n">
         <v>1.12</v>
@@ -19005,10 +19005,10 @@
         <v>1.91</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR85" t="n">
         <v>1.32</v>
@@ -19226,7 +19226,7 @@
         <v>1</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR86" t="n">
         <v>1.13</v>
@@ -19659,7 +19659,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.42</v>
@@ -20313,7 +20313,7 @@
         <v>2.08</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.68</v>
@@ -20531,10 +20531,10 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR92" t="n">
         <v>1.65</v>
@@ -20749,7 +20749,7 @@
         <v>1.69</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.42</v>
@@ -21406,7 +21406,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR96" t="n">
         <v>1.1</v>
@@ -21624,7 +21624,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR97" t="n">
         <v>1.46</v>
@@ -21839,7 +21839,7 @@
         <v>1.69</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.64</v>
@@ -22060,7 +22060,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR99" t="n">
         <v>1.09</v>
@@ -22275,10 +22275,10 @@
         <v>2</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ100" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR100" t="n">
         <v>1</v>
@@ -23150,7 +23150,7 @@
         <v>1.68</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR104" t="n">
         <v>1.14</v>
@@ -23365,7 +23365,7 @@
         <v>1.57</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.64</v>
@@ -23583,7 +23583,7 @@
         <v>0.36</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.79</v>
@@ -24022,7 +24022,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR108" t="n">
         <v>1.33</v>
@@ -24240,7 +24240,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR109" t="n">
         <v>1.17</v>
@@ -24891,7 +24891,7 @@
         <v>1.13</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.92</v>
@@ -25109,10 +25109,10 @@
         <v>2.53</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ113" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR113" t="n">
         <v>1.64</v>
@@ -25327,7 +25327,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ114" t="n">
         <v>1</v>
@@ -25548,7 +25548,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR115" t="n">
         <v>1.04</v>
@@ -25981,7 +25981,7 @@
         <v>1.31</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.24</v>
@@ -26420,7 +26420,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ119" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR119" t="n">
         <v>1.32</v>
@@ -26638,7 +26638,7 @@
         <v>1.68</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR120" t="n">
         <v>1.2</v>
@@ -26856,7 +26856,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR121" t="n">
         <v>1.49</v>
@@ -27510,7 +27510,7 @@
         <v>1</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR124" t="n">
         <v>1.1</v>
@@ -27725,7 +27725,7 @@
         <v>1.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.42</v>
@@ -28161,10 +28161,10 @@
         <v>2.59</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR127" t="n">
         <v>1.35</v>
@@ -28382,7 +28382,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ128" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR128" t="n">
         <v>1.45</v>
@@ -28600,7 +28600,7 @@
         <v>1.68</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR129" t="n">
         <v>1.19</v>
@@ -28818,7 +28818,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR130" t="n">
         <v>1.2</v>
@@ -29469,7 +29469,7 @@
         <v>1.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.42</v>
@@ -29687,7 +29687,7 @@
         <v>0.67</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.79</v>
@@ -29905,7 +29905,7 @@
         <v>0.89</v>
       </c>
       <c r="AP135" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.96</v>
@@ -30562,7 +30562,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR138" t="n">
         <v>1.36</v>
@@ -30777,7 +30777,7 @@
         <v>1.32</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.24</v>
@@ -30998,7 +30998,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR140" t="n">
         <v>1.39</v>
@@ -31216,7 +31216,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR141" t="n">
         <v>1.02</v>
@@ -31434,7 +31434,7 @@
         <v>1.68</v>
       </c>
       <c r="AQ142" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR142" t="n">
         <v>1.19</v>
@@ -31649,7 +31649,7 @@
         <v>0.95</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.8</v>
@@ -31867,10 +31867,10 @@
         <v>1.15</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR144" t="n">
         <v>1.24</v>
@@ -32742,7 +32742,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ148" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR148" t="n">
         <v>1.28</v>
@@ -33396,7 +33396,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR151" t="n">
         <v>1.2</v>
@@ -33829,7 +33829,7 @@
         <v>1.76</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.68</v>
@@ -34047,10 +34047,10 @@
         <v>1.43</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR154" t="n">
         <v>1.58</v>
@@ -34265,7 +34265,7 @@
         <v>0.95</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.8</v>
@@ -34486,7 +34486,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR156" t="n">
         <v>1.39</v>
@@ -34701,10 +34701,10 @@
         <v>2.45</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ157" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR157" t="n">
         <v>1.23</v>
@@ -35140,7 +35140,7 @@
         <v>1</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR159" t="n">
         <v>1.02</v>
@@ -35794,7 +35794,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ162" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR162" t="n">
         <v>1.15</v>
@@ -36230,7 +36230,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ164" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR164" t="n">
         <v>1.38</v>
@@ -36445,7 +36445,7 @@
         <v>0.87</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.8</v>
@@ -36663,10 +36663,10 @@
         <v>1.39</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR166" t="n">
         <v>1.09</v>
@@ -36881,7 +36881,7 @@
         <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ167" t="n">
         <v>1</v>
@@ -37832,6 +37832,878 @@
       </c>
       <c r="BP171" t="n">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>7813994</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F172" t="n">
+        <v>25</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Gyeongnam</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>1</v>
+      </c>
+      <c r="N172" t="n">
+        <v>2</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R172" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S172" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U172" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V172" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X172" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>7813993</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F173" t="n">
+        <v>25</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Cheongju</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Hwaseong</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>1</v>
+      </c>
+      <c r="N173" t="n">
+        <v>2</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R173" t="n">
+        <v>2</v>
+      </c>
+      <c r="S173" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U173" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V173" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W173" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X173" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>7813991</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F174" t="n">
+        <v>25</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Seongnam</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>2</v>
+      </c>
+      <c r="K174" t="n">
+        <v>2</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>2</v>
+      </c>
+      <c r="N174" t="n">
+        <v>3</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>['26', '33']</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" t="n">
+        <v>0</v>
+      </c>
+      <c r="W174" t="n">
+        <v>0</v>
+      </c>
+      <c r="X174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>7813992</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F175" t="n">
+        <v>25</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Suwon Bluewings</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1</v>
+      </c>
+      <c r="L175" t="n">
+        <v>3</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>4</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>['33', '60', '85']</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R175" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S175" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U175" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V175" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X175" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -37762,10 +37762,10 @@
         <v>1.26</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AU171" t="n">
         <v>3</v>
@@ -38195,13 +38195,13 @@
         <v>1</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AS173" t="n">
         <v>1.02</v>
       </c>
       <c r="AT173" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AU173" t="n">
         <v>3</v>
@@ -38416,10 +38416,10 @@
         <v>1.26</v>
       </c>
       <c r="AS174" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AU174" t="n">
         <v>1</v>
@@ -38631,13 +38631,13 @@
         <v>2</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS175" t="n">
         <v>1.57</v>
       </c>
       <c r="AT175" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="AU175" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP175"/>
+  <dimension ref="A1:BP176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.68</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.44</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.92</v>
@@ -3527,7 +3527,7 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.64</v>
@@ -3966,7 +3966,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR16" t="n">
         <v>1.51</v>
@@ -5053,7 +5053,7 @@
         <v>0.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.24</v>
@@ -6361,10 +6361,10 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR27" t="n">
         <v>1.14</v>
@@ -7672,7 +7672,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR33" t="n">
         <v>1.44</v>
@@ -7887,7 +7887,7 @@
         <v>1.25</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.44</v>
@@ -8544,7 +8544,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR37" t="n">
         <v>0.86</v>
@@ -8977,7 +8977,7 @@
         <v>1.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.68</v>
@@ -11157,7 +11157,7 @@
         <v>2.17</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.44</v>
@@ -11375,7 +11375,7 @@
         <v>0.17</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.8</v>
@@ -11814,7 +11814,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR52" t="n">
         <v>1.44</v>
@@ -12468,7 +12468,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR55" t="n">
         <v>1.05</v>
@@ -13337,7 +13337,7 @@
         <v>0.88</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.96</v>
@@ -14427,7 +14427,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ64" t="n">
         <v>1</v>
@@ -15735,7 +15735,7 @@
         <v>1.22</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.24</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR71" t="n">
         <v>1.23</v>
@@ -17264,7 +17264,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR77" t="n">
         <v>1.18</v>
@@ -17482,7 +17482,7 @@
         <v>2</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR78" t="n">
         <v>1.6</v>
@@ -18133,7 +18133,7 @@
         <v>1.45</v>
       </c>
       <c r="AP81" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.36</v>
@@ -18351,7 +18351,7 @@
         <v>1.91</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ82" t="n">
         <v>2</v>
@@ -19662,7 +19662,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR88" t="n">
         <v>0.99</v>
@@ -19880,7 +19880,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR89" t="n">
         <v>1.35</v>
@@ -20752,7 +20752,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR93" t="n">
         <v>1.16</v>
@@ -22057,7 +22057,7 @@
         <v>2.62</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ99" t="n">
         <v>2.32</v>
@@ -22929,7 +22929,7 @@
         <v>0.86</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.8</v>
@@ -23586,7 +23586,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR106" t="n">
         <v>1.32</v>
@@ -23804,7 +23804,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR107" t="n">
         <v>1.47</v>
@@ -24458,7 +24458,7 @@
         <v>1.68</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR110" t="n">
         <v>1.13</v>
@@ -25545,7 +25545,7 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.44</v>
@@ -26199,7 +26199,7 @@
         <v>0.75</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.96</v>
@@ -27292,7 +27292,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR123" t="n">
         <v>1.03</v>
@@ -27728,7 +27728,7 @@
         <v>2</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR125" t="n">
         <v>1.63</v>
@@ -29472,7 +29472,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR133" t="n">
         <v>1.34</v>
@@ -29690,7 +29690,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR134" t="n">
         <v>1.08</v>
@@ -30123,7 +30123,7 @@
         <v>0.84</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ136" t="n">
         <v>1</v>
@@ -30559,7 +30559,7 @@
         <v>1.16</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.36</v>
@@ -32088,7 +32088,7 @@
         <v>1</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR145" t="n">
         <v>1.06</v>
@@ -32524,7 +32524,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR147" t="n">
         <v>1.21</v>
@@ -32957,7 +32957,7 @@
         <v>1.81</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.64</v>
@@ -33175,7 +33175,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.92</v>
@@ -35576,7 +35576,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR161" t="n">
         <v>1.25</v>
@@ -35791,7 +35791,7 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AQ162" t="n">
         <v>2</v>
@@ -36227,7 +36227,7 @@
         <v>2.39</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AQ164" t="n">
         <v>2.32</v>
@@ -37102,7 +37102,7 @@
         <v>1.68</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AR168" t="n">
         <v>1.22</v>
@@ -38704,6 +38704,224 @@
       </c>
       <c r="BP175" t="n">
         <v>1.08</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="n">
+        <v>7813995</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>45886.29166666666</v>
+      </c>
+      <c r="F176" t="n">
+        <v>25</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Busan I'Park</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1</v>
+      </c>
+      <c r="K176" t="n">
+        <v>1</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>1</v>
+      </c>
+      <c r="N176" t="n">
+        <v>1</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S176" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T176" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U176" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V176" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W176" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X176" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="BP176" t="n">
+        <v>1.09</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -38861,13 +38861,13 @@
         <v>3</v>
       </c>
       <c r="AV176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW176" t="n">
         <v>4</v>
       </c>
       <c r="AX176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY176" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -19238,22 +19238,22 @@
         <v>2.32</v>
       </c>
       <c r="AU86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW86" t="n">
         <v>6</v>
       </c>
-      <c r="AV86" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW86" t="n">
-        <v>11</v>
-      </c>
       <c r="AX86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY86" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA86" t="n">
         <v>8</v>
@@ -19265,43 +19265,43 @@
         <v>13</v>
       </c>
       <c r="BD86" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BE86" t="n">
-        <v>0</v>
+        <v>7.76</v>
       </c>
       <c r="BF86" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG86" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BH86" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BI86" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BJ86" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BK86" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BL86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BM86" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BN86" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BO86" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="BP86" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="87">
@@ -19456,7 +19456,7 @@
         <v>2.29</v>
       </c>
       <c r="AU87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV87" t="n">
         <v>1</v>
@@ -19465,13 +19465,13 @@
         <v>5</v>
       </c>
       <c r="AX87" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY87" t="n">
         <v>7</v>
       </c>
-      <c r="AY87" t="n">
+      <c r="AZ87" t="n">
         <v>6</v>
-      </c>
-      <c r="AZ87" t="n">
-        <v>8</v>
       </c>
       <c r="BA87" t="n">
         <v>5</v>
@@ -19483,43 +19483,43 @@
         <v>9</v>
       </c>
       <c r="BD87" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BE87" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="BF87" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BG87" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BH87" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BI87" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BJ87" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BK87" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="BL87" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BM87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN87" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BO87" t="n">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="BP87" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="88">
@@ -19674,22 +19674,22 @@
         <v>2.34</v>
       </c>
       <c r="AU88" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY88" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA88" t="n">
         <v>5</v>
@@ -19701,43 +19701,43 @@
         <v>12</v>
       </c>
       <c r="BD88" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BE88" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF88" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BG88" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BH88" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BI88" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BJ88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK88" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BL88" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BM88" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="BN88" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BO88" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP88" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="89">
@@ -19892,22 +19892,22 @@
         <v>2.39</v>
       </c>
       <c r="AU89" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV89" t="n">
         <v>7</v>
       </c>
       <c r="AW89" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AX89" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY89" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ89" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA89" t="n">
         <v>5</v>
@@ -19919,19 +19919,19 @@
         <v>11</v>
       </c>
       <c r="BD89" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BE89" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="BF89" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="BG89" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BH89" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BI89" t="n">
         <v>1.8</v>
@@ -19940,22 +19940,22 @@
         <v>2</v>
       </c>
       <c r="BK89" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BL89" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BM89" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="BN89" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BO89" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="BP89" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="90">
@@ -20116,16 +20116,16 @@
         <v>9</v>
       </c>
       <c r="AW90" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX90" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AY90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ90" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA90" t="n">
         <v>4</v>
@@ -20137,43 +20137,43 @@
         <v>9</v>
       </c>
       <c r="BD90" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BE90" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="BF90" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BG90" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BH90" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BI90" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BJ90" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BK90" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BL90" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BM90" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BN90" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BO90" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="BP90" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="91">
@@ -20331,16 +20331,16 @@
         <v>7</v>
       </c>
       <c r="AV91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AX91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY91" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ91" t="n">
         <v>3</v>
@@ -20355,19 +20355,19 @@
         <v>9</v>
       </c>
       <c r="BD91" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BE91" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="BF91" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BG91" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BH91" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BI91" t="n">
         <v>1.9</v>
@@ -20376,22 +20376,22 @@
         <v>1.9</v>
       </c>
       <c r="BK91" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BL91" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BM91" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BN91" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BO91" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BP91" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="92">
@@ -20546,22 +20546,22 @@
         <v>2.94</v>
       </c>
       <c r="AU92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV92" t="n">
         <v>6</v>
       </c>
       <c r="AW92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ92" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA92" t="n">
         <v>9</v>
@@ -20573,19 +20573,19 @@
         <v>13</v>
       </c>
       <c r="BD92" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BE92" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="BF92" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="BG92" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BH92" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BI92" t="n">
         <v>1.88</v>
@@ -20594,22 +20594,22 @@
         <v>1.92</v>
       </c>
       <c r="BK92" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BL92" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BM92" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="BN92" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BO92" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="BP92" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="93">
@@ -20755,13 +20755,13 @@
         <v>1.48</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AS93" t="n">
         <v>1.32</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AU93" t="n">
         <v>4</v>
@@ -20770,16 +20770,16 @@
         <v>5</v>
       </c>
       <c r="AW93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ93" t="n">
         <v>6</v>
-      </c>
-      <c r="AZ93" t="n">
-        <v>7</v>
       </c>
       <c r="BA93" t="n">
         <v>1</v>
@@ -20976,10 +20976,10 @@
         <v>1.14</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AU94" t="n">
         <v>6</v>
@@ -20991,13 +20991,13 @@
         <v>5</v>
       </c>
       <c r="AX94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY94" t="n">
         <v>11</v>
       </c>
       <c r="AZ94" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA94" t="n">
         <v>4</v>
@@ -21191,10 +21191,10 @@
         <v>0.92</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AT95" t="n">
         <v>2.55</v>
@@ -21409,25 +21409,25 @@
         <v>1.36</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AS96" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AT96" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AU96" t="n">
         <v>4</v>
       </c>
       <c r="AV96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW96" t="n">
         <v>5</v>
       </c>
       <c r="AX96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY96" t="n">
         <v>9</v>
@@ -21627,13 +21627,13 @@
         <v>1.44</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT97" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AU97" t="n">
         <v>4</v>
@@ -21845,22 +21845,22 @@
         <v>1.64</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AU98" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV98" t="n">
         <v>3</v>
       </c>
       <c r="AW98" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX98" t="n">
         <v>14</v>
@@ -22063,13 +22063,13 @@
         <v>2.32</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AU99" t="n">
         <v>5</v>
@@ -22078,16 +22078,16 @@
         <v>4</v>
       </c>
       <c r="AW99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY99" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ99" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ99" t="n">
-        <v>8</v>
       </c>
       <c r="BA99" t="n">
         <v>4</v>
@@ -22281,25 +22281,25 @@
         <v>2</v>
       </c>
       <c r="AR100" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="AU100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV100" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX100" t="n">
         <v>6</v>
-      </c>
-      <c r="AW100" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX100" t="n">
-        <v>5</v>
       </c>
       <c r="AY100" t="n">
         <v>10</v>
@@ -22502,22 +22502,22 @@
         <v>1.18</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AU101" t="n">
         <v>0</v>
       </c>
       <c r="AV101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW101" t="n">
         <v>7</v>
       </c>
       <c r="AX101" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY101" t="n">
         <v>7</v>
@@ -22717,25 +22717,25 @@
         <v>1</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AU102" t="n">
         <v>5</v>
       </c>
       <c r="AV102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW102" t="n">
         <v>3</v>
       </c>
       <c r="AX102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY102" t="n">
         <v>8</v>
@@ -22935,13 +22935,13 @@
         <v>0.8</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AS103" t="n">
         <v>1.1</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AU103" t="n">
         <v>3</v>
@@ -23153,31 +23153,31 @@
         <v>1.44</v>
       </c>
       <c r="AR104" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS104" t="n">
         <v>1.14</v>
       </c>
-      <c r="AS104" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AT104" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AU104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW104" t="n">
         <v>3</v>
       </c>
       <c r="AX104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ104" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA104" t="n">
         <v>4</v>
@@ -23371,31 +23371,31 @@
         <v>1.64</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="AU105" t="n">
         <v>5</v>
       </c>
       <c r="AV105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW105" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX105" t="n">
         <v>3</v>
       </c>
       <c r="AY105" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA105" t="n">
         <v>3</v>
@@ -23589,25 +23589,25 @@
         <v>0.76</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="AU106" t="n">
         <v>2</v>
       </c>
       <c r="AV106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW106" t="n">
         <v>11</v>
       </c>
       <c r="AX106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY106" t="n">
         <v>13</v>
@@ -23807,13 +23807,13 @@
         <v>0.76</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="AU107" t="n">
         <v>4</v>
@@ -24028,19 +24028,19 @@
         <v>1.33</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AU108" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV108" t="n">
         <v>2</v>
       </c>
       <c r="AW108" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX108" t="n">
         <v>8</v>
@@ -24246,22 +24246,22 @@
         <v>1.17</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AU109" t="n">
         <v>3</v>
       </c>
       <c r="AV109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW109" t="n">
         <v>6</v>
       </c>
       <c r="AX109" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY109" t="n">
         <v>9</v>
@@ -24461,31 +24461,31 @@
         <v>1.48</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AU110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW110" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AX110" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY110" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ110" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA110" t="n">
         <v>6</v>
@@ -24679,13 +24679,13 @@
         <v>0.8</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AS111" t="n">
         <v>1.06</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AU111" t="n">
         <v>1</v>
@@ -24897,25 +24897,25 @@
         <v>0.92</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="AU112" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW112" t="n">
         <v>9</v>
       </c>
-      <c r="AV112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW112" t="n">
-        <v>10</v>
-      </c>
       <c r="AX112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY112" t="n">
         <v>19</v>
@@ -25115,31 +25115,31 @@
         <v>2.32</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AT113" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="AU113" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX113" t="n">
         <v>5</v>
       </c>
-      <c r="AV113" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW113" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX113" t="n">
-        <v>2</v>
-      </c>
       <c r="AY113" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BA113" t="n">
         <v>4</v>
@@ -25333,31 +25333,31 @@
         <v>1</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AU114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV114" t="n">
         <v>0</v>
       </c>
       <c r="AW114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX114" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY114" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ114" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BA114" t="n">
         <v>2</v>
@@ -25551,25 +25551,25 @@
         <v>1.44</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AS115" t="n">
         <v>1.17</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AU115" t="n">
         <v>6</v>
       </c>
       <c r="AV115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW115" t="n">
         <v>6</v>
       </c>
       <c r="AX115" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY115" t="n">
         <v>12</v>
@@ -25769,25 +25769,25 @@
         <v>1.64</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AT116" t="n">
         <v>2.39</v>
       </c>
       <c r="AU116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW116" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX116" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY116" t="n">
         <v>10</v>
@@ -25987,25 +25987,25 @@
         <v>1.24</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AU117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV117" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW117" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY117" t="n">
         <v>9</v>
@@ -26205,31 +26205,31 @@
         <v>0.96</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AS118" t="n">
         <v>1.18</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="AU118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW118" t="n">
         <v>4</v>
       </c>
-      <c r="AW118" t="n">
-        <v>3</v>
-      </c>
       <c r="AX118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY118" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ118" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA118" t="n">
         <v>6</v>
@@ -26423,25 +26423,25 @@
         <v>2</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="AU119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV119" t="n">
         <v>4</v>
       </c>
-      <c r="AV119" t="n">
-        <v>7</v>
-      </c>
       <c r="AW119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX119" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY119" t="n">
         <v>8</v>
@@ -26641,28 +26641,28 @@
         <v>1.44</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AT120" t="n">
         <v>2.59</v>
       </c>
       <c r="AU120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV120" t="n">
         <v>0</v>
       </c>
       <c r="AW120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX120" t="n">
         <v>1</v>
       </c>
       <c r="AY120" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ120" t="n">
         <v>1</v>
@@ -26859,22 +26859,22 @@
         <v>1.44</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AS121" t="n">
         <v>1.22</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="AU121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV121" t="n">
         <v>3</v>
       </c>
       <c r="AW121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX121" t="n">
         <v>7</v>
@@ -27080,22 +27080,22 @@
         <v>1.34</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AU122" t="n">
         <v>8</v>
       </c>
       <c r="AV122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW122" t="n">
         <v>14</v>
       </c>
       <c r="AX122" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY122" t="n">
         <v>22</v>
@@ -27295,22 +27295,22 @@
         <v>0.76</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AU123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV123" t="n">
         <v>3</v>
       </c>
       <c r="AW123" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX123" t="n">
         <v>9</v>
@@ -27513,25 +27513,25 @@
         <v>1.36</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AT124" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AU124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY124" t="n">
         <v>5</v>
@@ -27731,25 +27731,25 @@
         <v>1.48</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AS125" t="n">
         <v>1.34</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AU125" t="n">
         <v>2</v>
       </c>
       <c r="AV125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW125" t="n">
         <v>13</v>
       </c>
       <c r="AX125" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY125" t="n">
         <v>15</v>
@@ -27949,22 +27949,22 @@
         <v>1.68</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AT126" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AU126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV126" t="n">
         <v>3</v>
       </c>
       <c r="AW126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX126" t="n">
         <v>6</v>
@@ -28167,25 +28167,25 @@
         <v>2.32</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="AU127" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY127" t="n">
         <v>7</v>
@@ -28385,25 +28385,25 @@
         <v>2</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="AU128" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV128" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AW128" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX128" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY128" t="n">
         <v>16</v>
@@ -28603,25 +28603,25 @@
         <v>2.32</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AT129" t="n">
         <v>2.52</v>
       </c>
       <c r="AU129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW129" t="n">
         <v>3</v>
       </c>
-      <c r="AV129" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW129" t="n">
-        <v>2</v>
-      </c>
       <c r="AX129" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY129" t="n">
         <v>5</v>
@@ -28821,13 +28821,13 @@
         <v>1.44</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AS130" t="n">
         <v>1.21</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AU130" t="n">
         <v>5</v>
@@ -29039,25 +29039,25 @@
         <v>0.8</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AU131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV131" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW131" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY131" t="n">
         <v>13</v>
@@ -29257,25 +29257,25 @@
         <v>1.64</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="AU132" t="n">
         <v>2</v>
       </c>
       <c r="AV132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW132" t="n">
         <v>6</v>
       </c>
       <c r="AX132" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY132" t="n">
         <v>8</v>
@@ -29475,22 +29475,22 @@
         <v>1.48</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AS133" t="n">
         <v>1.4</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AU133" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AV133" t="n">
         <v>0</v>
       </c>
       <c r="AW133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX133" t="n">
         <v>6</v>
@@ -29693,22 +29693,22 @@
         <v>0.76</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AU134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV134" t="n">
         <v>0</v>
       </c>
       <c r="AW134" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX134" t="n">
         <v>4</v>
@@ -29911,16 +29911,16 @@
         <v>0.96</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AT135" t="n">
         <v>2.86</v>
       </c>
       <c r="AU135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV135" t="n">
         <v>0</v>
@@ -29932,7 +29932,7 @@
         <v>7</v>
       </c>
       <c r="AY135" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ135" t="n">
         <v>7</v>
@@ -30129,25 +30129,25 @@
         <v>1</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AU136" t="n">
         <v>5</v>
       </c>
       <c r="AV136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW136" t="n">
         <v>10</v>
       </c>
       <c r="AX136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY136" t="n">
         <v>15</v>
@@ -30347,31 +30347,31 @@
         <v>0.92</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AU137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ137" t="n">
         <v>3</v>
-      </c>
-      <c r="AV137" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW137" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX137" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY137" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ137" t="n">
-        <v>5</v>
       </c>
       <c r="BA137" t="n">
         <v>6</v>
@@ -30565,25 +30565,25 @@
         <v>1.36</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AU138" t="n">
         <v>2</v>
       </c>
       <c r="AV138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW138" t="n">
         <v>9</v>
       </c>
       <c r="AX138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY138" t="n">
         <v>11</v>
@@ -30592,13 +30592,13 @@
         <v>6</v>
       </c>
       <c r="BA138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC138" t="n">
         <v>6</v>
-      </c>
-      <c r="BB138" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC138" t="n">
-        <v>7</v>
       </c>
       <c r="BD138" t="n">
         <v>1.39</v>
@@ -30783,25 +30783,25 @@
         <v>1.24</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="AU139" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW139" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY139" t="n">
         <v>16</v>
@@ -31001,25 +31001,25 @@
         <v>1.44</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AT140" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AU140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV140" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX140" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY140" t="n">
         <v>6</v>
@@ -31219,25 +31219,25 @@
         <v>1.44</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AS141" t="n">
         <v>1.22</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AU141" t="n">
         <v>3</v>
       </c>
       <c r="AV141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW141" t="n">
         <v>2</v>
       </c>
       <c r="AX141" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY141" t="n">
         <v>5</v>
@@ -31437,25 +31437,25 @@
         <v>2</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AT142" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="AU142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AV142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW142" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AX142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY142" t="n">
         <v>18</v>
@@ -31655,25 +31655,25 @@
         <v>0.8</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AU143" t="n">
         <v>5</v>
       </c>
       <c r="AV143" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW143" t="n">
         <v>10</v>
       </c>
       <c r="AX143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY143" t="n">
         <v>15</v>
@@ -31876,10 +31876,10 @@
         <v>1.24</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AU144" t="n">
         <v>5</v>
@@ -32091,13 +32091,13 @@
         <v>1.48</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AS145" t="n">
         <v>1.36</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AU145" t="n">
         <v>1</v>
@@ -32309,13 +32309,13 @@
         <v>1.24</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AU146" t="n">
         <v>6</v>
@@ -32527,25 +32527,25 @@
         <v>0.76</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AU147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX147" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY147" t="n">
         <v>8</v>
@@ -32745,25 +32745,25 @@
         <v>2.32</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AU148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV148" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW148" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX148" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY148" t="n">
         <v>10</v>
@@ -32966,22 +32966,22 @@
         <v>1.36</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="AU149" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV149" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW149" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY149" t="n">
         <v>13</v>
@@ -32999,13 +32999,13 @@
         <v>5</v>
       </c>
       <c r="BD149" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BE149" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="BF149" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BG149" t="n">
         <v>1.54</v>
@@ -33181,22 +33181,22 @@
         <v>0.92</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AU150" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV150" t="n">
         <v>3</v>
       </c>
       <c r="AW150" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX150" t="n">
         <v>5</v>
@@ -33217,13 +33217,13 @@
         <v>9</v>
       </c>
       <c r="BD150" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BE150" t="n">
-        <v>0</v>
+        <v>6.96</v>
       </c>
       <c r="BF150" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BG150" t="n">
         <v>1.45</v>
@@ -33402,22 +33402,22 @@
         <v>1.2</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AU151" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV151" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW151" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY151" t="n">
         <v>11</v>
@@ -33435,13 +33435,13 @@
         <v>10</v>
       </c>
       <c r="BD151" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="BE151" t="n">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="BF151" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BG151" t="n">
         <v>1.67</v>
@@ -33617,13 +33617,13 @@
         <v>1</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AU152" t="n">
         <v>3</v>
@@ -33653,13 +33653,13 @@
         <v>9</v>
       </c>
       <c r="BD152" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BE152" t="n">
-        <v>0</v>
+        <v>7.89</v>
       </c>
       <c r="BF152" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="BG152" t="n">
         <v>1.54</v>
@@ -33835,25 +33835,25 @@
         <v>1.68</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="AU153" t="n">
         <v>4</v>
       </c>
       <c r="AV153" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW153" t="n">
         <v>6</v>
       </c>
       <c r="AX153" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY153" t="n">
         <v>10</v>
@@ -34053,22 +34053,22 @@
         <v>1.44</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AS154" t="n">
         <v>1.26</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="AU154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV154" t="n">
         <v>3</v>
       </c>
       <c r="AW154" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX154" t="n">
         <v>2</v>
@@ -34271,22 +34271,22 @@
         <v>0.8</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AU155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV155" t="n">
         <v>3</v>
       </c>
       <c r="AW155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX155" t="n">
         <v>5</v>
@@ -34489,22 +34489,22 @@
         <v>1.36</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AT156" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AU156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV156" t="n">
         <v>8</v>
       </c>
       <c r="AW156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX156" t="n">
         <v>4</v>
@@ -34716,13 +34716,13 @@
         <v>2.57</v>
       </c>
       <c r="AU157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV157" t="n">
         <v>0</v>
       </c>
       <c r="AW157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX157" t="n">
         <v>1</v>
@@ -34925,25 +34925,25 @@
         <v>1.24</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AU158" t="n">
         <v>2</v>
       </c>
       <c r="AV158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW158" t="n">
         <v>5</v>
       </c>
       <c r="AX158" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY158" t="n">
         <v>7</v>
@@ -35143,25 +35143,25 @@
         <v>1.44</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AU159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW159" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX159" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY159" t="n">
         <v>6</v>
@@ -35361,25 +35361,25 @@
         <v>0.96</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AU160" t="n">
         <v>6</v>
       </c>
       <c r="AV160" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW160" t="n">
         <v>5</v>
       </c>
       <c r="AX160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY160" t="n">
         <v>11</v>
@@ -35579,25 +35579,25 @@
         <v>1.48</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AU161" t="n">
         <v>2</v>
       </c>
       <c r="AV161" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW161" t="n">
         <v>0</v>
       </c>
       <c r="AX161" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AY161" t="n">
         <v>2</v>
@@ -35797,25 +35797,25 @@
         <v>2</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AT162" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AU162" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV162" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW162" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX162" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AY162" t="n">
         <v>18</v>
@@ -36015,22 +36015,22 @@
         <v>0.92</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AU163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV163" t="n">
         <v>4</v>
       </c>
       <c r="AW163" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX163" t="n">
         <v>2</v>
@@ -36233,13 +36233,13 @@
         <v>2.32</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AS164" t="n">
         <v>1.29</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="AU164" t="n">
         <v>5</v>
@@ -36451,13 +36451,13 @@
         <v>0.8</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AU165" t="n">
         <v>4</v>
@@ -36669,13 +36669,13 @@
         <v>1.44</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AT166" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AU166" t="n">
         <v>3</v>
@@ -36890,10 +36890,10 @@
         <v>1.23</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AU167" t="n">
         <v>1</v>
@@ -37105,25 +37105,25 @@
         <v>0.76</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AS168" t="n">
         <v>1.18</v>
       </c>
       <c r="AT168" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AU168" t="n">
         <v>7</v>
       </c>
       <c r="AV168" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW168" t="n">
         <v>10</v>
       </c>
       <c r="AX168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY168" t="n">
         <v>17</v>
@@ -37323,13 +37323,13 @@
         <v>1.64</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AT169" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AU169" t="n">
         <v>3</v>
@@ -37541,25 +37541,25 @@
         <v>1.24</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AU170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX170" t="n">
         <v>3</v>
-      </c>
-      <c r="AV170" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW170" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX170" t="n">
-        <v>4</v>
       </c>
       <c r="AY170" t="n">
         <v>9</v>
@@ -37759,25 +37759,25 @@
         <v>1.64</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AU171" t="n">
         <v>3</v>
       </c>
       <c r="AV171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW171" t="n">
         <v>6</v>
       </c>
       <c r="AX171" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY171" t="n">
         <v>9</v>
@@ -37986,13 +37986,13 @@
         <v>2.42</v>
       </c>
       <c r="AU172" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV172" t="n">
         <v>6</v>
       </c>
       <c r="AW172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX172" t="n">
         <v>8</v>
@@ -38195,25 +38195,25 @@
         <v>1</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AT173" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AU173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW173" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX173" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY173" t="n">
         <v>11</v>
@@ -38416,10 +38416,10 @@
         <v>1.26</v>
       </c>
       <c r="AS174" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="AU174" t="n">
         <v>1</v>
@@ -38631,13 +38631,13 @@
         <v>2</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AT175" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="AU175" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP176"/>
+  <dimension ref="A1:BP180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ5" t="n">
         <v>2</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.24</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.96</v>
@@ -2655,10 +2655,10 @@
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR10" t="n">
         <v>0.6899999999999999</v>
@@ -2873,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR11" t="n">
         <v>0.91</v>
@@ -3312,7 +3312,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR13" t="n">
         <v>1.27</v>
@@ -3527,10 +3527,10 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.96</v>
@@ -3963,7 +3963,7 @@
         <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.48</v>
@@ -4184,7 +4184,7 @@
         <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR17" t="n">
         <v>1.03</v>
@@ -4399,10 +4399,10 @@
         <v>2</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR18" t="n">
         <v>1.16</v>
@@ -4617,7 +4617,7 @@
         <v>0.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.96</v>
@@ -4835,7 +4835,7 @@
         <v>1.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ20" t="n">
         <v>2</v>
@@ -5053,7 +5053,7 @@
         <v>0.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.24</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ22" t="n">
         <v>2.32</v>
@@ -5492,7 +5492,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR23" t="n">
         <v>1.57</v>
@@ -5925,10 +5925,10 @@
         <v>2.33</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR25" t="n">
         <v>1.51</v>
@@ -6364,7 +6364,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR27" t="n">
         <v>1.14</v>
@@ -6579,10 +6579,10 @@
         <v>2.33</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR28" t="n">
         <v>0.9399999999999999</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR29" t="n">
         <v>1.24</v>
@@ -7015,7 +7015,7 @@
         <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
@@ -7236,7 +7236,7 @@
         <v>2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR31" t="n">
         <v>1.42</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.96</v>
@@ -7887,10 +7887,10 @@
         <v>1.25</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR34" t="n">
         <v>0.73</v>
@@ -8105,10 +8105,10 @@
         <v>2.25</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR35" t="n">
         <v>0.78</v>
@@ -8326,7 +8326,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR36" t="n">
         <v>1.2</v>
@@ -8541,10 +8541,10 @@
         <v>0.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR37" t="n">
         <v>0.86</v>
@@ -8980,7 +8980,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR39" t="n">
         <v>1.25</v>
@@ -9198,7 +9198,7 @@
         <v>2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR40" t="n">
         <v>1.53</v>
@@ -9413,10 +9413,10 @@
         <v>1.8</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR41" t="n">
         <v>1.35</v>
@@ -9849,10 +9849,10 @@
         <v>0.2</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR43" t="n">
         <v>0.82</v>
@@ -10067,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.24</v>
@@ -10288,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR45" t="n">
         <v>1.2</v>
@@ -10503,7 +10503,7 @@
         <v>1.67</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ46" t="n">
         <v>2</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR47" t="n">
         <v>1.21</v>
@@ -11160,7 +11160,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR49" t="n">
         <v>1.27</v>
@@ -11375,10 +11375,10 @@
         <v>0.17</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR50" t="n">
         <v>0.8100000000000001</v>
@@ -11593,7 +11593,7 @@
         <v>0.57</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.96</v>
@@ -11814,7 +11814,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR52" t="n">
         <v>1.44</v>
@@ -12247,10 +12247,10 @@
         <v>1.86</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR54" t="n">
         <v>0.89</v>
@@ -12465,7 +12465,7 @@
         <v>1.29</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.48</v>
@@ -12686,7 +12686,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -12901,10 +12901,10 @@
         <v>1.29</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR57" t="n">
         <v>1.29</v>
@@ -13119,10 +13119,10 @@
         <v>1.38</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR58" t="n">
         <v>1.16</v>
@@ -13337,7 +13337,7 @@
         <v>0.88</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.96</v>
@@ -13558,7 +13558,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR60" t="n">
         <v>1.45</v>
@@ -13773,7 +13773,7 @@
         <v>2.38</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.32</v>
@@ -13994,7 +13994,7 @@
         <v>2</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR62" t="n">
         <v>1.59</v>
@@ -14209,10 +14209,10 @@
         <v>1.88</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR63" t="n">
         <v>1.29</v>
@@ -14645,10 +14645,10 @@
         <v>1.89</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR65" t="n">
         <v>0.92</v>
@@ -14863,10 +14863,10 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR66" t="n">
         <v>1.37</v>
@@ -15081,10 +15081,10 @@
         <v>1.22</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR67" t="n">
         <v>1.14</v>
@@ -15520,7 +15520,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR69" t="n">
         <v>1.36</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR71" t="n">
         <v>1.23</v>
@@ -16171,7 +16171,7 @@
         <v>0.9</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ72" t="n">
         <v>1</v>
@@ -16389,10 +16389,10 @@
         <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR73" t="n">
         <v>1.28</v>
@@ -16825,10 +16825,10 @@
         <v>0.7</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR75" t="n">
         <v>1.21</v>
@@ -17043,10 +17043,10 @@
         <v>1.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR76" t="n">
         <v>1.15</v>
@@ -17482,7 +17482,7 @@
         <v>2</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR78" t="n">
         <v>1.6</v>
@@ -17697,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.24</v>
@@ -17915,7 +17915,7 @@
         <v>0.82</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ80" t="n">
         <v>1</v>
@@ -18133,10 +18133,10 @@
         <v>1.45</v>
       </c>
       <c r="AP81" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR81" t="n">
         <v>1.03</v>
@@ -18569,7 +18569,7 @@
         <v>2.55</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ83" t="n">
         <v>2.32</v>
@@ -18787,7 +18787,7 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.96</v>
@@ -19005,10 +19005,10 @@
         <v>1.91</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR85" t="n">
         <v>1.32</v>
@@ -19226,7 +19226,7 @@
         <v>1</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR86" t="n">
         <v>1.13</v>
@@ -19444,7 +19444,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR87" t="n">
         <v>1.18</v>
@@ -19659,7 +19659,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.48</v>
@@ -19877,10 +19877,10 @@
         <v>0.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR89" t="n">
         <v>1.35</v>
@@ -20098,7 +20098,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR90" t="n">
         <v>1.44</v>
@@ -20316,7 +20316,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR91" t="n">
         <v>1.36</v>
@@ -20534,7 +20534,7 @@
         <v>2</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR92" t="n">
         <v>1.65</v>
@@ -20749,7 +20749,7 @@
         <v>1.69</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.48</v>
@@ -20967,7 +20967,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ94" t="n">
         <v>1</v>
@@ -21188,7 +21188,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR95" t="n">
         <v>1.19</v>
@@ -21403,10 +21403,10 @@
         <v>1.38</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR96" t="n">
         <v>1.09</v>
@@ -21624,7 +21624,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR97" t="n">
         <v>1.44</v>
@@ -21842,7 +21842,7 @@
         <v>2</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR98" t="n">
         <v>1.67</v>
@@ -22057,7 +22057,7 @@
         <v>2.62</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ99" t="n">
         <v>2.32</v>
@@ -22275,7 +22275,7 @@
         <v>2</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ100" t="n">
         <v>2</v>
@@ -22711,7 +22711,7 @@
         <v>0.64</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ102" t="n">
         <v>1</v>
@@ -22932,7 +22932,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR103" t="n">
         <v>1.3</v>
@@ -23147,10 +23147,10 @@
         <v>1.93</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR104" t="n">
         <v>1.17</v>
@@ -23368,7 +23368,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR105" t="n">
         <v>1.39</v>
@@ -23583,10 +23583,10 @@
         <v>0.36</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR106" t="n">
         <v>1.28</v>
@@ -23804,7 +23804,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR107" t="n">
         <v>1.44</v>
@@ -24019,10 +24019,10 @@
         <v>1.87</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR108" t="n">
         <v>1.33</v>
@@ -24240,7 +24240,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR109" t="n">
         <v>1.17</v>
@@ -24455,7 +24455,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.48</v>
@@ -24676,7 +24676,7 @@
         <v>1</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR111" t="n">
         <v>1.13</v>
@@ -24891,10 +24891,10 @@
         <v>1.13</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR112" t="n">
         <v>1.28</v>
@@ -25545,10 +25545,10 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR115" t="n">
         <v>1.02</v>
@@ -25763,10 +25763,10 @@
         <v>1.56</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR116" t="n">
         <v>1.04</v>
@@ -25981,7 +25981,7 @@
         <v>1.31</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.24</v>
@@ -26417,7 +26417,7 @@
         <v>1.94</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ119" t="n">
         <v>2</v>
@@ -26635,10 +26635,10 @@
         <v>1.19</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR120" t="n">
         <v>1.23</v>
@@ -26856,7 +26856,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR121" t="n">
         <v>1.46</v>
@@ -27071,10 +27071,10 @@
         <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR122" t="n">
         <v>1.34</v>
@@ -27289,10 +27289,10 @@
         <v>0.65</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR123" t="n">
         <v>1.04</v>
@@ -27510,7 +27510,7 @@
         <v>1</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR124" t="n">
         <v>1.05</v>
@@ -27946,7 +27946,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR126" t="n">
         <v>1.16</v>
@@ -28161,7 +28161,7 @@
         <v>2.59</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ127" t="n">
         <v>2.32</v>
@@ -28597,7 +28597,7 @@
         <v>2.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ129" t="n">
         <v>2.32</v>
@@ -28818,7 +28818,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR130" t="n">
         <v>1.19</v>
@@ -29033,10 +29033,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP131" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR131" t="n">
         <v>1.27</v>
@@ -29254,7 +29254,7 @@
         <v>1</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR132" t="n">
         <v>1.04</v>
@@ -29469,7 +29469,7 @@
         <v>1.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.48</v>
@@ -29687,10 +29687,10 @@
         <v>0.67</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR134" t="n">
         <v>1.13</v>
@@ -30123,7 +30123,7 @@
         <v>0.84</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ136" t="n">
         <v>1</v>
@@ -30341,10 +30341,10 @@
         <v>0.95</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR137" t="n">
         <v>1.21</v>
@@ -30562,7 +30562,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR138" t="n">
         <v>1.37</v>
@@ -30995,10 +30995,10 @@
         <v>1.26</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR140" t="n">
         <v>1.38</v>
@@ -31213,10 +31213,10 @@
         <v>1.53</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR141" t="n">
         <v>1.04</v>
@@ -31431,7 +31431,7 @@
         <v>2.05</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ142" t="n">
         <v>2</v>
@@ -31649,10 +31649,10 @@
         <v>0.95</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR143" t="n">
         <v>1.29</v>
@@ -31867,10 +31867,10 @@
         <v>1.15</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR144" t="n">
         <v>1.24</v>
@@ -32303,7 +32303,7 @@
         <v>1.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.24</v>
@@ -32524,7 +32524,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR147" t="n">
         <v>1.2</v>
@@ -32739,7 +32739,7 @@
         <v>2.4</v>
       </c>
       <c r="AP148" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ148" t="n">
         <v>2.32</v>
@@ -32960,7 +32960,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR149" t="n">
         <v>1.36</v>
@@ -33175,10 +33175,10 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR150" t="n">
         <v>1.08</v>
@@ -33396,7 +33396,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR151" t="n">
         <v>1.2</v>
@@ -33829,10 +33829,10 @@
         <v>1.76</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AR153" t="n">
         <v>1.09</v>
@@ -34050,7 +34050,7 @@
         <v>2</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR154" t="n">
         <v>1.61</v>
@@ -34268,7 +34268,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR155" t="n">
         <v>1.33</v>
@@ -34483,10 +34483,10 @@
         <v>1.23</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR156" t="n">
         <v>1.37</v>
@@ -34701,7 +34701,7 @@
         <v>2.45</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ157" t="n">
         <v>2.32</v>
@@ -34919,7 +34919,7 @@
         <v>1.18</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.24</v>
@@ -35140,7 +35140,7 @@
         <v>1</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR159" t="n">
         <v>1</v>
@@ -35355,7 +35355,7 @@
         <v>0.91</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.96</v>
@@ -35573,7 +35573,7 @@
         <v>1.55</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.48</v>
@@ -35791,7 +35791,7 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ162" t="n">
         <v>2</v>
@@ -36012,7 +36012,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AR163" t="n">
         <v>1.41</v>
@@ -36448,7 +36448,7 @@
         <v>2</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AR165" t="n">
         <v>1.62</v>
@@ -36663,10 +36663,10 @@
         <v>1.39</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR166" t="n">
         <v>1.14</v>
@@ -36881,7 +36881,7 @@
         <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ167" t="n">
         <v>1</v>
@@ -37099,10 +37099,10 @@
         <v>0.7</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AR168" t="n">
         <v>1.27</v>
@@ -37320,7 +37320,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR169" t="n">
         <v>1.2</v>
@@ -37535,7 +37535,7 @@
         <v>1.17</v>
       </c>
       <c r="AP170" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.24</v>
@@ -37753,10 +37753,10 @@
         <v>1.71</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR171" t="n">
         <v>1.3</v>
@@ -37971,10 +37971,10 @@
         <v>1.46</v>
       </c>
       <c r="AP172" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR172" t="n">
         <v>1.2</v>
@@ -38410,7 +38410,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR174" t="n">
         <v>1.26</v>
@@ -38625,7 +38625,7 @@
         <v>2.08</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AQ175" t="n">
         <v>2</v>
@@ -38843,7 +38843,7 @@
         <v>1.42</v>
       </c>
       <c r="AP176" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.48</v>
@@ -38922,6 +38922,878 @@
       </c>
       <c r="BP176" t="n">
         <v>1.09</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="n">
+        <v>7813996</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F177" t="n">
+        <v>26</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Jeonnam Dragons</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>2</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>['57', '90+2']</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R177" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S177" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T177" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U177" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V177" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W177" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X177" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="n">
+        <v>7813997</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F178" t="n">
+        <v>26</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R178" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S178" t="n">
+        <v>4</v>
+      </c>
+      <c r="T178" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U178" t="n">
+        <v>3</v>
+      </c>
+      <c r="V178" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W178" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X178" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>7813999</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F179" t="n">
+        <v>26</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Seongnam</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Gyeongnam</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" t="n">
+        <v>2</v>
+      </c>
+      <c r="L179" t="n">
+        <v>2</v>
+      </c>
+      <c r="M179" t="n">
+        <v>1</v>
+      </c>
+      <c r="N179" t="n">
+        <v>3</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>['45', '49']</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R179" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S179" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T179" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U179" t="n">
+        <v>3</v>
+      </c>
+      <c r="V179" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W179" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X179" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="n">
+        <v>7813998</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F180" t="n">
+        <v>26</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="n">
+        <v>1</v>
+      </c>
+      <c r="N180" t="n">
+        <v>2</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R180" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S180" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V180" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X180" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BH180" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI180" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM180" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>1.07</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -39076,7 +39076,7 @@
         <v>2.37</v>
       </c>
       <c r="AU177" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV177" t="n">
         <v>0</v>
@@ -39088,7 +39088,7 @@
         <v>8</v>
       </c>
       <c r="AY177" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ177" t="n">
         <v>8</v>
@@ -39300,16 +39300,16 @@
         <v>1</v>
       </c>
       <c r="AW178" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX178" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY178" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ178" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA178" t="n">
         <v>9</v>
@@ -39512,22 +39512,22 @@
         <v>2.33</v>
       </c>
       <c r="AU179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW179" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX179" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY179" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ179" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA179" t="n">
         <v>4</v>
@@ -39736,13 +39736,13 @@
         <v>3</v>
       </c>
       <c r="AW180" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX180" t="n">
         <v>5</v>
       </c>
       <c r="AY180" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ180" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP180"/>
+  <dimension ref="A1:BP183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.88</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.42</v>
@@ -1568,7 +1568,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>3</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR9" t="n">
         <v>2.45</v>
@@ -3094,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR12" t="n">
         <v>0.67</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.88</v>
@@ -3748,7 +3748,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR15" t="n">
         <v>0.6899999999999999</v>
@@ -3966,7 +3966,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR16" t="n">
         <v>1.51</v>
@@ -4620,7 +4620,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR19" t="n">
         <v>1.3</v>
@@ -4838,7 +4838,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR20" t="n">
         <v>0.93</v>
@@ -5056,7 +5056,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR21" t="n">
         <v>0.89</v>
@@ -5274,7 +5274,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR22" t="n">
         <v>0.79</v>
@@ -5489,7 +5489,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.42</v>
@@ -5710,7 +5710,7 @@
         <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR24" t="n">
         <v>1.08</v>
@@ -6143,10 +6143,10 @@
         <v>0.33</v>
       </c>
       <c r="AP26" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR26" t="n">
         <v>1.55</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.77</v>
@@ -7233,7 +7233,7 @@
         <v>2</v>
       </c>
       <c r="AP31" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.73</v>
@@ -7454,7 +7454,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR32" t="n">
         <v>0.92</v>
@@ -7669,10 +7669,10 @@
         <v>1.75</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR33" t="n">
         <v>1.44</v>
@@ -8323,7 +8323,7 @@
         <v>2</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.42</v>
@@ -8762,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR38" t="n">
         <v>1.24</v>
@@ -8977,7 +8977,7 @@
         <v>1.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.73</v>
@@ -9195,7 +9195,7 @@
         <v>1.6</v>
       </c>
       <c r="AP40" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.88</v>
@@ -9631,10 +9631,10 @@
         <v>0.8</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR42" t="n">
         <v>1.31</v>
@@ -10070,7 +10070,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR44" t="n">
         <v>1.31</v>
@@ -10506,7 +10506,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR46" t="n">
         <v>1.29</v>
@@ -10939,10 +10939,10 @@
         <v>0.67</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR48" t="n">
         <v>1.41</v>
@@ -11157,7 +11157,7 @@
         <v>2.17</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.42</v>
@@ -11596,7 +11596,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR51" t="n">
         <v>1.07</v>
@@ -11811,7 +11811,7 @@
         <v>0.43</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.77</v>
@@ -12029,7 +12029,7 @@
         <v>0.86</v>
       </c>
       <c r="AP53" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ53" t="n">
         <v>1</v>
@@ -12468,7 +12468,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR55" t="n">
         <v>1.05</v>
@@ -12683,7 +12683,7 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.73</v>
@@ -13340,7 +13340,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR59" t="n">
         <v>0.9399999999999999</v>
@@ -13555,7 +13555,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.77</v>
@@ -13776,7 +13776,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR61" t="n">
         <v>1.32</v>
@@ -13991,7 +13991,7 @@
         <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.42</v>
@@ -14427,7 +14427,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ64" t="n">
         <v>1</v>
@@ -15299,10 +15299,10 @@
         <v>1.89</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR68" t="n">
         <v>1.12</v>
@@ -15517,7 +15517,7 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.42</v>
@@ -15735,10 +15735,10 @@
         <v>1.22</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR70" t="n">
         <v>1.36</v>
@@ -16607,10 +16607,10 @@
         <v>2.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR74" t="n">
         <v>1.43</v>
@@ -17261,10 +17261,10 @@
         <v>1.8</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR77" t="n">
         <v>1.18</v>
@@ -17479,7 +17479,7 @@
         <v>0.3</v>
       </c>
       <c r="AP78" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.77</v>
@@ -17700,7 +17700,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR79" t="n">
         <v>1.28</v>
@@ -18351,10 +18351,10 @@
         <v>1.91</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ82" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR82" t="n">
         <v>1.34</v>
@@ -18572,7 +18572,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR83" t="n">
         <v>1.12</v>
@@ -18790,7 +18790,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR84" t="n">
         <v>1.13</v>
@@ -19441,7 +19441,7 @@
         <v>0.67</v>
       </c>
       <c r="AP87" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.77</v>
@@ -19662,7 +19662,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR88" t="n">
         <v>0.99</v>
@@ -20095,7 +20095,7 @@
         <v>1.75</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.62</v>
@@ -20313,7 +20313,7 @@
         <v>2.08</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.73</v>
@@ -20531,7 +20531,7 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.42</v>
@@ -20752,7 +20752,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR93" t="n">
         <v>1.15</v>
@@ -21185,7 +21185,7 @@
         <v>1.08</v>
       </c>
       <c r="AP95" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.88</v>
@@ -21621,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.42</v>
@@ -21839,7 +21839,7 @@
         <v>1.69</v>
       </c>
       <c r="AP98" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.62</v>
@@ -22060,7 +22060,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR99" t="n">
         <v>1.08</v>
@@ -22278,7 +22278,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ100" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR100" t="n">
         <v>1.07</v>
@@ -22493,10 +22493,10 @@
         <v>1.29</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR101" t="n">
         <v>1.18</v>
@@ -22929,7 +22929,7 @@
         <v>0.86</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.77</v>
@@ -23365,7 +23365,7 @@
         <v>1.57</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.62</v>
@@ -23801,7 +23801,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.77</v>
@@ -24237,7 +24237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.42</v>
@@ -24458,7 +24458,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR110" t="n">
         <v>1.17</v>
@@ -25109,10 +25109,10 @@
         <v>2.53</v>
       </c>
       <c r="AP113" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ113" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR113" t="n">
         <v>1.67</v>
@@ -25327,7 +25327,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ114" t="n">
         <v>1</v>
@@ -25984,7 +25984,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR117" t="n">
         <v>1.11</v>
@@ -26199,10 +26199,10 @@
         <v>0.75</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR118" t="n">
         <v>1.33</v>
@@ -26420,7 +26420,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ119" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR119" t="n">
         <v>1.31</v>
@@ -26853,7 +26853,7 @@
         <v>1.65</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.42</v>
@@ -27725,10 +27725,10 @@
         <v>1.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR125" t="n">
         <v>1.66</v>
@@ -27943,7 +27943,7 @@
         <v>1.76</v>
       </c>
       <c r="AP126" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.73</v>
@@ -28164,7 +28164,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR127" t="n">
         <v>1.32</v>
@@ -28379,10 +28379,10 @@
         <v>1.94</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ128" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR128" t="n">
         <v>1.43</v>
@@ -28600,7 +28600,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR129" t="n">
         <v>1.23</v>
@@ -28815,7 +28815,7 @@
         <v>1.61</v>
       </c>
       <c r="AP130" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.42</v>
@@ -29472,7 +29472,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR133" t="n">
         <v>1.29</v>
@@ -29905,10 +29905,10 @@
         <v>0.89</v>
       </c>
       <c r="AP135" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR135" t="n">
         <v>1.64</v>
@@ -30559,7 +30559,7 @@
         <v>1.16</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.42</v>
@@ -30777,10 +30777,10 @@
         <v>1.32</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR139" t="n">
         <v>1.31</v>
@@ -31434,7 +31434,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ142" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR142" t="n">
         <v>1.22</v>
@@ -32088,7 +32088,7 @@
         <v>1</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR145" t="n">
         <v>1.03</v>
@@ -32306,7 +32306,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR146" t="n">
         <v>1.35</v>
@@ -32521,7 +32521,7 @@
         <v>0.65</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.77</v>
@@ -32742,7 +32742,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ148" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR148" t="n">
         <v>1.26</v>
@@ -32957,7 +32957,7 @@
         <v>1.81</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.62</v>
@@ -33393,7 +33393,7 @@
         <v>1.24</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.42</v>
@@ -33611,7 +33611,7 @@
         <v>1.05</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ152" t="n">
         <v>1</v>
@@ -34047,7 +34047,7 @@
         <v>1.43</v>
       </c>
       <c r="AP154" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.42</v>
@@ -34265,7 +34265,7 @@
         <v>0.95</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.77</v>
@@ -34704,7 +34704,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ157" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR157" t="n">
         <v>1.23</v>
@@ -34922,7 +34922,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR158" t="n">
         <v>1.28</v>
@@ -35358,7 +35358,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR160" t="n">
         <v>1.04</v>
@@ -35576,7 +35576,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR161" t="n">
         <v>1.24</v>
@@ -35794,7 +35794,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ162" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR162" t="n">
         <v>1.14</v>
@@ -36009,7 +36009,7 @@
         <v>0.91</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.88</v>
@@ -36227,10 +36227,10 @@
         <v>2.39</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ164" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AR164" t="n">
         <v>1.39</v>
@@ -36445,7 +36445,7 @@
         <v>0.87</v>
       </c>
       <c r="AP165" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.77</v>
@@ -37317,7 +37317,7 @@
         <v>1.65</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.62</v>
@@ -37538,7 +37538,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR170" t="n">
         <v>1.07</v>
@@ -38189,7 +38189,7 @@
         <v>1</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ173" t="n">
         <v>1</v>
@@ -38407,7 +38407,7 @@
         <v>1.29</v>
       </c>
       <c r="AP174" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.42</v>
@@ -38628,7 +38628,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ175" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AR175" t="n">
         <v>1.33</v>
@@ -38846,7 +38846,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR176" t="n">
         <v>1.17</v>
@@ -39794,6 +39794,660 @@
       </c>
       <c r="BP180" t="n">
         <v>1.07</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="n">
+        <v>7814000</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>45893.29166666666</v>
+      </c>
+      <c r="F181" t="n">
+        <v>26</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Cheongju</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>2</v>
+      </c>
+      <c r="K181" t="n">
+        <v>2</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>4</v>
+      </c>
+      <c r="N181" t="n">
+        <v>4</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>['18', '40', '55', '88']</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>5</v>
+      </c>
+      <c r="R181" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S181" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V181" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X181" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="n">
+        <v>7814001</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>45893.29166666666</v>
+      </c>
+      <c r="F182" t="n">
+        <v>26</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Asan Mugunghwa</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Busan I'Park</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>1</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>3</v>
+      </c>
+      <c r="R182" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S182" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T182" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U182" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V182" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W182" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X182" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF182" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG182" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BH182" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI182" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ182" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK182" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BL182" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM182" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BN182" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO182" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BP182" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="n">
+        <v>7814002</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>45893.29166666666</v>
+      </c>
+      <c r="F183" t="n">
+        <v>26</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Hwaseong</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Suwon Bluewings</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>1</v>
+      </c>
+      <c r="L183" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" t="n">
+        <v>1</v>
+      </c>
+      <c r="N183" t="n">
+        <v>2</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="R183" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S183" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T183" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U183" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V183" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W183" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X183" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BM183" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BN183" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BO183" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP183" t="n">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -40393,13 +40393,13 @@
         <v>5</v>
       </c>
       <c r="AX183" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY183" t="n">
         <v>8</v>
       </c>
       <c r="AZ183" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA183" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -39948,16 +39948,16 @@
         <v>2.46</v>
       </c>
       <c r="AU181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV181" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AW181" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX181" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY181" t="n">
         <v>12</v>
@@ -40166,16 +40166,16 @@
         <v>2.8</v>
       </c>
       <c r="AU182" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV182" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW182" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX182" t="n">
         <v>4</v>
-      </c>
-      <c r="AX182" t="n">
-        <v>5</v>
       </c>
       <c r="AY182" t="n">
         <v>9</v>
@@ -40387,13 +40387,13 @@
         <v>3</v>
       </c>
       <c r="AV183" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW183" t="n">
         <v>5</v>
       </c>
       <c r="AX183" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY183" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP182"/>
+  <dimension ref="A1:BP188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.62</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.93</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>3</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.85</v>
@@ -2658,7 +2658,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR10" t="n">
         <v>0.6899999999999999</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.62</v>
@@ -3530,7 +3530,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR15" t="n">
         <v>0.6899999999999999</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.85</v>
@@ -4620,7 +4620,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ22" t="n">
         <v>2.08</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR23" t="n">
         <v>1.8</v>
@@ -5710,7 +5710,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR24" t="n">
         <v>1.28</v>
@@ -5928,7 +5928,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR25" t="n">
         <v>1.94</v>
@@ -6361,10 +6361,10 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR27" t="n">
         <v>1.28</v>
@@ -6579,7 +6579,7 @@
         <v>2.33</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.5</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.85</v>
@@ -7451,10 +7451,10 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR32" t="n">
         <v>0.87</v>
@@ -7669,7 +7669,7 @@
         <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.85</v>
@@ -7890,7 +7890,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR34" t="n">
         <v>0.85</v>
@@ -8108,7 +8108,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR35" t="n">
         <v>0.92</v>
@@ -8326,7 +8326,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR36" t="n">
         <v>0</v>
@@ -8544,7 +8544,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR37" t="n">
         <v>0.98</v>
@@ -8977,7 +8977,7 @@
         <v>1.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.5</v>
@@ -9416,7 +9416,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR41" t="n">
         <v>1.39</v>
@@ -9634,7 +9634,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR42" t="n">
         <v>1.72</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.85</v>
@@ -10503,7 +10503,7 @@
         <v>1</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.85</v>
@@ -10721,10 +10721,10 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR47" t="n">
         <v>1.61</v>
@@ -10939,10 +10939,10 @@
         <v>0.67</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR48" t="n">
         <v>1.5</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR49" t="n">
         <v>1.45</v>
@@ -11596,7 +11596,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR51" t="n">
         <v>1.07</v>
@@ -11811,10 +11811,10 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR52" t="n">
         <v>1.52</v>
@@ -12247,10 +12247,10 @@
         <v>2</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR54" t="n">
         <v>0.97</v>
@@ -12901,10 +12901,10 @@
         <v>2.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR57" t="n">
         <v>1.66</v>
@@ -13340,7 +13340,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR59" t="n">
         <v>0.97</v>
@@ -13773,7 +13773,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.08</v>
@@ -13994,7 +13994,7 @@
         <v>2</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR62" t="n">
         <v>1.66</v>
@@ -14427,7 +14427,7 @@
         <v>0.33</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.93</v>
@@ -14645,10 +14645,10 @@
         <v>0.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR65" t="n">
         <v>0.9399999999999999</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.5</v>
@@ -15299,7 +15299,7 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.85</v>
@@ -15517,10 +15517,10 @@
         <v>1.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR69" t="n">
         <v>1.47</v>
@@ -15735,7 +15735,7 @@
         <v>0.6</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.21</v>
@@ -15956,7 +15956,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR71" t="n">
         <v>1.31</v>
@@ -16389,10 +16389,10 @@
         <v>1.75</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR73" t="n">
         <v>1.64</v>
@@ -17046,7 +17046,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR76" t="n">
         <v>0</v>
@@ -17261,7 +17261,7 @@
         <v>2.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.85</v>
@@ -17482,7 +17482,7 @@
         <v>2</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR78" t="n">
         <v>1.66</v>
@@ -17697,7 +17697,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.21</v>
@@ -17915,7 +17915,7 @@
         <v>0.2</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.93</v>
@@ -18136,7 +18136,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR81" t="n">
         <v>1.04</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.85</v>
@@ -18790,7 +18790,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR84" t="n">
         <v>0.89</v>
@@ -19008,7 +19008,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR85" t="n">
         <v>1.5</v>
@@ -19226,7 +19226,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR86" t="n">
         <v>1.29</v>
@@ -19441,7 +19441,7 @@
         <v>0.8</v>
       </c>
       <c r="AP87" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.85</v>
@@ -19659,7 +19659,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.85</v>
@@ -19877,10 +19877,10 @@
         <v>0</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR89" t="n">
         <v>1.66</v>
@@ -20098,7 +20098,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR90" t="n">
         <v>1.69</v>
@@ -20313,7 +20313,7 @@
         <v>1.9</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.5</v>
@@ -20534,7 +20534,7 @@
         <v>2</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR92" t="n">
         <v>1.73</v>
@@ -21185,7 +21185,7 @@
         <v>0.67</v>
       </c>
       <c r="AP95" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.62</v>
@@ -21406,7 +21406,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR96" t="n">
         <v>1.18</v>
@@ -21624,7 +21624,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR97" t="n">
         <v>1.63</v>
@@ -21842,7 +21842,7 @@
         <v>2</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR98" t="n">
         <v>1.74</v>
@@ -22275,7 +22275,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.85</v>
@@ -22493,7 +22493,7 @@
         <v>0.86</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.21</v>
@@ -22711,7 +22711,7 @@
         <v>0.14</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.93</v>
@@ -22929,7 +22929,7 @@
         <v>0.83</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.85</v>
@@ -23150,7 +23150,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR104" t="n">
         <v>1.5</v>
@@ -23365,10 +23365,10 @@
         <v>1.57</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR105" t="n">
         <v>1.58</v>
@@ -23586,7 +23586,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR106" t="n">
         <v>1.43</v>
@@ -23804,7 +23804,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR107" t="n">
         <v>1.57</v>
@@ -24019,10 +24019,10 @@
         <v>1.83</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR108" t="n">
         <v>1.31</v>
@@ -24237,10 +24237,10 @@
         <v>0.86</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR109" t="n">
         <v>1.29</v>
@@ -25327,7 +25327,7 @@
         <v>0.5</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.93</v>
@@ -25548,7 +25548,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR115" t="n">
         <v>1.05</v>
@@ -25766,7 +25766,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR116" t="n">
         <v>1.19</v>
@@ -25981,7 +25981,7 @@
         <v>1.13</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.21</v>
@@ -26199,10 +26199,10 @@
         <v>1</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR118" t="n">
         <v>1.52</v>
@@ -26417,7 +26417,7 @@
         <v>1.57</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.85</v>
@@ -26638,7 +26638,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR120" t="n">
         <v>1.55</v>
@@ -26856,7 +26856,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR121" t="n">
         <v>1.58</v>
@@ -27071,7 +27071,7 @@
         <v>0.88</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.62</v>
@@ -27292,7 +27292,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR123" t="n">
         <v>1.18</v>
@@ -27510,7 +27510,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR124" t="n">
         <v>1.18</v>
@@ -27943,7 +27943,7 @@
         <v>1.73</v>
       </c>
       <c r="AP126" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.5</v>
@@ -28815,10 +28815,10 @@
         <v>1.33</v>
       </c>
       <c r="AP130" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR130" t="n">
         <v>1.34</v>
@@ -29033,7 +29033,7 @@
         <v>1.13</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.85</v>
@@ -29254,7 +29254,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR132" t="n">
         <v>1.14</v>
@@ -29687,10 +29687,10 @@
         <v>0.44</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR134" t="n">
         <v>1.05</v>
@@ -29908,7 +29908,7 @@
         <v>2</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR135" t="n">
         <v>1.74</v>
@@ -30559,10 +30559,10 @@
         <v>1</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR138" t="n">
         <v>1.53</v>
@@ -30777,7 +30777,7 @@
         <v>1.33</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.21</v>
@@ -30995,10 +30995,10 @@
         <v>1.13</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR140" t="n">
         <v>1.46</v>
@@ -31216,7 +31216,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR141" t="n">
         <v>1.19</v>
@@ -31870,7 +31870,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR144" t="n">
         <v>1.19</v>
@@ -32303,7 +32303,7 @@
         <v>1.2</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.21</v>
@@ -32521,10 +32521,10 @@
         <v>0.5</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR147" t="n">
         <v>1.39</v>
@@ -32739,7 +32739,7 @@
         <v>1.89</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ148" t="n">
         <v>2.08</v>
@@ -32957,10 +32957,10 @@
         <v>1.7</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR149" t="n">
         <v>1.5</v>
@@ -33393,10 +33393,10 @@
         <v>1.11</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR151" t="n">
         <v>1.37</v>
@@ -33829,7 +33829,7 @@
         <v>1.67</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.5</v>
@@ -34050,7 +34050,7 @@
         <v>2</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR154" t="n">
         <v>1.7</v>
@@ -34265,7 +34265,7 @@
         <v>1.1</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.85</v>
@@ -34483,10 +34483,10 @@
         <v>1.18</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR156" t="n">
         <v>1.41</v>
@@ -35140,7 +35140,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR159" t="n">
         <v>1.08</v>
@@ -35358,7 +35358,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR160" t="n">
         <v>1.16</v>
@@ -35573,7 +35573,7 @@
         <v>1.8</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.85</v>
@@ -36227,7 +36227,7 @@
         <v>1.91</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ164" t="n">
         <v>2.08</v>
@@ -36531,7 +36531,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>7813986</v>
+        <v>7813985</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -36544,19 +36544,19 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>45879.29166666666</v>
+        <v>45878.33333333334</v>
       </c>
       <c r="F166" t="n">
         <v>24</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -36588,160 +36588,160 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="R166" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="S166" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="T166" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="U166" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="V166" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="W166" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="X166" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y166" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP166" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Z166" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA166" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AB166" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AC166" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD166" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AE166" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF166" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AG166" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH166" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI166" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ166" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK166" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL166" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM166" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN166" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AO166" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="AP166" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AQ166" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AR166" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AS166" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AT166" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU166" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV166" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW166" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX166" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY166" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ166" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA166" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB166" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC166" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD166" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BE166" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="BF166" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG166" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BH166" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BI166" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BJ166" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BK166" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BL166" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BM166" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BN166" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BO166" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="BP166" t="n">
-        <v>1.09</v>
       </c>
     </row>
     <row r="167">
@@ -36749,7 +36749,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>7813987</v>
+        <v>7813986</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -36769,12 +36769,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -36787,38 +36787,38 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R167" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S167" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U167" t="n">
         <v>3</v>
-      </c>
-      <c r="M167" t="n">
-        <v>4</v>
-      </c>
-      <c r="N167" t="n">
-        <v>7</v>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>['49', '51', '85']</t>
-        </is>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>['57', '65', '74', '90+9']</t>
-        </is>
-      </c>
-      <c r="Q167" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R167" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S167" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T167" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U167" t="n">
-        <v>3.25</v>
       </c>
       <c r="V167" t="n">
         <v>2.63</v>
@@ -36827,139 +36827,139 @@
         <v>1.44</v>
       </c>
       <c r="X167" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z167" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AA167" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="AB167" t="n">
-        <v>3.21</v>
+        <v>3.99</v>
       </c>
       <c r="AC167" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AD167" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AE167" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK167" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AF167" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AG167" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AH167" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AI167" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ167" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK167" t="n">
-        <v>1.25</v>
       </c>
       <c r="AL167" t="n">
         <v>1.3</v>
       </c>
       <c r="AM167" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AN167" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AO167" t="n">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AS167" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="AU167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY167" t="n">
         <v>7</v>
-      </c>
-      <c r="AV167" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW167" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX167" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY167" t="n">
-        <v>17</v>
       </c>
       <c r="AZ167" t="n">
         <v>7</v>
       </c>
       <c r="BA167" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BB167" t="n">
         <v>1</v>
       </c>
       <c r="BC167" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BD167" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="BE167" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="BF167" t="n">
-        <v>3.16</v>
+        <v>3.85</v>
       </c>
       <c r="BG167" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BH167" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="BI167" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BJ167" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="BK167" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="BL167" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BM167" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="BN167" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="BO167" t="n">
-        <v>4.51</v>
+        <v>4.96</v>
       </c>
       <c r="BP167" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="168">
@@ -36967,7 +36967,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>7813990</v>
+        <v>7813987</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -36980,204 +36980,204 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>45884.29166666666</v>
+        <v>45879.29166666666</v>
       </c>
       <c r="F168" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="I168" t="n">
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M168" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N168" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49', '51', '85']</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>['10', '43']</t>
+          <t>['57', '65', '74', '90+9']</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="R168" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S168" t="n">
-        <v>2.54</v>
+        <v>4.33</v>
       </c>
       <c r="T168" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="U168" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="V168" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="W168" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X168" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="Y168" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z168" t="n">
-        <v>3.69</v>
+        <v>1.88</v>
       </c>
       <c r="AA168" t="n">
-        <v>3.27</v>
+        <v>3.63</v>
       </c>
       <c r="AB168" t="n">
-        <v>1.84</v>
+        <v>3.21</v>
       </c>
       <c r="AC168" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AD168" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE168" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AF168" t="n">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="AG168" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AH168" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AI168" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM168" t="n">
         <v>1.83</v>
       </c>
-      <c r="AJ168" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AK168" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL168" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AM168" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AN168" t="n">
-        <v>0.75</v>
+        <v>1.8</v>
       </c>
       <c r="AO168" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="AP168" t="n">
-        <v>0.64</v>
+        <v>1.85</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="AT168" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="AU168" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV168" t="n">
         <v>5</v>
       </c>
       <c r="AW168" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC168" t="n">
         <v>3</v>
       </c>
-      <c r="AY168" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ168" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA168" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB168" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC168" t="n">
-        <v>14</v>
-      </c>
       <c r="BD168" t="n">
-        <v>2.88</v>
+        <v>1.55</v>
       </c>
       <c r="BE168" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF168" t="n">
-        <v>1.56</v>
+        <v>3.16</v>
       </c>
       <c r="BG168" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BL168" t="n">
         <v>1.54</v>
       </c>
-      <c r="BH168" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BI168" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ168" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BK168" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BL168" t="n">
-        <v>1.43</v>
-      </c>
       <c r="BM168" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="BN168" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="BO168" t="n">
-        <v>5.35</v>
+        <v>4.51</v>
       </c>
       <c r="BP168" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="169">
@@ -37185,7 +37185,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>7813989</v>
+        <v>7813988</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -37198,14 +37198,14 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>45884.29166666666</v>
+        <v>45879.3125</v>
       </c>
       <c r="F169" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -37223,179 +37223,179 @@
         <v>0</v>
       </c>
       <c r="L169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
         <v>1</v>
       </c>
       <c r="N169" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>['85', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="R169" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S169" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="T169" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="U169" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="V169" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="W169" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X169" t="n">
         <v>6.5</v>
       </c>
       <c r="Y169" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z169" t="n">
-        <v>2.3</v>
+        <v>3.03</v>
       </c>
       <c r="AA169" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AB169" t="n">
-        <v>2.57</v>
+        <v>1.98</v>
       </c>
       <c r="AC169" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD169" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AE169" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF169" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="AG169" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH169" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AI169" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AJ169" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AK169" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AL169" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM169" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AN169" t="n">
-        <v>1.64</v>
+        <v>0.9</v>
       </c>
       <c r="AO169" t="n">
         <v>1.55</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.85</v>
+        <v>0.77</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AS169" t="n">
         <v>1.33</v>
       </c>
       <c r="AT169" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AU169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW169" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX169" t="n">
         <v>6</v>
       </c>
-      <c r="AX169" t="n">
-        <v>2</v>
-      </c>
       <c r="AY169" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ169" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB169" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC169" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD169" t="n">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="BE169" t="n">
-        <v>5.95</v>
+        <v>6.45</v>
       </c>
       <c r="BF169" t="n">
-        <v>2.22</v>
+        <v>1.56</v>
       </c>
       <c r="BG169" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="BH169" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="BI169" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="BJ169" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="BK169" t="n">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="BL169" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="BM169" t="n">
-        <v>3.92</v>
+        <v>3.44</v>
       </c>
       <c r="BN169" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BO169" t="n">
-        <v>6.07</v>
+        <v>5.15</v>
       </c>
       <c r="BP169" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="170">
@@ -37403,7 +37403,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>7813992</v>
+        <v>7813990</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -37416,204 +37416,204 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>45885.29166666666</v>
+        <v>45884.29166666666</v>
       </c>
       <c r="F170" t="n">
         <v>25</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L170" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N170" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>['33', '60', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['10', '43']</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R170" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S170" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="T170" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U170" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="V170" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="W170" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X170" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="Y170" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Z170" t="n">
-        <v>2.84</v>
+        <v>3.69</v>
       </c>
       <c r="AA170" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="AB170" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="AC170" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD170" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AE170" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF170" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AG170" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH170" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI170" t="n">
         <v>1.83</v>
       </c>
-      <c r="AI170" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ170" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AK170" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AL170" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AM170" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AN170" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AO170" t="n">
-        <v>2.09</v>
+        <v>1.08</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.57</v>
+        <v>0.64</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.99</v>
+        <v>2.52</v>
       </c>
       <c r="AU170" t="n">
         <v>4</v>
       </c>
       <c r="AV170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX170" t="n">
         <v>3</v>
       </c>
-      <c r="AW170" t="n">
+      <c r="AY170" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB170" t="n">
         <v>4</v>
       </c>
-      <c r="AX170" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY170" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ170" t="n">
+      <c r="BC170" t="n">
         <v>14</v>
       </c>
-      <c r="BA170" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB170" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC170" t="n">
-        <v>11</v>
-      </c>
       <c r="BD170" t="n">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="BE170" t="n">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="BF170" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="BG170" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BH170" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="BI170" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BJ170" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="BK170" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="BL170" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BM170" t="n">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="BN170" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO170" t="n">
-        <v>5.21</v>
+        <v>5.35</v>
       </c>
       <c r="BP170" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="171">
@@ -37621,7 +37621,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>7813993</v>
+        <v>7813989</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -37634,19 +37634,19 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>45885.29166666666</v>
+        <v>45884.29166666666</v>
       </c>
       <c r="F171" t="n">
         <v>25</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -37659,179 +37659,179 @@
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M171" t="n">
         <v>1</v>
       </c>
       <c r="N171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['85', '90+5']</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R171" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S171" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T171" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U171" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V171" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W171" t="n">
         <v>1.42</v>
       </c>
-      <c r="U171" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V171" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="W171" t="n">
-        <v>1.36</v>
-      </c>
       <c r="X171" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD171" t="n">
         <v>8.5</v>
       </c>
-      <c r="Y171" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z171" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA171" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AB171" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC171" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD171" t="n">
-        <v>7</v>
-      </c>
       <c r="AE171" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AF171" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="AG171" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AH171" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO171" t="n">
         <v>1.67</v>
       </c>
-      <c r="AI171" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ171" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AK171" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AL171" t="n">
+      <c r="AP171" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS171" t="n">
         <v>1.3</v>
       </c>
-      <c r="AM171" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN171" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AO171" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP171" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AQ171" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AR171" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS171" t="n">
-        <v>0.92</v>
-      </c>
       <c r="AT171" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="AU171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW171" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX171" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AY171" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ171" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC171" t="n">
         <v>9</v>
       </c>
-      <c r="BA171" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB171" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC171" t="n">
-        <v>5</v>
-      </c>
       <c r="BD171" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BE171" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="BF171" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="BG171" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="BH171" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="BI171" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BJ171" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="BK171" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="BL171" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="BM171" t="n">
-        <v>3.54</v>
+        <v>3.92</v>
       </c>
       <c r="BN171" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BO171" t="n">
-        <v>5.35</v>
+        <v>6.07</v>
       </c>
       <c r="BP171" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="172">
@@ -37839,7 +37839,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>7813995</v>
+        <v>7813992</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -37852,69 +37852,69 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>45886.29166666666</v>
+        <v>45885.29166666666</v>
       </c>
       <c r="F172" t="n">
         <v>25</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K172" t="n">
         <v>1</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M172" t="n">
         <v>1</v>
       </c>
       <c r="N172" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '60', '85']</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R172" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S172" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="T172" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U172" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V172" t="n">
         <v>2.8</v>
       </c>
       <c r="W172" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X172" t="n">
         <v>7</v>
@@ -37923,133 +37923,133 @@
         <v>1.1</v>
       </c>
       <c r="Z172" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="AA172" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="AB172" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="AC172" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD172" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AE172" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL172" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF172" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AG172" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH172" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI172" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ172" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK172" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL172" t="n">
+      <c r="AM172" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN172" t="n">
         <v>1.33</v>
       </c>
-      <c r="AM172" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN172" t="n">
-        <v>0.92</v>
-      </c>
       <c r="AO172" t="n">
-        <v>1.64</v>
+        <v>2.09</v>
       </c>
       <c r="AP172" t="n">
-        <v>0.85</v>
+        <v>1.57</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.85</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AT172" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="AU172" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV172" t="n">
         <v>3</v>
-      </c>
-      <c r="AV172" t="n">
-        <v>2</v>
       </c>
       <c r="AW172" t="n">
         <v>4</v>
       </c>
       <c r="AX172" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AY172" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB172" t="n">
         <v>7</v>
       </c>
-      <c r="AZ172" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA172" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB172" t="n">
-        <v>2</v>
-      </c>
       <c r="BC172" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="BD172" t="n">
-        <v>2.47</v>
+        <v>2.02</v>
       </c>
       <c r="BE172" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="BF172" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="BG172" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BH172" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="BI172" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="BJ172" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BK172" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="BL172" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BM172" t="n">
-        <v>3.34</v>
+        <v>3.47</v>
       </c>
       <c r="BN172" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BO172" t="n">
-        <v>4.96</v>
+        <v>5.21</v>
       </c>
       <c r="BP172" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="173">
@@ -38057,7 +38057,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>7813998</v>
+        <v>7813993</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -38070,19 +38070,19 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>45892.29166666666</v>
+        <v>45885.29166666666</v>
       </c>
       <c r="F173" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="I173" t="n">
@@ -38105,139 +38105,139 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R173" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S173" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="T173" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="U173" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V173" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="W173" t="n">
         <v>1.36</v>
       </c>
       <c r="X173" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Y173" t="n">
         <v>1.07</v>
       </c>
       <c r="Z173" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="AA173" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="AB173" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="AC173" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AD173" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ173" t="n">
         <v>9</v>
       </c>
-      <c r="AE173" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF173" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG173" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH173" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI173" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ173" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK173" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL173" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM173" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN173" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AO173" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AP173" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AQ173" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR173" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AS173" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AT173" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AU173" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV173" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW173" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX173" t="n">
+      <c r="BA173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC173" t="n">
         <v>5</v>
       </c>
-      <c r="AY173" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ173" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA173" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB173" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC173" t="n">
-        <v>4</v>
-      </c>
       <c r="BD173" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="BE173" t="n">
-        <v>7.22</v>
+        <v>5.9</v>
       </c>
       <c r="BF173" t="n">
-        <v>3.3</v>
+        <v>2.31</v>
       </c>
       <c r="BG173" t="n">
         <v>1.54</v>
@@ -38252,7 +38252,7 @@
         <v>1.8</v>
       </c>
       <c r="BK173" t="n">
-        <v>3.19</v>
+        <v>2.53</v>
       </c>
       <c r="BL173" t="n">
         <v>1.43</v>
@@ -38275,7 +38275,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>7813999</v>
+        <v>7813994</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -38288,204 +38288,204 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>45892.29166666666</v>
+        <v>45885.3125</v>
       </c>
       <c r="F174" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M174" t="n">
         <v>1</v>
       </c>
       <c r="N174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>['45', '49']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="Q174" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R174" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S174" t="n">
         <v>2.4</v>
       </c>
-      <c r="R174" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S174" t="n">
-        <v>4.2</v>
-      </c>
       <c r="T174" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="U174" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V174" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="W174" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X174" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Y174" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z174" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA174" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="AB174" t="n">
-        <v>3.51</v>
+        <v>1.82</v>
       </c>
       <c r="AC174" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AD174" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AE174" t="n">
         <v>1.25</v>
       </c>
       <c r="AF174" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AG174" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK174" t="n">
         <v>1.85</v>
       </c>
-      <c r="AH174" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI174" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ174" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK174" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AL174" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AM174" t="n">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AN174" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AO174" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.62</v>
+        <v>1.31</v>
       </c>
       <c r="AR174" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="AS174" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="AU174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV174" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW174" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AX174" t="n">
         <v>8</v>
       </c>
       <c r="AY174" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AZ174" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB174" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BC174" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD174" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF174" t="n">
         <v>1.54</v>
       </c>
-      <c r="BE174" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BF174" t="n">
-        <v>3.39</v>
-      </c>
       <c r="BG174" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="BH174" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="BI174" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="BJ174" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="BK174" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="BL174" t="n">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="BM174" t="n">
-        <v>2.66</v>
+        <v>3.47</v>
       </c>
       <c r="BN174" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="BO174" t="n">
-        <v>3.71</v>
+        <v>5.21</v>
       </c>
       <c r="BP174" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="175">
@@ -38493,7 +38493,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>7813996</v>
+        <v>7813991</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -38506,204 +38506,204 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>45892.29166666666</v>
+        <v>45885.33333333334</v>
       </c>
       <c r="F175" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="I175" t="n">
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>['57', '90+2']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '34']</t>
         </is>
       </c>
       <c r="Q175" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R175" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S175" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U175" t="n">
         <v>2.4</v>
       </c>
-      <c r="R175" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S175" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T175" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U175" t="n">
-        <v>2.9</v>
-      </c>
       <c r="V175" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="W175" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="X175" t="n">
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="Y175" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC175" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z175" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA175" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB175" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AC175" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AD175" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="AE175" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK175" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF175" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG175" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH175" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI175" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ175" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK175" t="n">
+      <c r="AL175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS175" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL175" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM175" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN175" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO175" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AP175" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ175" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AR175" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS175" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="AT175" t="n">
-        <v>2.43</v>
+        <v>2.71</v>
       </c>
       <c r="AU175" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV175" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW175" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX175" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY175" t="n">
         <v>8</v>
-      </c>
-      <c r="AY175" t="n">
-        <v>12</v>
       </c>
       <c r="AZ175" t="n">
         <v>8</v>
       </c>
       <c r="BA175" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB175" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BC175" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD175" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BE175" t="n">
-        <v>7.6</v>
+        <v>7.38</v>
       </c>
       <c r="BF175" t="n">
-        <v>4.11</v>
+        <v>3.63</v>
       </c>
       <c r="BG175" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BH175" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="BI175" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="BJ175" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BK175" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="BL175" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="BM175" t="n">
-        <v>4.32</v>
+        <v>3.78</v>
       </c>
       <c r="BN175" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BO175" t="n">
-        <v>6.85</v>
+        <v>5.47</v>
       </c>
       <c r="BP175" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="176">
@@ -38711,7 +38711,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>7814000</v>
+        <v>7813995</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -38724,38 +38724,38 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>45893.29166666666</v>
+        <v>45886.29166666666</v>
       </c>
       <c r="F176" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N176" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -38764,164 +38764,164 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>['18', '40', '55', '88']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="R176" t="n">
         <v>2.15</v>
       </c>
       <c r="S176" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="T176" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="U176" t="n">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="V176" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="W176" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X176" t="n">
         <v>7</v>
       </c>
       <c r="Y176" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z176" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="AA176" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="AB176" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO176" t="n">
         <v>1.64</v>
       </c>
-      <c r="AC176" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD176" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE176" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF176" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AG176" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH176" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI176" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ176" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK176" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL176" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM176" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN176" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AO176" t="n">
-        <v>2</v>
-      </c>
       <c r="AP176" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ176" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AT176" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH176" t="n">
         <v>2.38</v>
       </c>
-      <c r="AU176" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV176" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW176" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX176" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY176" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ176" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA176" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB176" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC176" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD176" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BE176" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="BF176" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BG176" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BH176" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BI176" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="BJ176" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="BK176" t="n">
-        <v>2.77</v>
+        <v>2.42</v>
       </c>
       <c r="BL176" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="BM176" t="n">
-        <v>3.99</v>
+        <v>3.34</v>
       </c>
       <c r="BN176" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BO176" t="n">
-        <v>6.21</v>
+        <v>4.96</v>
       </c>
       <c r="BP176" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="177">
@@ -38929,7 +38929,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>7814001</v>
+        <v>7813998</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -38942,19 +38942,19 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>45893.29166666666</v>
+        <v>45892.29166666666</v>
       </c>
       <c r="F177" t="n">
         <v>26</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -38967,62 +38967,62 @@
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
         <v>1</v>
       </c>
       <c r="N177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R177" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S177" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="T177" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U177" t="n">
         <v>2.8</v>
       </c>
       <c r="V177" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="W177" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X177" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Y177" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC177" t="n">
         <v>1.03</v>
-      </c>
-      <c r="Z177" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA177" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AB177" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AC177" t="n">
-        <v>1.06</v>
       </c>
       <c r="AD177" t="n">
         <v>9</v>
@@ -39040,76 +39040,76 @@
         <v>1.75</v>
       </c>
       <c r="AI177" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AJ177" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AK177" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL177" t="n">
         <v>1.33</v>
       </c>
       <c r="AM177" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AN177" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AO177" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="AS177" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AT177" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AU177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV177" t="n">
         <v>3</v>
       </c>
-      <c r="AV177" t="n">
-        <v>6</v>
-      </c>
       <c r="AW177" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX177" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY177" t="n">
         <v>9</v>
       </c>
       <c r="AZ177" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA177" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BB177" t="n">
         <v>1</v>
       </c>
       <c r="BC177" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BD177" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="BE177" t="n">
-        <v>7</v>
+        <v>7.22</v>
       </c>
       <c r="BF177" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="BG177" t="n">
         <v>1.54</v>
@@ -39147,7 +39147,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>7814002</v>
+        <v>7813999</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -39160,84 +39160,84 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>45893.29166666666</v>
+        <v>45892.29166666666</v>
       </c>
       <c r="F178" t="n">
         <v>26</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="I178" t="n">
         <v>1</v>
       </c>
       <c r="J178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M178" t="n">
         <v>1</v>
       </c>
       <c r="N178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['45', '49']</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>4.94</v>
+        <v>2.4</v>
       </c>
       <c r="R178" t="n">
         <v>2.25</v>
       </c>
       <c r="S178" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="T178" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U178" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="V178" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="W178" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X178" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y178" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z178" t="n">
-        <v>3.95</v>
+        <v>1.85</v>
       </c>
       <c r="AA178" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.71</v>
+        <v>3.51</v>
       </c>
       <c r="AC178" t="n">
         <v>1.02</v>
@@ -39246,10 +39246,10 @@
         <v>10</v>
       </c>
       <c r="AE178" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF178" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AG178" t="n">
         <v>1.85</v>
@@ -39258,106 +39258,106 @@
         <v>1.85</v>
       </c>
       <c r="AI178" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AJ178" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AK178" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL178" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AM178" t="n">
-        <v>1.2</v>
+        <v>1.91</v>
       </c>
       <c r="AN178" t="n">
         <v>1.25</v>
       </c>
       <c r="AO178" t="n">
-        <v>1.92</v>
+        <v>0.67</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.85</v>
+        <v>0.62</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AS178" t="n">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AT178" t="n">
-        <v>2.61</v>
+        <v>2.1</v>
       </c>
       <c r="AU178" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW178" t="n">
         <v>7</v>
       </c>
-      <c r="AW178" t="n">
-        <v>5</v>
-      </c>
       <c r="AX178" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY178" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ178" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA178" t="n">
         <v>4</v>
       </c>
       <c r="BB178" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BC178" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BD178" t="n">
-        <v>2.97</v>
+        <v>1.54</v>
       </c>
       <c r="BE178" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="BF178" t="n">
-        <v>1.66</v>
+        <v>3.39</v>
       </c>
       <c r="BG178" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BH178" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BI178" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="BJ178" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="BK178" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="BL178" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="BM178" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="BN178" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="BO178" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="BP178" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="179">
@@ -39365,7 +39365,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>7814003</v>
+        <v>7813996</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -39378,19 +39378,19 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>45899.29166666666</v>
+        <v>45892.29166666666</v>
       </c>
       <c r="F179" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="I179" t="n">
@@ -39403,179 +39403,179 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
         <v>2</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['57', '90+2']</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R179" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S179" t="n">
-        <v>5.16</v>
+        <v>4.4</v>
       </c>
       <c r="T179" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U179" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V179" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W179" t="n">
         <v>1.4</v>
       </c>
-      <c r="U179" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="V179" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W179" t="n">
-        <v>1.36</v>
-      </c>
       <c r="X179" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y179" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z179" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AA179" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AB179" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AC179" t="n">
         <v>1.02</v>
       </c>
       <c r="AD179" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="AE179" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF179" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AG179" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AH179" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN179" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI179" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ179" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK179" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AL179" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AM179" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AN179" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AO179" t="n">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AP179" t="n">
-        <v>2.69</v>
+        <v>1.85</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.21</v>
+        <v>0.85</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AS179" t="n">
-        <v>1.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT179" t="n">
-        <v>2.82</v>
+        <v>2.43</v>
       </c>
       <c r="AU179" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW179" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX179" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY179" t="n">
         <v>12</v>
       </c>
       <c r="AZ179" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA179" t="n">
         <v>5</v>
       </c>
-      <c r="BA179" t="n">
-        <v>3</v>
-      </c>
       <c r="BB179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC179" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BD179" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="BE179" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="BF179" t="n">
-        <v>2.7</v>
+        <v>4.11</v>
       </c>
       <c r="BG179" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="BH179" t="n">
-        <v>2.52</v>
+        <v>2.03</v>
       </c>
       <c r="BI179" t="n">
-        <v>1.82</v>
+        <v>2.17</v>
       </c>
       <c r="BJ179" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="BK179" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="BL179" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="BM179" t="n">
-        <v>3.1</v>
+        <v>4.32</v>
       </c>
       <c r="BN179" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="BO179" t="n">
-        <v>4.51</v>
+        <v>6.85</v>
       </c>
       <c r="BP179" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="180">
@@ -39583,7 +39583,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>7814004</v>
+        <v>7813997</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -39596,66 +39596,66 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>45899.29166666666</v>
+        <v>45892.3125</v>
       </c>
       <c r="F180" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R180" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S180" t="n">
         <v>4</v>
       </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>['90+7', '90+9']</t>
-        </is>
-      </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>['6', '90']</t>
-        </is>
-      </c>
-      <c r="Q180" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R180" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="S180" t="n">
-        <v>4.19</v>
-      </c>
       <c r="T180" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="U180" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="V180" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="W180" t="n">
         <v>1.44</v>
@@ -39664,37 +39664,37 @@
         <v>6.5</v>
       </c>
       <c r="Y180" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z180" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AA180" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="AB180" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AC180" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD180" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="AE180" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF180" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AG180" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AH180" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AI180" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AJ180" t="n">
         <v>2.05</v>
@@ -39703,97 +39703,97 @@
         <v>1.25</v>
       </c>
       <c r="AL180" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AM180" t="n">
         <v>1.85</v>
       </c>
       <c r="AN180" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AO180" t="n">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP180" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.31</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.87</v>
+        <v>2.42</v>
       </c>
       <c r="AU180" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV180" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AW180" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AX180" t="n">
         <v>5</v>
       </c>
       <c r="AY180" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AZ180" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA180" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB180" t="n">
         <v>4</v>
       </c>
       <c r="BC180" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD180" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BE180" t="n">
-        <v>8.1</v>
+        <v>7.55</v>
       </c>
       <c r="BF180" t="n">
-        <v>2.83</v>
+        <v>3.45</v>
       </c>
       <c r="BG180" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="BH180" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="BI180" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BJ180" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="BK180" t="n">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="BL180" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BM180" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="BN180" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="BO180" t="n">
-        <v>4.16</v>
+        <v>3.92</v>
       </c>
       <c r="BP180" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="181">
@@ -39801,7 +39801,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>7814005</v>
+        <v>7814000</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -39814,38 +39814,38 @@
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>45899.29166666666</v>
+        <v>45893.29166666666</v>
       </c>
       <c r="F181" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -39854,164 +39854,164 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['18', '40', '55', '88']</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>3.46</v>
+        <v>5</v>
       </c>
       <c r="R181" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S181" t="n">
-        <v>3.38</v>
+        <v>2.2</v>
       </c>
       <c r="T181" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="U181" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="V181" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="W181" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X181" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="Y181" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS181" t="n">
         <v>1.01</v>
       </c>
-      <c r="Z181" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA181" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB181" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AC181" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD181" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE181" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF181" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AG181" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AH181" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI181" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ181" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AK181" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AL181" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AM181" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN181" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AO181" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="AP181" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AQ181" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AR181" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AS181" t="n">
-        <v>0.92</v>
-      </c>
       <c r="AT181" t="n">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
       <c r="AU181" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AV181" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AW181" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY181" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ181" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BA181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BC181" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BD181" t="n">
-        <v>1.94</v>
+        <v>2.95</v>
       </c>
       <c r="BE181" t="n">
-        <v>5.9</v>
+        <v>6.86</v>
       </c>
       <c r="BF181" t="n">
-        <v>2.31</v>
+        <v>1.69</v>
       </c>
       <c r="BG181" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="BH181" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="BI181" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ181" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BK181" t="n">
-        <v>3.41</v>
+        <v>2.77</v>
       </c>
       <c r="BL181" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="BM181" t="n">
-        <v>3.78</v>
+        <v>3.99</v>
       </c>
       <c r="BN181" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BO181" t="n">
-        <v>5.79</v>
+        <v>6.21</v>
       </c>
       <c r="BP181" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="182">
@@ -40019,7 +40019,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>7814006</v>
+        <v>7814001</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -40032,204 +40032,1512 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>45899.29166666666</v>
+        <v>45893.29166666666</v>
       </c>
       <c r="F182" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>['44', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R182" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S182" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="T182" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U182" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V182" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W182" t="n">
         <v>1.42</v>
       </c>
-      <c r="U182" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V182" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W182" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X182" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="Y182" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z182" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AA182" t="n">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="AB182" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="AC182" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AD182" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AE182" t="n">
         <v>1.29</v>
       </c>
       <c r="AF182" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="AG182" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH182" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AI182" t="n">
         <v>1.75</v>
       </c>
       <c r="AJ182" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AK182" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL182" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AM182" t="n">
         <v>1.48</v>
       </c>
       <c r="AN182" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB182" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF182" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG182" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BH182" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI182" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ182" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK182" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BL182" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM182" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BN182" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO182" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BP182" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="n">
+        <v>7814002</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>45893.29166666666</v>
+      </c>
+      <c r="F183" t="n">
+        <v>26</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Hwaseong</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Suwon Bluewings</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>1</v>
+      </c>
+      <c r="L183" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" t="n">
+        <v>1</v>
+      </c>
+      <c r="N183" t="n">
+        <v>2</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="R183" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S183" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T183" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U183" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V183" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W183" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X183" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BM183" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BN183" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BO183" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP183" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="n">
+        <v>7814003</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>45899.29166666666</v>
+      </c>
+      <c r="F184" t="n">
+        <v>27</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Asan Mugunghwa</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>1</v>
+      </c>
+      <c r="N184" t="n">
+        <v>2</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R184" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S184" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="T184" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U184" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V184" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W184" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X184" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BO184" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="BP184" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="n">
+        <v>7814004</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>45899.29166666666</v>
+      </c>
+      <c r="F185" t="n">
+        <v>27</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Suwon Bluewings</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Seongnam</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="n">
+        <v>1</v>
+      </c>
+      <c r="L185" t="n">
+        <v>2</v>
+      </c>
+      <c r="M185" t="n">
+        <v>2</v>
+      </c>
+      <c r="N185" t="n">
+        <v>4</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>['90+7', '90+9']</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>['6', '90']</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R185" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S185" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="T185" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U185" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="V185" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W185" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X185" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO185" t="n">
         <v>1.46</v>
       </c>
-      <c r="AO182" t="n">
+      <c r="AP185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB185" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF185" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BG185" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BH185" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BI185" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK185" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BL185" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BM185" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN185" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO185" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="BP185" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="n">
+        <v>7814005</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>45899.29166666666</v>
+      </c>
+      <c r="F186" t="n">
+        <v>27</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Hwaseong</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" t="n">
+        <v>1</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>1</v>
+      </c>
+      <c r="N186" t="n">
+        <v>1</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R186" t="n">
+        <v>2</v>
+      </c>
+      <c r="S186" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T186" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U186" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V186" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W186" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X186" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AU186" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA186" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC186" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE186" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF186" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG186" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BH186" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BI186" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BJ186" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BK186" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="BL186" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BM186" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BN186" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BO186" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="BP186" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>7814006</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>45899.29166666666</v>
+      </c>
+      <c r="F187" t="n">
+        <v>27</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Jeonnam Dragons</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>1</v>
+      </c>
+      <c r="L187" t="n">
+        <v>2</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>2</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>['44', '82']</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R187" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S187" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T187" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U187" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V187" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W187" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X187" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO187" t="n">
         <v>1.62</v>
       </c>
-      <c r="AP182" t="n">
+      <c r="AP187" t="n">
         <v>1.57</v>
       </c>
-      <c r="AQ182" t="n">
+      <c r="AQ187" t="n">
         <v>1.5</v>
       </c>
-      <c r="AR182" t="n">
+      <c r="AR187" t="n">
         <v>1.43</v>
       </c>
-      <c r="AS182" t="n">
+      <c r="AS187" t="n">
         <v>1.12</v>
       </c>
-      <c r="AT182" t="n">
+      <c r="AT187" t="n">
         <v>2.55</v>
       </c>
-      <c r="AU182" t="n">
+      <c r="AU187" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX187" t="n">
         <v>5</v>
       </c>
-      <c r="AV182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW182" t="n">
+      <c r="AY187" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB187" t="n">
         <v>9</v>
       </c>
-      <c r="AX182" t="n">
+      <c r="BC187" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF187" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BG187" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BH187" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BI187" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BJ187" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BK187" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BL187" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BM187" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="BN187" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BO187" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="BP187" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>7814008</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>45899.29166666666</v>
+      </c>
+      <c r="F188" t="n">
+        <v>27</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Busan I'Park</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Cheongju</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1</v>
+      </c>
+      <c r="L188" t="n">
+        <v>2</v>
+      </c>
+      <c r="M188" t="n">
+        <v>2</v>
+      </c>
+      <c r="N188" t="n">
+        <v>4</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>['45+3', '61']</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>['58', '68']</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R188" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S188" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T188" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U188" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V188" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W188" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X188" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU188" t="n">
         <v>5</v>
       </c>
-      <c r="AY182" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ182" t="n">
+      <c r="AV188" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB188" t="n">
         <v>5</v>
       </c>
-      <c r="BA182" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB182" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC182" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD182" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BE182" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="BF182" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BG182" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BH182" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BI182" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BJ182" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BK182" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BL182" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BM182" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="BN182" t="n">
+      <c r="BC188" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF188" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="BG188" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BI188" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BJ188" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BK188" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BL188" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM188" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BN188" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO188" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="BP188" t="n">
         <v>1.16</v>
-      </c>
-      <c r="BO182" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="BP182" t="n">
-        <v>1.04</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -41447,7 +41447,7 @@
         <v>1.26</v>
       </c>
       <c r="AL188" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AM188" t="n">
         <v>2.21</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP188"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.5</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -5053,7 +5053,7 @@
         <v>0.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.21</v>
@@ -5492,7 +5492,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR23" t="n">
         <v>1.8</v>
@@ -6579,7 +6579,7 @@
         <v>2.33</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.5</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.07</v>
@@ -7887,7 +7887,7 @@
         <v>2</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.38</v>
@@ -8108,7 +8108,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR35" t="n">
         <v>0.92</v>
@@ -9416,7 +9416,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR41" t="n">
         <v>1.39</v>
@@ -10721,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.43</v>
@@ -11160,7 +11160,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR49" t="n">
         <v>1.45</v>
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.85</v>
@@ -12250,7 +12250,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR54" t="n">
         <v>0.97</v>
@@ -12901,7 +12901,7 @@
         <v>2.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.38</v>
@@ -13337,7 +13337,7 @@
         <v>0.88</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.07</v>
@@ -14648,7 +14648,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR65" t="n">
         <v>0.9399999999999999</v>
@@ -16389,10 +16389,10 @@
         <v>1.75</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR73" t="n">
         <v>1.64</v>
@@ -17697,7 +17697,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.21</v>
@@ -18133,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="AP81" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.43</v>
@@ -19008,7 +19008,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR85" t="n">
         <v>1.5</v>
@@ -19226,7 +19226,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR86" t="n">
         <v>1.29</v>
@@ -19877,7 +19877,7 @@
         <v>0</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.6899999999999999</v>
@@ -20098,7 +20098,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR90" t="n">
         <v>1.69</v>
@@ -21842,7 +21842,7 @@
         <v>2</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR98" t="n">
         <v>1.74</v>
@@ -22057,7 +22057,7 @@
         <v>2.4</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ99" t="n">
         <v>2.08</v>
@@ -22711,7 +22711,7 @@
         <v>0.14</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.93</v>
@@ -23150,7 +23150,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR104" t="n">
         <v>1.5</v>
@@ -23368,7 +23368,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR105" t="n">
         <v>1.58</v>
@@ -24022,7 +24022,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR108" t="n">
         <v>1.31</v>
@@ -25545,10 +25545,10 @@
         <v>1.57</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR115" t="n">
         <v>1.05</v>
@@ -25766,7 +25766,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR116" t="n">
         <v>1.19</v>
@@ -26417,7 +26417,7 @@
         <v>1.57</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.85</v>
@@ -26856,7 +26856,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR121" t="n">
         <v>1.58</v>
@@ -28818,7 +28818,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR130" t="n">
         <v>1.34</v>
@@ -29033,7 +29033,7 @@
         <v>1.13</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.85</v>
@@ -29254,7 +29254,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR132" t="n">
         <v>1.14</v>
@@ -30123,7 +30123,7 @@
         <v>0.44</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.93</v>
@@ -31216,7 +31216,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR141" t="n">
         <v>1.19</v>
@@ -32739,7 +32739,7 @@
         <v>1.89</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ148" t="n">
         <v>2.08</v>
@@ -32960,7 +32960,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR149" t="n">
         <v>1.5</v>
@@ -33175,7 +33175,7 @@
         <v>0.7</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.62</v>
@@ -34050,7 +34050,7 @@
         <v>2</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR154" t="n">
         <v>1.7</v>
@@ -35573,7 +35573,7 @@
         <v>1.8</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.85</v>
@@ -35791,7 +35791,7 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.85</v>
@@ -37320,7 +37320,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR169" t="n">
         <v>1.38</v>
@@ -37756,7 +37756,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR171" t="n">
         <v>1.52</v>
@@ -38407,10 +38407,10 @@
         <v>1.33</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR174" t="n">
         <v>1.39</v>
@@ -38843,7 +38843,7 @@
         <v>1.64</v>
       </c>
       <c r="AP176" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.85</v>
@@ -41538,6 +41538,442 @@
       </c>
       <c r="BP188" t="n">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>7814009</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F189" t="n">
+        <v>27</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" t="n">
+        <v>3</v>
+      </c>
+      <c r="L189" t="n">
+        <v>2</v>
+      </c>
+      <c r="M189" t="n">
+        <v>5</v>
+      </c>
+      <c r="N189" t="n">
+        <v>7</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>['57', '82']</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>['5', '15', '44', '84', '90+5']</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R189" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S189" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T189" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U189" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="V189" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W189" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X189" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="BF189" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BG189" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BI189" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BK189" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BL189" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BM189" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BN189" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BO189" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="BP189" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>7814007</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F190" t="n">
+        <v>27</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gyeongnam</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="n">
+        <v>1</v>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="n">
+        <v>2</v>
+      </c>
+      <c r="N190" t="n">
+        <v>3</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>['37', '60']</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R190" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S190" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T190" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U190" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V190" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="W190" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X190" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BK190" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BL190" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BM190" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BN190" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BO190" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="BP190" t="n">
+        <v>1.05</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -41038,19 +41038,19 @@
         <v>2.11</v>
       </c>
       <c r="AU186" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV186" t="n">
         <v>2</v>
       </c>
       <c r="AW186" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX186" t="n">
         <v>3</v>
       </c>
       <c r="AY186" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ186" t="n">
         <v>5</v>
@@ -41474,13 +41474,13 @@
         <v>2.59</v>
       </c>
       <c r="AU188" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV188" t="n">
         <v>3</v>
       </c>
       <c r="AW188" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX188" t="n">
         <v>6</v>
@@ -41665,7 +41665,7 @@
         <v>1.3</v>
       </c>
       <c r="AL189" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM189" t="n">
         <v>1.29</v>
@@ -41883,7 +41883,7 @@
         <v>1.29</v>
       </c>
       <c r="AL190" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM190" t="n">
         <v>1.29</v>
@@ -41910,22 +41910,22 @@
         <v>2.67</v>
       </c>
       <c r="AU190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV190" t="n">
         <v>6</v>
       </c>
       <c r="AW190" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX190" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY190" t="n">
         <v>15</v>
       </c>
       <c r="AZ190" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA190" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -40820,16 +40820,16 @@
         <v>2.88</v>
       </c>
       <c r="AU185" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV185" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW185" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX185" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY185" t="n">
         <v>16</v>
@@ -41038,13 +41038,13 @@
         <v>2.11</v>
       </c>
       <c r="AU186" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV186" t="n">
         <v>2</v>
       </c>
       <c r="AW186" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX186" t="n">
         <v>3</v>
@@ -41256,13 +41256,13 @@
         <v>2.55</v>
       </c>
       <c r="AU187" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV187" t="n">
         <v>0</v>
       </c>
       <c r="AW187" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX187" t="n">
         <v>5</v>
@@ -41474,13 +41474,13 @@
         <v>2.59</v>
       </c>
       <c r="AU188" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV188" t="n">
         <v>3</v>
       </c>
       <c r="AW188" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX188" t="n">
         <v>6</v>
@@ -41910,13 +41910,13 @@
         <v>2.67</v>
       </c>
       <c r="AU190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV190" t="n">
         <v>6</v>
       </c>
       <c r="AW190" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX190" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -40820,16 +40820,16 @@
         <v>2.88</v>
       </c>
       <c r="AU185" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV185" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW185" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX185" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY185" t="n">
         <v>16</v>
@@ -41038,13 +41038,13 @@
         <v>2.11</v>
       </c>
       <c r="AU186" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV186" t="n">
         <v>2</v>
       </c>
       <c r="AW186" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX186" t="n">
         <v>3</v>
@@ -41256,13 +41256,13 @@
         <v>2.55</v>
       </c>
       <c r="AU187" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV187" t="n">
         <v>0</v>
       </c>
       <c r="AW187" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX187" t="n">
         <v>5</v>
@@ -41474,13 +41474,13 @@
         <v>2.59</v>
       </c>
       <c r="AU188" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV188" t="n">
         <v>3</v>
       </c>
       <c r="AW188" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX188" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -41910,13 +41910,13 @@
         <v>2.67</v>
       </c>
       <c r="AU190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV190" t="n">
         <v>6</v>
       </c>
       <c r="AW190" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX190" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -41910,13 +41910,13 @@
         <v>2.67</v>
       </c>
       <c r="AU190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV190" t="n">
         <v>6</v>
       </c>
       <c r="AW190" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX190" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>3</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR9" t="n">
         <v>2.45</v>
@@ -2655,10 +2655,10 @@
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR10" t="n">
         <v>0.6899999999999999</v>
@@ -2873,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR11" t="n">
         <v>0.91</v>
@@ -3091,19 +3091,19 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AS12" t="n">
         <v>0.79</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.79</v>
+        <v>1.46</v>
       </c>
       <c r="AU12" t="n">
         <v>5</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR13" t="n">
         <v>1.27</v>
@@ -3524,22 +3524,22 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>2.49</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR15" t="n">
         <v>0.6899999999999999</v>
@@ -3960,22 +3960,22 @@
         <v>3</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.48</v>
+        <v>2.79</v>
       </c>
       <c r="AU16" t="n">
         <v>1</v>
@@ -4175,25 +4175,25 @@
         <v>1.57</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
         <v>0.79</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="AU17" t="n">
         <v>3</v>
@@ -4399,10 +4399,10 @@
         <v>2</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR18" t="n">
         <v>1.16</v>
@@ -4611,25 +4611,25 @@
         <v>1.71</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO19" t="n">
         <v>0.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS19" t="n">
         <v>0.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="AU19" t="n">
         <v>8</v>
@@ -4835,10 +4835,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR20" t="n">
         <v>0.93</v>
@@ -5053,10 +5053,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR21" t="n">
         <v>0.89</v>
@@ -5268,22 +5268,22 @@
         <v>2</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR22" t="n">
         <v>0.79</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.79</v>
+        <v>2.59</v>
       </c>
       <c r="AU22" t="n">
         <v>4</v>
@@ -5483,25 +5483,25 @@
         <v>1.7</v>
       </c>
       <c r="AN23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="AU23" t="n">
         <v>1</v>
@@ -5701,25 +5701,25 @@
         <v>1.61</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO24" t="n">
         <v>1.33</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AS24" t="n">
         <v>0.73</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AU24" t="n">
         <v>8</v>
@@ -5919,25 +5919,25 @@
         <v>1.8</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.94</v>
+        <v>1.51</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="AU25" t="n">
         <v>2</v>
@@ -6137,25 +6137,25 @@
         <v>1.75</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO26" t="n">
         <v>0.33</v>
       </c>
       <c r="AP26" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS26" t="n">
         <v>1.32</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.32</v>
+        <v>2.87</v>
       </c>
       <c r="AU26" t="n">
         <v>1</v>
@@ -6355,25 +6355,25 @@
         <v>2.2</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.28</v>
+        <v>1.99</v>
       </c>
       <c r="AU27" t="n">
         <v>7</v>
@@ -6573,25 +6573,25 @@
         <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO28" t="n">
         <v>2.33</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS28" t="n">
         <v>1.16</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.16</v>
+        <v>2.1</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -6791,25 +6791,25 @@
         <v>2.15</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS29" t="n">
         <v>1.09</v>
       </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
       <c r="AT29" t="n">
-        <v>1.09</v>
+        <v>2.33</v>
       </c>
       <c r="AU29" t="n">
         <v>4</v>
@@ -7012,22 +7012,22 @@
         <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.67</v>
+        <v>1.28</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.76</v>
+        <v>2.27</v>
       </c>
       <c r="AU30" t="n">
         <v>6</v>
@@ -7233,19 +7233,19 @@
         <v>2</v>
       </c>
       <c r="AP31" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="AS31" t="n">
         <v>1.12</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.16</v>
+        <v>2.54</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -7445,25 +7445,25 @@
         <v>1.53</v>
       </c>
       <c r="AN32" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO32" t="n">
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="AS32" t="n">
         <v>0.98</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AU32" t="n">
         <v>8</v>
@@ -7663,25 +7663,25 @@
         <v>1.61</v>
       </c>
       <c r="AN33" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO33" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.84</v>
+        <v>1.31</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="AU33" t="n">
         <v>1</v>
@@ -7881,25 +7881,25 @@
         <v>1.29</v>
       </c>
       <c r="AN34" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO34" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AU34" t="n">
         <v>2</v>
@@ -8099,25 +8099,25 @@
         <v>1.57</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AO35" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="AU35" t="n">
         <v>4</v>
@@ -8317,25 +8317,25 @@
         <v>1.88</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.72</v>
+        <v>2.05</v>
       </c>
       <c r="AU36" t="n">
         <v>7</v>
@@ -8535,25 +8535,25 @@
         <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.38</v>
+        <v>0.78</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AU37" t="n">
         <v>6</v>
@@ -8753,25 +8753,25 @@
         <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="AU38" t="n">
         <v>3</v>
@@ -8971,25 +8971,25 @@
         <v>1.55</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AO39" t="n">
         <v>1.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AS39" t="n">
         <v>1.22</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="AU39" t="n">
         <v>4</v>
@@ -9189,25 +9189,25 @@
         <v>2.2</v>
       </c>
       <c r="AN40" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AP40" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="AU40" t="n">
         <v>7</v>
@@ -9407,25 +9407,25 @@
         <v>1.44</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="AO41" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="AU41" t="n">
         <v>4</v>
@@ -9625,25 +9625,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AO42" t="n">
         <v>0.8</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="AS42" t="n">
         <v>0.99</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="AU42" t="n">
         <v>6</v>
@@ -9843,25 +9843,25 @@
         <v>1.67</v>
       </c>
       <c r="AN43" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AU43" t="n">
         <v>3</v>
@@ -10061,25 +10061,25 @@
         <v>1.44</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.33</v>
+        <v>1.33</v>
       </c>
       <c r="AO44" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.49</v>
+        <v>2.68</v>
       </c>
       <c r="AU44" t="n">
         <v>5</v>
@@ -10279,25 +10279,25 @@
         <v>1.36</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO45" t="n">
         <v>1.83</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AS45" t="n">
         <v>1.2</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AU45" t="n">
         <v>4</v>
@@ -10500,22 +10500,22 @@
         <v>2</v>
       </c>
       <c r="AO46" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AU46" t="n">
         <v>5</v>
@@ -10715,25 +10715,25 @@
         <v>1.65</v>
       </c>
       <c r="AN47" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.61</v>
+        <v>1.21</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="AU47" t="n">
         <v>3</v>
@@ -10933,25 +10933,25 @@
         <v>2.38</v>
       </c>
       <c r="AN48" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AO48" t="n">
         <v>0.67</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AS48" t="n">
         <v>1.06</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AU48" t="n">
         <v>5</v>
@@ -11151,25 +11151,25 @@
         <v>1.55</v>
       </c>
       <c r="AN49" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.37</v>
+        <v>0.95</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.82</v>
+        <v>2.22</v>
       </c>
       <c r="AU49" t="n">
         <v>8</v>
@@ -11369,25 +11369,25 @@
         <v>1.67</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AO50" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.83</v>
+        <v>1.07</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AU50" t="n">
         <v>2</v>
@@ -11587,16 +11587,16 @@
         <v>2.2</v>
       </c>
       <c r="AN51" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AO51" t="n">
         <v>0.57</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR51" t="n">
         <v>1.07</v>
@@ -11805,25 +11805,25 @@
         <v>2.7</v>
       </c>
       <c r="AN52" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AO52" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AS52" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AU52" t="n">
         <v>5</v>
@@ -12023,25 +12023,25 @@
         <v>2.3</v>
       </c>
       <c r="AN53" t="n">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO53" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AP53" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AS53" t="n">
-        <v>0.89</v>
+        <v>1.19</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AU53" t="n">
         <v>6</v>
@@ -12241,25 +12241,25 @@
         <v>1.3</v>
       </c>
       <c r="AN54" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AO54" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR54" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AU54" t="n">
         <v>1</v>
@@ -12459,25 +12459,25 @@
         <v>1.22</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.25</v>
+        <v>0.57</v>
       </c>
       <c r="AO55" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AU55" t="n">
         <v>4</v>
@@ -12677,25 +12677,25 @@
         <v>1.53</v>
       </c>
       <c r="AN56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO56" t="n">
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="AS56" t="n">
         <v>1.16</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="AU56" t="n">
         <v>6</v>
@@ -12895,25 +12895,25 @@
         <v>1.36</v>
       </c>
       <c r="AN57" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AO57" t="n">
-        <v>2.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="AU57" t="n">
         <v>8</v>
@@ -13113,25 +13113,25 @@
         <v>2.1</v>
       </c>
       <c r="AN58" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AO58" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AT58" t="n">
-        <v>2.19</v>
+        <v>2.49</v>
       </c>
       <c r="AU58" t="n">
         <v>3</v>
@@ -13331,25 +13331,25 @@
         <v>1.53</v>
       </c>
       <c r="AN59" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="AO59" t="n">
         <v>0.88</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR59" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS59" t="n">
         <v>1.13</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AU59" t="n">
         <v>1</v>
@@ -13549,25 +13549,25 @@
         <v>2.15</v>
       </c>
       <c r="AN60" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO60" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.89</v>
+        <v>1.45</v>
       </c>
       <c r="AS60" t="n">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AT60" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AU60" t="n">
         <v>6</v>
@@ -13770,22 +13770,22 @@
         <v>1.75</v>
       </c>
       <c r="AO61" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AT61" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="AU61" t="n">
         <v>5</v>
@@ -13985,25 +13985,25 @@
         <v>2.2</v>
       </c>
       <c r="AN62" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO62" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AS62" t="n">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AU62" t="n">
         <v>6</v>
@@ -14203,25 +14203,25 @@
         <v>1.5</v>
       </c>
       <c r="AN63" t="n">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AO63" t="n">
         <v>1.88</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS63" t="n">
         <v>1.15</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="AU63" t="n">
         <v>7</v>
@@ -14421,22 +14421,22 @@
         <v>1.95</v>
       </c>
       <c r="AN64" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO64" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AS64" t="n">
-        <v>0.96</v>
+        <v>1.18</v>
       </c>
       <c r="AT64" t="n">
         <v>2.46</v>
@@ -14639,25 +14639,25 @@
         <v>0</v>
       </c>
       <c r="AN65" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AO65" t="n">
-        <v>0.5</v>
+        <v>1.89</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR65" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AT65" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AU65" t="n">
         <v>2</v>
@@ -14857,25 +14857,25 @@
         <v>0</v>
       </c>
       <c r="AN66" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AO66" t="n">
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS66" t="n">
         <v>1.12</v>
       </c>
       <c r="AT66" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AU66" t="n">
         <v>3</v>
@@ -15075,25 +15075,25 @@
         <v>0</v>
       </c>
       <c r="AN67" t="n">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="AO67" t="n">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="AT67" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AU67" t="n">
         <v>2</v>
@@ -15293,25 +15293,25 @@
         <v>0</v>
       </c>
       <c r="AN68" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO68" t="n">
-        <v>1</v>
+        <v>1.89</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR68" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AT68" t="n">
-        <v>1.53</v>
+        <v>2.72</v>
       </c>
       <c r="AU68" t="n">
         <v>5</v>
@@ -15511,25 +15511,25 @@
         <v>0</v>
       </c>
       <c r="AN69" t="n">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="AO69" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AT69" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="AU69" t="n">
         <v>5</v>
@@ -15729,25 +15729,25 @@
         <v>0</v>
       </c>
       <c r="AN70" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AO70" t="n">
-        <v>0.6</v>
+        <v>1.22</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AT70" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="AU70" t="n">
         <v>5</v>
@@ -15947,25 +15947,25 @@
         <v>0</v>
       </c>
       <c r="AN71" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO71" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP71" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AR71" t="n">
         <v>1.23</v>
       </c>
-      <c r="AQ71" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR71" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AS71" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="AT71" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AU71" t="n">
         <v>4</v>
@@ -16165,25 +16165,25 @@
         <v>0</v>
       </c>
       <c r="AN72" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="AO72" t="n">
-        <v>0.25</v>
+        <v>0.9</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AT72" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="AU72" t="n">
         <v>1</v>
@@ -16383,25 +16383,25 @@
         <v>0</v>
       </c>
       <c r="AN73" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AO73" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AT73" t="n">
-        <v>3.03</v>
+        <v>2.61</v>
       </c>
       <c r="AU73" t="n">
         <v>4</v>
@@ -16601,25 +16601,25 @@
         <v>0</v>
       </c>
       <c r="AN74" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="AO74" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="AU74" t="n">
         <v>2</v>
@@ -16819,25 +16819,25 @@
         <v>0</v>
       </c>
       <c r="AN75" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AO75" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AS75" t="n">
-        <v>0.98</v>
+        <v>1.12</v>
       </c>
       <c r="AT75" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AU75" t="n">
         <v>4</v>
@@ -17037,25 +17037,25 @@
         <v>0</v>
       </c>
       <c r="AN76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO76" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR76" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS76" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AT76" t="n">
-        <v>0.89</v>
+        <v>2.05</v>
       </c>
       <c r="AU76" t="n">
         <v>3</v>
@@ -17255,25 +17255,25 @@
         <v>0</v>
       </c>
       <c r="AN77" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AO77" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AS77" t="n">
-        <v>0.92</v>
+        <v>1.34</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="AU77" t="n">
         <v>4</v>
@@ -17473,25 +17473,25 @@
         <v>0</v>
       </c>
       <c r="AN78" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT78" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR78" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS78" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AT78" t="n">
-        <v>2.59</v>
       </c>
       <c r="AU78" t="n">
         <v>7</v>
@@ -17691,25 +17691,25 @@
         <v>1.38</v>
       </c>
       <c r="AN79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS79" t="n">
         <v>1.4</v>
       </c>
-      <c r="AO79" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS79" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AT79" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="AU79" t="n">
         <v>4</v>
@@ -17909,25 +17909,25 @@
         <v>1.83</v>
       </c>
       <c r="AN80" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR80" t="n">
         <v>1.33</v>
       </c>
-      <c r="AO80" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AP80" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AQ80" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AR80" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AS80" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AT80" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AU80" t="n">
         <v>2</v>
@@ -18127,25 +18127,25 @@
         <v>1.4</v>
       </c>
       <c r="AN81" t="n">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="AO81" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AP81" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AU81" t="n">
         <v>3</v>
@@ -18345,25 +18345,25 @@
         <v>1.36</v>
       </c>
       <c r="AN82" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AO82" t="n">
-        <v>1</v>
+        <v>1.91</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AT82" t="n">
-        <v>3.07</v>
+        <v>2.99</v>
       </c>
       <c r="AU82" t="n">
         <v>8</v>
@@ -18563,25 +18563,25 @@
         <v>1.1</v>
       </c>
       <c r="AN83" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="AO83" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="AU83" t="n">
         <v>0</v>
@@ -18781,25 +18781,25 @@
         <v>2</v>
       </c>
       <c r="AN84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO84" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR84" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AT84" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="AU84" t="n">
         <v>7</v>
@@ -18999,25 +18999,25 @@
         <v>1.36</v>
       </c>
       <c r="AN85" t="n">
-        <v>0.83</v>
+        <v>1.09</v>
       </c>
       <c r="AO85" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AU85" t="n">
         <v>3</v>
@@ -19217,25 +19217,25 @@
         <v>1.25</v>
       </c>
       <c r="AN86" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AO86" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="AU86" t="n">
         <v>4</v>
@@ -19435,25 +19435,25 @@
         <v>1.75</v>
       </c>
       <c r="AN87" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="AO87" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP87" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT87" t="n">
-        <v>2.53</v>
+        <v>2.29</v>
       </c>
       <c r="AU87" t="n">
         <v>2</v>
@@ -19653,25 +19653,25 @@
         <v>1.3</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="AO88" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR88" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="AU88" t="n">
         <v>5</v>
@@ -19871,25 +19871,25 @@
         <v>1.73</v>
       </c>
       <c r="AN89" t="n">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="AO89" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AT89" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="AU89" t="n">
         <v>8</v>
@@ -20089,25 +20089,25 @@
         <v>1.53</v>
       </c>
       <c r="AN90" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AO90" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="AU90" t="n">
         <v>3</v>
@@ -20307,25 +20307,25 @@
         <v>2</v>
       </c>
       <c r="AN91" t="n">
-        <v>2.71</v>
+        <v>2.58</v>
       </c>
       <c r="AO91" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AT91" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AU91" t="n">
         <v>7</v>
@@ -20525,25 +20525,25 @@
         <v>1.95</v>
       </c>
       <c r="AN92" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="AO92" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="AU92" t="n">
         <v>7</v>
@@ -20743,25 +20743,25 @@
         <v>1.62</v>
       </c>
       <c r="AN93" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AO93" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="AU93" t="n">
         <v>4</v>
@@ -20961,25 +20961,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94" t="n">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="AO94" t="n">
-        <v>0.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AS94" t="n">
-        <v>0.98</v>
+        <v>1.15</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="AU94" t="n">
         <v>6</v>
@@ -21179,25 +21179,25 @@
         <v>1.5</v>
       </c>
       <c r="AN95" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="AO95" t="n">
-        <v>0.67</v>
+        <v>1.08</v>
       </c>
       <c r="AP95" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AU95" t="n">
         <v>4</v>
@@ -21397,25 +21397,25 @@
         <v>1.35</v>
       </c>
       <c r="AN96" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO96" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AT96" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="AU96" t="n">
         <v>4</v>
@@ -21615,25 +21615,25 @@
         <v>1.65</v>
       </c>
       <c r="AN97" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AO97" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AT97" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AU97" t="n">
         <v>4</v>
@@ -21833,25 +21833,25 @@
         <v>2</v>
       </c>
       <c r="AN98" t="n">
-        <v>2.43</v>
+        <v>1.92</v>
       </c>
       <c r="AO98" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AP98" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.19</v>
+        <v>3.04</v>
       </c>
       <c r="AU98" t="n">
         <v>9</v>
@@ -22051,25 +22051,25 @@
         <v>1.08</v>
       </c>
       <c r="AN99" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="AU99" t="n">
         <v>5</v>
@@ -22269,25 +22269,25 @@
         <v>1.17</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="AO100" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR100" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.57</v>
+        <v>2.76</v>
       </c>
       <c r="AU100" t="n">
         <v>3</v>
@@ -22487,25 +22487,25 @@
         <v>1.28</v>
       </c>
       <c r="AN101" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AO101" t="n">
-        <v>0.86</v>
+        <v>1.29</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AU101" t="n">
         <v>0</v>
@@ -22705,25 +22705,25 @@
         <v>1.57</v>
       </c>
       <c r="AN102" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AO102" t="n">
-        <v>0.14</v>
+        <v>0.64</v>
       </c>
       <c r="AP102" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ102" t="n">
         <v>1.07</v>
       </c>
-      <c r="AQ102" t="n">
-        <v>0.93</v>
-      </c>
       <c r="AR102" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AS102" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AU102" t="n">
         <v>5</v>
@@ -22923,25 +22923,25 @@
         <v>2.22</v>
       </c>
       <c r="AN103" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="AO103" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AS103" t="n">
-        <v>0.99</v>
+        <v>1.1</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AU103" t="n">
         <v>3</v>
@@ -23141,25 +23141,25 @@
         <v>1.42</v>
       </c>
       <c r="AN104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO104" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="AU104" t="n">
         <v>4</v>
@@ -23359,25 +23359,25 @@
         <v>2.05</v>
       </c>
       <c r="AN105" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AO105" t="n">
         <v>1.57</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AT105" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AU105" t="n">
         <v>5</v>
@@ -23577,25 +23577,25 @@
         <v>1.85</v>
       </c>
       <c r="AN106" t="n">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="AO106" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AU106" t="n">
         <v>2</v>
@@ -23795,25 +23795,25 @@
         <v>2.3</v>
       </c>
       <c r="AN107" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AO107" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.58</v>
+        <v>2.47</v>
       </c>
       <c r="AU107" t="n">
         <v>4</v>
@@ -24013,25 +24013,25 @@
         <v>1.44</v>
       </c>
       <c r="AN108" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AO108" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="AU108" t="n">
         <v>6</v>
@@ -24231,25 +24231,25 @@
         <v>1.41</v>
       </c>
       <c r="AN109" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AO109" t="n">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="AU109" t="n">
         <v>3</v>
@@ -24449,25 +24449,25 @@
         <v>1.44</v>
       </c>
       <c r="AN110" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AO110" t="n">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AU110" t="n">
         <v>8</v>
@@ -24667,25 +24667,25 @@
         <v>1.73</v>
       </c>
       <c r="AN111" t="n">
-        <v>1.14</v>
+        <v>0.8</v>
       </c>
       <c r="AO111" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AS111" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AU111" t="n">
         <v>1</v>
@@ -24885,25 +24885,25 @@
         <v>1.77</v>
       </c>
       <c r="AN112" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO112" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AU112" t="n">
         <v>10</v>
@@ -25103,25 +25103,25 @@
         <v>1.46</v>
       </c>
       <c r="AN113" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AO113" t="n">
-        <v>2.17</v>
+        <v>2.53</v>
       </c>
       <c r="AP113" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ113" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="AU113" t="n">
         <v>6</v>
@@ -25321,25 +25321,25 @@
         <v>3.02</v>
       </c>
       <c r="AN114" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="AO114" t="n">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AS114" t="n">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AU114" t="n">
         <v>3</v>
@@ -25539,25 +25539,25 @@
         <v>1.15</v>
       </c>
       <c r="AN115" t="n">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AO115" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AU115" t="n">
         <v>6</v>
@@ -25757,25 +25757,25 @@
         <v>1.22</v>
       </c>
       <c r="AN116" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO116" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AS116" t="n">
         <v>1.35</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="AU116" t="n">
         <v>4</v>
@@ -25975,25 +25975,25 @@
         <v>1.33</v>
       </c>
       <c r="AN117" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AO117" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR117" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="AU117" t="n">
         <v>2</v>
@@ -26193,25 +26193,25 @@
         <v>2.1</v>
       </c>
       <c r="AN118" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AO118" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="AU118" t="n">
         <v>8</v>
@@ -26411,25 +26411,25 @@
         <v>1.17</v>
       </c>
       <c r="AN119" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AO119" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.13</v>
+        <v>2.98</v>
       </c>
       <c r="AU119" t="n">
         <v>3</v>
@@ -26629,25 +26629,25 @@
         <v>1.57</v>
       </c>
       <c r="AN120" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AO120" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="AU120" t="n">
         <v>3</v>
@@ -26847,25 +26847,25 @@
         <v>1.5</v>
       </c>
       <c r="AN121" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AO121" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="AU121" t="n">
         <v>3</v>
@@ -27065,25 +27065,25 @@
         <v>2.04</v>
       </c>
       <c r="AN122" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AO122" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="AU122" t="n">
         <v>8</v>
@@ -27283,25 +27283,25 @@
         <v>1.52</v>
       </c>
       <c r="AN123" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO123" t="n">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AS123" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AU123" t="n">
         <v>3</v>
@@ -27501,25 +27501,25 @@
         <v>1.43</v>
       </c>
       <c r="AN124" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS124" t="n">
         <v>1.13</v>
       </c>
-      <c r="AO124" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AP124" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ124" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR124" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AS124" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AT124" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AU124" t="n">
         <v>2</v>
@@ -27719,25 +27719,25 @@
         <v>1.8</v>
       </c>
       <c r="AN125" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AO125" t="n">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AU125" t="n">
         <v>2</v>
@@ -27937,25 +27937,25 @@
         <v>1.36</v>
       </c>
       <c r="AN126" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="AO126" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AP126" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AT126" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AU126" t="n">
         <v>7</v>
@@ -28155,22 +28155,22 @@
         <v>1.22</v>
       </c>
       <c r="AN127" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AO127" t="n">
-        <v>2.29</v>
+        <v>2.59</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AT127" t="n">
         <v>2.63</v>
@@ -28373,25 +28373,25 @@
         <v>1.36</v>
       </c>
       <c r="AN128" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AO128" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="AU128" t="n">
         <v>6</v>
@@ -28591,25 +28591,25 @@
         <v>1.2</v>
       </c>
       <c r="AN129" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AO129" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AU129" t="n">
         <v>2</v>
@@ -28809,25 +28809,25 @@
         <v>1.25</v>
       </c>
       <c r="AN130" t="n">
-        <v>0.43</v>
+        <v>0.78</v>
       </c>
       <c r="AO130" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AP130" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AU130" t="n">
         <v>5</v>
@@ -29027,25 +29027,25 @@
         <v>1.6</v>
       </c>
       <c r="AN131" t="n">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO131" t="n">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AS131" t="n">
-        <v>0.89</v>
+        <v>1.05</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="AU131" t="n">
         <v>6</v>
@@ -29245,25 +29245,25 @@
         <v>1.25</v>
       </c>
       <c r="AN132" t="n">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AO132" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AU132" t="n">
         <v>2</v>
@@ -29463,25 +29463,25 @@
         <v>1.44</v>
       </c>
       <c r="AN133" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AO133" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="AU133" t="n">
         <v>5</v>
@@ -29681,25 +29681,25 @@
         <v>1.75</v>
       </c>
       <c r="AN134" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO134" t="n">
-        <v>0.44</v>
+        <v>0.67</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AU134" t="n">
         <v>3</v>
@@ -29899,25 +29899,25 @@
         <v>2.82</v>
       </c>
       <c r="AN135" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AO135" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP135" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AU135" t="n">
         <v>4</v>
@@ -30117,25 +30117,25 @@
         <v>1.48</v>
       </c>
       <c r="AN136" t="n">
-        <v>0.89</v>
+        <v>0.68</v>
       </c>
       <c r="AO136" t="n">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AS136" t="n">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AU136" t="n">
         <v>5</v>
@@ -30335,25 +30335,25 @@
         <v>2.03</v>
       </c>
       <c r="AN137" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AO137" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AU137" t="n">
         <v>4</v>
@@ -30553,25 +30553,25 @@
         <v>1.77</v>
       </c>
       <c r="AN138" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="AO138" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AU138" t="n">
         <v>2</v>
@@ -30771,25 +30771,25 @@
         <v>2</v>
       </c>
       <c r="AN139" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="AO139" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="AU139" t="n">
         <v>7</v>
@@ -30989,25 +30989,25 @@
         <v>1.62</v>
       </c>
       <c r="AN140" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AO140" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ140" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR140" t="n">
         <v>1.38</v>
       </c>
-      <c r="AR140" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AS140" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AT140" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="AU140" t="n">
         <v>1</v>
@@ -31207,25 +31207,25 @@
         <v>1.25</v>
       </c>
       <c r="AN141" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="AO141" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="AU141" t="n">
         <v>3</v>
@@ -31425,25 +31425,25 @@
         <v>1.3</v>
       </c>
       <c r="AN142" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AO142" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AT142" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="AU142" t="n">
         <v>10</v>
@@ -31643,25 +31643,25 @@
         <v>2.03</v>
       </c>
       <c r="AN143" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AO143" t="n">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AS143" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AU143" t="n">
         <v>5</v>
@@ -31861,25 +31861,25 @@
         <v>1.73</v>
       </c>
       <c r="AN144" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AO144" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="AU144" t="n">
         <v>5</v>
@@ -32079,25 +32079,25 @@
         <v>1.3</v>
       </c>
       <c r="AN145" t="n">
-        <v>1.2</v>
+        <v>0.95</v>
       </c>
       <c r="AO145" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AU145" t="n">
         <v>1</v>
@@ -32297,25 +32297,25 @@
         <v>1.62</v>
       </c>
       <c r="AN146" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AO146" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="AU146" t="n">
         <v>6</v>
@@ -32515,25 +32515,25 @@
         <v>1.62</v>
       </c>
       <c r="AN147" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="AO147" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AS147" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AU147" t="n">
         <v>3</v>
@@ -32733,25 +32733,25 @@
         <v>1.11</v>
       </c>
       <c r="AN148" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AO148" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ148" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AU148" t="n">
         <v>3</v>
@@ -32951,25 +32951,25 @@
         <v>1.43</v>
       </c>
       <c r="AN149" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AO149" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AU149" t="n">
         <v>6</v>
@@ -33169,25 +33169,25 @@
         <v>1.48</v>
       </c>
       <c r="AN150" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AO150" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AU150" t="n">
         <v>10</v>
@@ -33387,25 +33387,25 @@
         <v>1.3</v>
       </c>
       <c r="AN151" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AO151" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AU151" t="n">
         <v>3</v>
@@ -33605,25 +33605,25 @@
         <v>2.03</v>
       </c>
       <c r="AN152" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AO152" t="n">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AS152" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AU152" t="n">
         <v>3</v>
@@ -33823,25 +33823,25 @@
         <v>1.4</v>
       </c>
       <c r="AN153" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AO153" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ153" t="n">
         <v>1.67</v>
       </c>
-      <c r="AP153" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ153" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AR153" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="AU153" t="n">
         <v>4</v>
@@ -34041,25 +34041,25 @@
         <v>2.05</v>
       </c>
       <c r="AN154" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AO154" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AP154" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="AU154" t="n">
         <v>2</v>
@@ -34259,25 +34259,25 @@
         <v>3.3</v>
       </c>
       <c r="AN155" t="n">
-        <v>2.82</v>
+        <v>2.43</v>
       </c>
       <c r="AO155" t="n">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AS155" t="n">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AU155" t="n">
         <v>6</v>
@@ -34477,25 +34477,25 @@
         <v>1.85</v>
       </c>
       <c r="AN156" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AO156" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AT156" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="AU156" t="n">
         <v>3</v>
@@ -34695,25 +34695,25 @@
         <v>1.22</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AO157" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ157" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.37</v>
+        <v>2.57</v>
       </c>
       <c r="AU157" t="n">
         <v>1</v>
@@ -34913,25 +34913,25 @@
         <v>1.57</v>
       </c>
       <c r="AN158" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AO158" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AU158" t="n">
         <v>2</v>
@@ -35131,25 +35131,25 @@
         <v>1.28</v>
       </c>
       <c r="AN159" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AO159" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AU159" t="n">
         <v>4</v>
@@ -35349,25 +35349,25 @@
         <v>1.45</v>
       </c>
       <c r="AN160" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AO160" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AU160" t="n">
         <v>6</v>
@@ -35567,25 +35567,25 @@
         <v>1.3</v>
       </c>
       <c r="AN161" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AO161" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AU161" t="n">
         <v>2</v>
@@ -35785,25 +35785,25 @@
         <v>1.13</v>
       </c>
       <c r="AN162" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AO162" t="n">
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AT162" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AU162" t="n">
         <v>7</v>
@@ -36003,25 +36003,25 @@
         <v>2.1</v>
       </c>
       <c r="AN163" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AO163" t="n">
-        <v>0.64</v>
+        <v>0.91</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AU163" t="n">
         <v>6</v>
@@ -36221,25 +36221,25 @@
         <v>1.25</v>
       </c>
       <c r="AN164" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AO164" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AQ164" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="AU164" t="n">
         <v>5</v>
@@ -36439,25 +36439,25 @@
         <v>2.8</v>
       </c>
       <c r="AN165" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AO165" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AP165" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AS165" t="n">
-        <v>0.92</v>
+        <v>1.06</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AU165" t="n">
         <v>4</v>
@@ -36657,25 +36657,25 @@
         <v>1.45</v>
       </c>
       <c r="AN166" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AO166" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AT166" t="n">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="AU166" t="n">
         <v>2</v>
@@ -36875,25 +36875,25 @@
         <v>2</v>
       </c>
       <c r="AN167" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AO167" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AS167" t="n">
-        <v>0.92</v>
+        <v>1.01</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="AU167" t="n">
         <v>1</v>
@@ -37093,25 +37093,25 @@
         <v>1.83</v>
       </c>
       <c r="AN168" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AO168" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AS168" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AT168" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AU168" t="n">
         <v>7</v>
@@ -37311,25 +37311,25 @@
         <v>1.4</v>
       </c>
       <c r="AN169" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AO169" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AT169" t="n">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="AU169" t="n">
         <v>2</v>
@@ -37529,25 +37529,25 @@
         <v>1.22</v>
       </c>
       <c r="AN170" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AO170" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AP170" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AU170" t="n">
         <v>4</v>
@@ -37747,25 +37747,25 @@
         <v>1.5</v>
       </c>
       <c r="AN171" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AO171" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AP171" t="n">
         <v>1.67</v>
       </c>
-      <c r="AP171" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AQ171" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="AU171" t="n">
         <v>3</v>
@@ -37965,25 +37965,25 @@
         <v>1.35</v>
       </c>
       <c r="AN172" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AO172" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AT172" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="AU172" t="n">
         <v>4</v>
@@ -38183,25 +38183,25 @@
         <v>1.53</v>
       </c>
       <c r="AN173" t="n">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="AO173" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ173" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AS173" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AT173" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AU173" t="n">
         <v>1</v>
@@ -38401,25 +38401,25 @@
         <v>1.2</v>
       </c>
       <c r="AN174" t="n">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="AO174" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR174" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AS174" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AU174" t="n">
         <v>5</v>
@@ -38619,25 +38619,25 @@
         <v>2.2</v>
       </c>
       <c r="AN175" t="n">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="AO175" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AT175" t="n">
-        <v>2.71</v>
+        <v>2.41</v>
       </c>
       <c r="AU175" t="n">
         <v>4</v>
@@ -38837,25 +38837,25 @@
         <v>1.3</v>
       </c>
       <c r="AN176" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="AO176" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AP176" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AU176" t="n">
         <v>3</v>
@@ -39055,25 +39055,25 @@
         <v>1.62</v>
       </c>
       <c r="AN177" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AO177" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AS177" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AT177" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="AU177" t="n">
         <v>2</v>
@@ -39273,25 +39273,25 @@
         <v>1.91</v>
       </c>
       <c r="AN178" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AO178" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AS178" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AT178" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AU178" t="n">
         <v>4</v>
@@ -39491,25 +39491,25 @@
         <v>2</v>
       </c>
       <c r="AN179" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AO179" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AS179" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="AT179" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AU179" t="n">
         <v>5</v>
@@ -39709,25 +39709,25 @@
         <v>1.85</v>
       </c>
       <c r="AN180" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AO180" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AQ180" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="AU180" t="n">
         <v>6</v>
@@ -39927,25 +39927,25 @@
         <v>1.13</v>
       </c>
       <c r="AN181" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="AO181" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AP181" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AQ181" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="AU181" t="n">
         <v>2</v>
@@ -40145,25 +40145,25 @@
         <v>1.48</v>
       </c>
       <c r="AN182" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AO182" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AR182" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AS182" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AU182" t="n">
         <v>3</v>
@@ -40363,25 +40363,25 @@
         <v>1.2</v>
       </c>
       <c r="AN183" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO183" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR183" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AS183" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AT183" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AU183" t="n">
         <v>3</v>
@@ -40581,25 +40581,25 @@
         <v>1.87</v>
       </c>
       <c r="AN184" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AO184" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AR184" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AS184" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AT184" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AU184" t="n">
         <v>2</v>
@@ -40799,25 +40799,25 @@
         <v>1.85</v>
       </c>
       <c r="AN185" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AO185" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AP185" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR185" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AS185" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AT185" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AU185" t="n">
         <v>6</v>
@@ -41017,25 +41017,25 @@
         <v>1.41</v>
       </c>
       <c r="AN186" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="AO186" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AP186" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AQ186" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR186" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AS186" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AT186" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AU186" t="n">
         <v>6</v>
@@ -41235,25 +41235,25 @@
         <v>1.48</v>
       </c>
       <c r="AN187" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AO187" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR187" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS187" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AT187" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="AU187" t="n">
         <v>4</v>
@@ -41453,25 +41453,25 @@
         <v>2.21</v>
       </c>
       <c r="AN188" t="n">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AO188" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AP188" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS188" t="n">
         <v>1.21</v>
       </c>
-      <c r="AQ188" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AR188" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS188" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AT188" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AU188" t="n">
         <v>6</v>
@@ -41671,25 +41671,25 @@
         <v>1.29</v>
       </c>
       <c r="AN189" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="AO189" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AS189" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT189" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AU189" t="n">
         <v>2</v>
@@ -41889,25 +41889,25 @@
         <v>1.29</v>
       </c>
       <c r="AN190" t="n">
-        <v>1.15</v>
+        <v>0.88</v>
       </c>
       <c r="AO190" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AS190" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AT190" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AU190" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.48</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.07</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.19</v>
@@ -2222,7 +2222,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR9" t="n">
         <v>2.45</v>
@@ -2655,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.48</v>
@@ -2873,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR11" t="n">
         <v>0.91</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR13" t="n">
         <v>1.27</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR15" t="n">
         <v>0.6899999999999999</v>
@@ -3966,7 +3966,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR16" t="n">
         <v>1.51</v>
@@ -4184,7 +4184,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR17" t="n">
         <v>1.03</v>
@@ -4399,10 +4399,10 @@
         <v>2</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR18" t="n">
         <v>1.16</v>
@@ -4620,7 +4620,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR19" t="n">
         <v>1.3</v>
@@ -4835,10 +4835,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR20" t="n">
         <v>0.93</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ22" t="n">
         <v>2.3</v>
@@ -5492,7 +5492,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR23" t="n">
         <v>1.57</v>
@@ -5710,7 +5710,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR24" t="n">
         <v>1.08</v>
@@ -5928,7 +5928,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR25" t="n">
         <v>1.51</v>
@@ -6143,7 +6143,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.19</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.74</v>
@@ -6579,10 +6579,10 @@
         <v>2.33</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR28" t="n">
         <v>0.9399999999999999</v>
@@ -6800,7 +6800,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR29" t="n">
         <v>1.24</v>
@@ -7015,7 +7015,7 @@
         <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.07</v>
@@ -7233,10 +7233,10 @@
         <v>2</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR31" t="n">
         <v>1.42</v>
@@ -7451,10 +7451,10 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR32" t="n">
         <v>0.92</v>
@@ -7672,7 +7672,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR33" t="n">
         <v>1.44</v>
@@ -8105,7 +8105,7 @@
         <v>2.25</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.67</v>
@@ -8326,7 +8326,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR36" t="n">
         <v>1.2</v>
@@ -8541,7 +8541,7 @@
         <v>0.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.74</v>
@@ -8977,10 +8977,10 @@
         <v>1.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR39" t="n">
         <v>1.25</v>
@@ -9195,10 +9195,10 @@
         <v>1.6</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR40" t="n">
         <v>1.53</v>
@@ -9634,7 +9634,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR42" t="n">
         <v>1.31</v>
@@ -9849,10 +9849,10 @@
         <v>0.2</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR43" t="n">
         <v>0.82</v>
@@ -10288,7 +10288,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR45" t="n">
         <v>1.2</v>
@@ -10506,7 +10506,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR46" t="n">
         <v>1.29</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR47" t="n">
         <v>1.21</v>
@@ -10942,7 +10942,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR48" t="n">
         <v>1.41</v>
@@ -11157,10 +11157,10 @@
         <v>2.17</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR49" t="n">
         <v>1.27</v>
@@ -11378,7 +11378,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR50" t="n">
         <v>0.8100000000000001</v>
@@ -11593,10 +11593,10 @@
         <v>0.57</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR51" t="n">
         <v>1.07</v>
@@ -12029,7 +12029,7 @@
         <v>0.86</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.07</v>
@@ -12247,7 +12247,7 @@
         <v>1.86</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.67</v>
@@ -12465,10 +12465,10 @@
         <v>1.29</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR55" t="n">
         <v>1.05</v>
@@ -12686,7 +12686,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -12901,7 +12901,7 @@
         <v>1.29</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.48</v>
@@ -13119,10 +13119,10 @@
         <v>1.38</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR58" t="n">
         <v>1.16</v>
@@ -13340,7 +13340,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR59" t="n">
         <v>0.9399999999999999</v>
@@ -13558,7 +13558,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR60" t="n">
         <v>1.45</v>
@@ -13991,10 +13991,10 @@
         <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR62" t="n">
         <v>1.59</v>
@@ -14212,7 +14212,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR63" t="n">
         <v>1.29</v>
@@ -14427,7 +14427,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.07</v>
@@ -14645,10 +14645,10 @@
         <v>1.89</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR65" t="n">
         <v>0.92</v>
@@ -14866,7 +14866,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR66" t="n">
         <v>1.37</v>
@@ -15081,10 +15081,10 @@
         <v>1.22</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR67" t="n">
         <v>1.14</v>
@@ -15299,10 +15299,10 @@
         <v>1.89</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR68" t="n">
         <v>1.12</v>
@@ -15735,7 +15735,7 @@
         <v>1.22</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.19</v>
@@ -16389,7 +16389,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.67</v>
@@ -16825,10 +16825,10 @@
         <v>0.7</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR75" t="n">
         <v>1.21</v>
@@ -17043,10 +17043,10 @@
         <v>1.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR76" t="n">
         <v>1.15</v>
@@ -17261,10 +17261,10 @@
         <v>1.8</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR77" t="n">
         <v>1.18</v>
@@ -17479,7 +17479,7 @@
         <v>0.3</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.74</v>
@@ -17697,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.19</v>
@@ -18136,7 +18136,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR81" t="n">
         <v>1.03</v>
@@ -18351,10 +18351,10 @@
         <v>1.91</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR82" t="n">
         <v>1.34</v>
@@ -18569,7 +18569,7 @@
         <v>2.55</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ83" t="n">
         <v>2.3</v>
@@ -18787,10 +18787,10 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR84" t="n">
         <v>1.13</v>
@@ -19008,7 +19008,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR85" t="n">
         <v>1.32</v>
@@ -19226,7 +19226,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR86" t="n">
         <v>1.13</v>
@@ -19441,10 +19441,10 @@
         <v>0.67</v>
       </c>
       <c r="AP87" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR87" t="n">
         <v>1.18</v>
@@ -19659,10 +19659,10 @@
         <v>1.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR88" t="n">
         <v>0.99</v>
@@ -19877,7 +19877,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.74</v>
@@ -20316,7 +20316,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR91" t="n">
         <v>1.36</v>
@@ -20531,7 +20531,7 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.48</v>
@@ -20749,10 +20749,10 @@
         <v>1.69</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR93" t="n">
         <v>1.15</v>
@@ -20967,7 +20967,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.07</v>
@@ -21185,10 +21185,10 @@
         <v>1.08</v>
       </c>
       <c r="AP95" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AQ95" t="n">
         <v>0.93</v>
-      </c>
-      <c r="AQ95" t="n">
-        <v>0.85</v>
       </c>
       <c r="AR95" t="n">
         <v>1.19</v>
@@ -21403,10 +21403,10 @@
         <v>1.38</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR96" t="n">
         <v>1.09</v>
@@ -21839,7 +21839,7 @@
         <v>1.69</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.67</v>
@@ -22275,10 +22275,10 @@
         <v>2</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR100" t="n">
         <v>1.07</v>
@@ -22493,7 +22493,7 @@
         <v>1.29</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.19</v>
@@ -22711,7 +22711,7 @@
         <v>0.64</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.07</v>
@@ -22929,10 +22929,10 @@
         <v>0.86</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR103" t="n">
         <v>1.3</v>
@@ -23147,10 +23147,10 @@
         <v>1.93</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR104" t="n">
         <v>1.17</v>
@@ -24022,7 +24022,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR108" t="n">
         <v>1.33</v>
@@ -24237,10 +24237,10 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR109" t="n">
         <v>1.17</v>
@@ -24455,10 +24455,10 @@
         <v>1.67</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR110" t="n">
         <v>1.17</v>
@@ -24676,7 +24676,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR111" t="n">
         <v>1.13</v>
@@ -24894,7 +24894,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR112" t="n">
         <v>1.28</v>
@@ -25109,7 +25109,7 @@
         <v>2.53</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ113" t="n">
         <v>2.3</v>
@@ -25548,7 +25548,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR115" t="n">
         <v>1.02</v>
@@ -25763,7 +25763,7 @@
         <v>1.56</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.67</v>
@@ -25981,7 +25981,7 @@
         <v>1.31</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.19</v>
@@ -26199,10 +26199,10 @@
         <v>0.75</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR118" t="n">
         <v>1.33</v>
@@ -26417,10 +26417,10 @@
         <v>1.94</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR119" t="n">
         <v>1.31</v>
@@ -26635,7 +26635,7 @@
         <v>1.19</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.48</v>
@@ -26856,7 +26856,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR121" t="n">
         <v>1.46</v>
@@ -27074,7 +27074,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR122" t="n">
         <v>1.34</v>
@@ -27289,7 +27289,7 @@
         <v>0.65</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.74</v>
@@ -27510,7 +27510,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR124" t="n">
         <v>1.05</v>
@@ -27725,10 +27725,10 @@
         <v>1.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR125" t="n">
         <v>1.66</v>
@@ -27943,10 +27943,10 @@
         <v>1.76</v>
       </c>
       <c r="AP126" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR126" t="n">
         <v>1.16</v>
@@ -28382,7 +28382,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR128" t="n">
         <v>1.43</v>
@@ -28597,7 +28597,7 @@
         <v>2.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ129" t="n">
         <v>2.3</v>
@@ -28815,10 +28815,10 @@
         <v>1.61</v>
       </c>
       <c r="AP130" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR130" t="n">
         <v>1.19</v>
@@ -29033,10 +29033,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP131" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR131" t="n">
         <v>1.27</v>
@@ -29472,7 +29472,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR133" t="n">
         <v>1.29</v>
@@ -29687,7 +29687,7 @@
         <v>0.67</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.74</v>
@@ -29905,10 +29905,10 @@
         <v>0.89</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR135" t="n">
         <v>1.64</v>
@@ -30341,10 +30341,10 @@
         <v>0.95</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR137" t="n">
         <v>1.21</v>
@@ -30559,10 +30559,10 @@
         <v>1.16</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR138" t="n">
         <v>1.37</v>
@@ -31213,10 +31213,10 @@
         <v>1.53</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR141" t="n">
         <v>1.04</v>
@@ -31431,10 +31431,10 @@
         <v>2.05</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR142" t="n">
         <v>1.22</v>
@@ -31652,7 +31652,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR143" t="n">
         <v>1.29</v>
@@ -31867,10 +31867,10 @@
         <v>1.15</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR144" t="n">
         <v>1.24</v>
@@ -32088,7 +32088,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR145" t="n">
         <v>1.03</v>
@@ -32521,7 +32521,7 @@
         <v>0.65</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.74</v>
@@ -32739,7 +32739,7 @@
         <v>2.4</v>
       </c>
       <c r="AP148" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ148" t="n">
         <v>2.3</v>
@@ -32957,7 +32957,7 @@
         <v>1.81</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.67</v>
@@ -33178,7 +33178,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR150" t="n">
         <v>1.08</v>
@@ -33393,7 +33393,7 @@
         <v>1.24</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.48</v>
@@ -33829,10 +33829,10 @@
         <v>1.76</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR153" t="n">
         <v>1.09</v>
@@ -34047,10 +34047,10 @@
         <v>1.43</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR154" t="n">
         <v>1.61</v>
@@ -34268,7 +34268,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR155" t="n">
         <v>1.33</v>
@@ -34486,7 +34486,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR156" t="n">
         <v>1.37</v>
@@ -34701,7 +34701,7 @@
         <v>2.45</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ157" t="n">
         <v>2.3</v>
@@ -34919,7 +34919,7 @@
         <v>1.18</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.19</v>
@@ -35355,10 +35355,10 @@
         <v>0.91</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR160" t="n">
         <v>1.04</v>
@@ -35573,10 +35573,10 @@
         <v>1.55</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR161" t="n">
         <v>1.24</v>
@@ -35794,7 +35794,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR162" t="n">
         <v>1.14</v>
@@ -36012,7 +36012,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR163" t="n">
         <v>1.41</v>
@@ -36227,7 +36227,7 @@
         <v>2.39</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ164" t="n">
         <v>2.3</v>
@@ -36445,10 +36445,10 @@
         <v>0.87</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR165" t="n">
         <v>1.62</v>
@@ -36663,7 +36663,7 @@
         <v>1.39</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.48</v>
@@ -36881,7 +36881,7 @@
         <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.07</v>
@@ -37099,7 +37099,7 @@
         <v>0.7</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.74</v>
@@ -37317,7 +37317,7 @@
         <v>1.65</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.67</v>
@@ -37535,7 +37535,7 @@
         <v>1.17</v>
       </c>
       <c r="AP170" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.19</v>
@@ -37753,7 +37753,7 @@
         <v>1.71</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.67</v>
@@ -37974,7 +37974,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR172" t="n">
         <v>1.32</v>
@@ -38189,7 +38189,7 @@
         <v>1</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.07</v>
@@ -38407,10 +38407,10 @@
         <v>1.46</v>
       </c>
       <c r="AP174" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR174" t="n">
         <v>1.2</v>
@@ -38628,7 +38628,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR175" t="n">
         <v>1.26</v>
@@ -38846,7 +38846,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR176" t="n">
         <v>1.17</v>
@@ -39061,7 +39061,7 @@
         <v>1.44</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.48</v>
@@ -39279,10 +39279,10 @@
         <v>0.92</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR178" t="n">
         <v>1.16</v>
@@ -39497,10 +39497,10 @@
         <v>0.8</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR179" t="n">
         <v>1.3</v>
@@ -39933,7 +39933,7 @@
         <v>2.32</v>
       </c>
       <c r="AP181" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AQ181" t="n">
         <v>2.3</v>
@@ -40154,7 +40154,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR182" t="n">
         <v>1.42</v>
@@ -40372,7 +40372,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR183" t="n">
         <v>1</v>
@@ -40805,10 +40805,10 @@
         <v>1.42</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AR185" t="n">
         <v>1.61</v>
@@ -41023,7 +41023,7 @@
         <v>1</v>
       </c>
       <c r="AP186" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.07</v>
@@ -41244,7 +41244,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AR187" t="n">
         <v>1.3</v>
@@ -41459,10 +41459,10 @@
         <v>0.92</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AR188" t="n">
         <v>1.37</v>
@@ -41680,7 +41680,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR189" t="n">
         <v>1.17</v>
@@ -41895,7 +41895,7 @@
         <v>1.62</v>
       </c>
       <c r="AP190" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.67</v>
@@ -41974,6 +41974,878 @@
       </c>
       <c r="BP190" t="n">
         <v>1.05</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>7814010</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>45906.29166666666</v>
+      </c>
+      <c r="F191" t="n">
+        <v>28</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Busan I'Park</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Suwon Bluewings</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>1</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="n">
+        <v>1</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R191" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S191" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U191" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V191" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W191" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X191" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>7814011</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>45906.29166666666</v>
+      </c>
+      <c r="F192" t="n">
+        <v>28</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Jeonnam Dragons</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" t="n">
+        <v>2</v>
+      </c>
+      <c r="K192" t="n">
+        <v>3</v>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="n">
+        <v>2</v>
+      </c>
+      <c r="N192" t="n">
+        <v>3</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>['45+5']</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>['3', '35']</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R192" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S192" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V192" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W192" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X192" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY192" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="BF192" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG192" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BH192" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BI192" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BJ192" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BK192" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BL192" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BM192" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BO192" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="BP192" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>7814012</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>45906.29166666666</v>
+      </c>
+      <c r="F193" t="n">
+        <v>28</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Cheongju</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Gyeongnam</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>1</v>
+      </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R193" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S193" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T193" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U193" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V193" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W193" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X193" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX193" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY193" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB193" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BE193" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF193" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BG193" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BH193" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI193" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ193" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK193" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BL193" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM193" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BN193" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO193" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BP193" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>7814013</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>45906.29166666666</v>
+      </c>
+      <c r="F194" t="n">
+        <v>28</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Seongnam</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>3</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>3</v>
+      </c>
+      <c r="L194" t="n">
+        <v>4</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>4</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>['6', '19', '43', '54']</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R194" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S194" t="n">
+        <v>5</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V194" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X194" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX194" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY194" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB194" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC194" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE194" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BF194" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BG194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH194" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BI194" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ194" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BK194" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL194" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BM194" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BN194" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BO194" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="BP194" t="n">
+        <v>1.09</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP194"/>
+  <dimension ref="A1:BP197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.93</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.61</v>
@@ -1350,7 +1350,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.89</v>
@@ -2437,7 +2437,7 @@
         <v>3</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.86</v>
@@ -2658,7 +2658,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR10" t="n">
         <v>0.6899999999999999</v>
@@ -3094,7 +3094,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR12" t="n">
         <v>0.67</v>
@@ -3527,10 +3527,10 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -3963,7 +3963,7 @@
         <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.57</v>
@@ -4617,7 +4617,7 @@
         <v>0.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.89</v>
@@ -5053,10 +5053,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR21" t="n">
         <v>0.89</v>
@@ -5274,7 +5274,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR22" t="n">
         <v>0.79</v>
@@ -5489,7 +5489,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.54</v>
@@ -5925,7 +5925,7 @@
         <v>2.33</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.46</v>
@@ -6146,7 +6146,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR26" t="n">
         <v>1.55</v>
@@ -6364,7 +6364,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR27" t="n">
         <v>1.14</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.71</v>
@@ -7669,7 +7669,7 @@
         <v>1.75</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.57</v>
@@ -7887,10 +7887,10 @@
         <v>1.25</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR34" t="n">
         <v>0.73</v>
@@ -8108,7 +8108,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR35" t="n">
         <v>0.78</v>
@@ -8323,7 +8323,7 @@
         <v>2</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.46</v>
@@ -8544,7 +8544,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR37" t="n">
         <v>0.86</v>
@@ -8762,7 +8762,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR38" t="n">
         <v>1.24</v>
@@ -9413,10 +9413,10 @@
         <v>1.8</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR41" t="n">
         <v>1.35</v>
@@ -9631,7 +9631,7 @@
         <v>0.8</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.89</v>
@@ -10067,10 +10067,10 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR44" t="n">
         <v>1.31</v>
@@ -10503,7 +10503,7 @@
         <v>1.67</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.86</v>
@@ -10939,7 +10939,7 @@
         <v>0.67</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.89</v>
@@ -11375,7 +11375,7 @@
         <v>0.17</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.71</v>
@@ -11811,10 +11811,10 @@
         <v>0.43</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR52" t="n">
         <v>1.44</v>
@@ -12250,7 +12250,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR54" t="n">
         <v>0.89</v>
@@ -12683,7 +12683,7 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.61</v>
@@ -12904,7 +12904,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR57" t="n">
         <v>1.29</v>
@@ -13337,7 +13337,7 @@
         <v>0.88</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.89</v>
@@ -13555,7 +13555,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.71</v>
@@ -13773,10 +13773,10 @@
         <v>2.38</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR61" t="n">
         <v>1.32</v>
@@ -14209,7 +14209,7 @@
         <v>1.88</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.61</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.61</v>
@@ -15517,10 +15517,10 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR69" t="n">
         <v>1.36</v>
@@ -15738,7 +15738,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR70" t="n">
         <v>1.36</v>
@@ -15956,7 +15956,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR71" t="n">
         <v>1.23</v>
@@ -16171,7 +16171,7 @@
         <v>0.9</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.07</v>
@@ -16392,7 +16392,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR73" t="n">
         <v>1.28</v>
@@ -16607,10 +16607,10 @@
         <v>2.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR74" t="n">
         <v>1.43</v>
@@ -17482,7 +17482,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR78" t="n">
         <v>1.6</v>
@@ -17700,7 +17700,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR79" t="n">
         <v>1.28</v>
@@ -17915,7 +17915,7 @@
         <v>0.82</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.07</v>
@@ -18133,7 +18133,7 @@
         <v>1.45</v>
       </c>
       <c r="AP81" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.46</v>
@@ -18572,7 +18572,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR83" t="n">
         <v>1.12</v>
@@ -19005,7 +19005,7 @@
         <v>1.91</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.54</v>
@@ -19880,7 +19880,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR89" t="n">
         <v>1.35</v>
@@ -20095,10 +20095,10 @@
         <v>1.75</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR90" t="n">
         <v>1.44</v>
@@ -20313,7 +20313,7 @@
         <v>2.08</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.61</v>
@@ -20534,7 +20534,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR92" t="n">
         <v>1.65</v>
@@ -21621,10 +21621,10 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR97" t="n">
         <v>1.44</v>
@@ -21842,7 +21842,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR98" t="n">
         <v>1.67</v>
@@ -22057,10 +22057,10 @@
         <v>2.62</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR99" t="n">
         <v>1.08</v>
@@ -22496,7 +22496,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR101" t="n">
         <v>1.18</v>
@@ -23365,10 +23365,10 @@
         <v>1.57</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR105" t="n">
         <v>1.39</v>
@@ -23583,10 +23583,10 @@
         <v>0.36</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR106" t="n">
         <v>1.28</v>
@@ -23801,10 +23801,10 @@
         <v>0.33</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR107" t="n">
         <v>1.44</v>
@@ -24019,7 +24019,7 @@
         <v>1.87</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.54</v>
@@ -24891,7 +24891,7 @@
         <v>1.13</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.93</v>
@@ -25112,7 +25112,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ113" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR113" t="n">
         <v>1.67</v>
@@ -25327,7 +25327,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.07</v>
@@ -25545,7 +25545,7 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.54</v>
@@ -25766,7 +25766,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR116" t="n">
         <v>1.04</v>
@@ -25984,7 +25984,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR117" t="n">
         <v>1.11</v>
@@ -26638,7 +26638,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR120" t="n">
         <v>1.23</v>
@@ -26853,7 +26853,7 @@
         <v>1.65</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.54</v>
@@ -27071,7 +27071,7 @@
         <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.93</v>
@@ -27292,7 +27292,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR123" t="n">
         <v>1.04</v>
@@ -28161,10 +28161,10 @@
         <v>2.59</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR127" t="n">
         <v>1.32</v>
@@ -28379,7 +28379,7 @@
         <v>1.94</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.86</v>
@@ -28600,7 +28600,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR129" t="n">
         <v>1.23</v>
@@ -29254,7 +29254,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR132" t="n">
         <v>1.04</v>
@@ -29469,7 +29469,7 @@
         <v>1.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.57</v>
@@ -29690,7 +29690,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR134" t="n">
         <v>1.13</v>
@@ -30123,7 +30123,7 @@
         <v>0.84</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.07</v>
@@ -30777,10 +30777,10 @@
         <v>1.32</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR139" t="n">
         <v>1.31</v>
@@ -30995,10 +30995,10 @@
         <v>1.26</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR140" t="n">
         <v>1.38</v>
@@ -31649,7 +31649,7 @@
         <v>0.95</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.71</v>
@@ -32303,10 +32303,10 @@
         <v>1.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR146" t="n">
         <v>1.35</v>
@@ -32524,7 +32524,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR147" t="n">
         <v>1.2</v>
@@ -32742,7 +32742,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ148" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR148" t="n">
         <v>1.26</v>
@@ -32960,7 +32960,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR149" t="n">
         <v>1.36</v>
@@ -33175,7 +33175,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.93</v>
@@ -33396,7 +33396,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR151" t="n">
         <v>1.2</v>
@@ -33611,7 +33611,7 @@
         <v>1.05</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.07</v>
@@ -34265,7 +34265,7 @@
         <v>0.95</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.71</v>
@@ -34483,7 +34483,7 @@
         <v>1.23</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.46</v>
@@ -34704,7 +34704,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ157" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR157" t="n">
         <v>1.23</v>
@@ -34922,7 +34922,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR158" t="n">
         <v>1.28</v>
@@ -35140,7 +35140,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR159" t="n">
         <v>1</v>
@@ -35791,7 +35791,7 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.86</v>
@@ -36009,7 +36009,7 @@
         <v>0.91</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.93</v>
@@ -36230,7 +36230,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ164" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR164" t="n">
         <v>1.39</v>
@@ -36666,7 +36666,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR166" t="n">
         <v>1.14</v>
@@ -37102,7 +37102,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR168" t="n">
         <v>1.27</v>
@@ -37320,7 +37320,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR169" t="n">
         <v>1.2</v>
@@ -37538,7 +37538,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR170" t="n">
         <v>1.07</v>
@@ -37756,7 +37756,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR171" t="n">
         <v>1.3</v>
@@ -37971,7 +37971,7 @@
         <v>2.08</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.86</v>
@@ -38625,7 +38625,7 @@
         <v>1.29</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.46</v>
@@ -38843,7 +38843,7 @@
         <v>1.42</v>
       </c>
       <c r="AP176" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.57</v>
@@ -39064,7 +39064,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AR177" t="n">
         <v>1.22</v>
@@ -39715,10 +39715,10 @@
         <v>0.76</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ180" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AR180" t="n">
         <v>1.34</v>
@@ -39936,7 +39936,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ181" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AR181" t="n">
         <v>1.21</v>
@@ -40151,7 +40151,7 @@
         <v>1.48</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ182" t="n">
         <v>1.57</v>
@@ -40587,10 +40587,10 @@
         <v>1.19</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR184" t="n">
         <v>1.28</v>
@@ -41241,7 +41241,7 @@
         <v>1.73</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.61</v>
@@ -41677,7 +41677,7 @@
         <v>1.42</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.54</v>
@@ -41898,7 +41898,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR190" t="n">
         <v>1.2</v>
@@ -42134,13 +42134,13 @@
         <v>2</v>
       </c>
       <c r="AW191" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX191" t="n">
         <v>5</v>
       </c>
       <c r="AY191" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ191" t="n">
         <v>7</v>
@@ -42346,22 +42346,22 @@
         <v>2.53</v>
       </c>
       <c r="AU192" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV192" t="n">
         <v>4</v>
       </c>
-      <c r="AV192" t="n">
+      <c r="AW192" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX192" t="n">
         <v>3</v>
       </c>
-      <c r="AW192" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX192" t="n">
-        <v>2</v>
-      </c>
       <c r="AY192" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ192" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA192" t="n">
         <v>4</v>
@@ -42782,19 +42782,19 @@
         <v>2.27</v>
       </c>
       <c r="AU194" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV194" t="n">
         <v>1</v>
       </c>
       <c r="AW194" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AX194" t="n">
         <v>9</v>
       </c>
       <c r="AY194" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ194" t="n">
         <v>10</v>
@@ -42846,6 +42846,660 @@
       </c>
       <c r="BP194" t="n">
         <v>1.09</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>7814014</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>45907.29166666666</v>
+      </c>
+      <c r="F195" t="n">
+        <v>28</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" t="n">
+        <v>1</v>
+      </c>
+      <c r="L195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="n">
+        <v>3</v>
+      </c>
+      <c r="N195" t="n">
+        <v>4</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>['21', '48', '52']</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R195" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S195" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T195" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V195" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X195" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV195" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY195" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB195" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC195" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE195" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF195" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BG195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH195" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BI195" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ195" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BK195" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL195" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BM195" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BN195" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BO195" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="BP195" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>7814015</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>45907.29166666666</v>
+      </c>
+      <c r="F196" t="n">
+        <v>28</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R196" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S196" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V196" t="n">
+        <v>3</v>
+      </c>
+      <c r="W196" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X196" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB196" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BE196" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF196" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG196" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH196" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BI196" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BL196" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BM196" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BN196" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BO196" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="BP196" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>7814016</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>45907.29166666666</v>
+      </c>
+      <c r="F197" t="n">
+        <v>28</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Hwaseong</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Asan Mugunghwa</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>1</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" t="n">
+        <v>2</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>1</v>
+      </c>
+      <c r="N197" t="n">
+        <v>2</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R197" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S197" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U197" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V197" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="W197" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X197" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BE197" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF197" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BG197" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH197" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BI197" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BJ197" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BK197" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BM197" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BN197" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -43218,13 +43218,13 @@
         <v>2.64</v>
       </c>
       <c r="AU196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV196" t="n">
         <v>0</v>
       </c>
       <c r="AW196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX196" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -43000,22 +43000,22 @@
         <v>2.48</v>
       </c>
       <c r="AU195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV195" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW195" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX195" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY195" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ195" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA195" t="n">
         <v>9</v>
@@ -43218,7 +43218,7 @@
         <v>2.64</v>
       </c>
       <c r="AU196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV196" t="n">
         <v>0</v>
@@ -43230,7 +43230,7 @@
         <v>8</v>
       </c>
       <c r="AY196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ196" t="n">
         <v>8</v>
@@ -43436,22 +43436,22 @@
         <v>2.38</v>
       </c>
       <c r="AU197" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW197" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX197" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY197" t="n">
         <v>15</v>
       </c>
       <c r="AZ197" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA197" t="n">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -42346,16 +42346,16 @@
         <v>2.53</v>
       </c>
       <c r="AU192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX192" t="n">
         <v>4</v>
-      </c>
-      <c r="AW192" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX192" t="n">
-        <v>3</v>
       </c>
       <c r="AY192" t="n">
         <v>14</v>
@@ -42782,13 +42782,13 @@
         <v>2.27</v>
       </c>
       <c r="AU194" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AV194" t="n">
         <v>1</v>
       </c>
       <c r="AW194" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX194" t="n">
         <v>9</v>
@@ -43218,13 +43218,13 @@
         <v>2.64</v>
       </c>
       <c r="AU196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV196" t="n">
         <v>0</v>
       </c>
       <c r="AW196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX196" t="n">
         <v>8</v>
@@ -43436,13 +43436,13 @@
         <v>2.38</v>
       </c>
       <c r="AU197" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV197" t="n">
         <v>4</v>
       </c>
       <c r="AW197" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX197" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -42346,19 +42346,19 @@
         <v>2.53</v>
       </c>
       <c r="AU192" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV192" t="n">
         <v>4</v>
-      </c>
-      <c r="AV192" t="n">
-        <v>3</v>
       </c>
       <c r="AW192" t="n">
         <v>10</v>
       </c>
       <c r="AX192" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY192" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ192" t="n">
         <v>7</v>
@@ -42782,13 +42782,13 @@
         <v>2.27</v>
       </c>
       <c r="AU194" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV194" t="n">
         <v>1</v>
       </c>
       <c r="AW194" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX194" t="n">
         <v>9</v>
@@ -43218,13 +43218,13 @@
         <v>2.64</v>
       </c>
       <c r="AU196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV196" t="n">
         <v>0</v>
       </c>
       <c r="AW196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX196" t="n">
         <v>8</v>
@@ -43436,13 +43436,13 @@
         <v>2.38</v>
       </c>
       <c r="AU197" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV197" t="n">
         <v>4</v>
       </c>
       <c r="AW197" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX197" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP197"/>
+  <dimension ref="A1:BP204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>3</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR9" t="n">
         <v>2.45</v>
@@ -2655,10 +2655,10 @@
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR10" t="n">
         <v>0.6899999999999999</v>
@@ -2873,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR11" t="n">
         <v>0.91</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR12" t="n">
         <v>0.67</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR13" t="n">
         <v>1.27</v>
@@ -3527,10 +3527,10 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR15" t="n">
         <v>0.6899999999999999</v>
@@ -3963,10 +3963,10 @@
         <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR16" t="n">
         <v>1.51</v>
@@ -4181,10 +4181,10 @@
         <v>1.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR17" t="n">
         <v>1.03</v>
@@ -4399,10 +4399,10 @@
         <v>2</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR18" t="n">
         <v>1.16</v>
@@ -4617,10 +4617,10 @@
         <v>0.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR19" t="n">
         <v>1.3</v>
@@ -4835,10 +4835,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR20" t="n">
         <v>0.93</v>
@@ -5053,10 +5053,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR21" t="n">
         <v>0.89</v>
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR22" t="n">
         <v>0.79</v>
@@ -5489,10 +5489,10 @@
         <v>2.33</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR23" t="n">
         <v>1.57</v>
@@ -5707,10 +5707,10 @@
         <v>1.33</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR24" t="n">
         <v>1.08</v>
@@ -5925,10 +5925,10 @@
         <v>2.33</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR25" t="n">
         <v>1.51</v>
@@ -6143,10 +6143,10 @@
         <v>0.33</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR26" t="n">
         <v>1.55</v>
@@ -6361,10 +6361,10 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR27" t="n">
         <v>1.14</v>
@@ -6579,10 +6579,10 @@
         <v>2.33</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR28" t="n">
         <v>0.9399999999999999</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR29" t="n">
         <v>1.24</v>
@@ -7015,10 +7015,10 @@
         <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR30" t="n">
         <v>0.99</v>
@@ -7233,10 +7233,10 @@
         <v>2</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR31" t="n">
         <v>1.42</v>
@@ -7451,10 +7451,10 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR32" t="n">
         <v>0.92</v>
@@ -7669,10 +7669,10 @@
         <v>1.75</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR33" t="n">
         <v>1.44</v>
@@ -7887,10 +7887,10 @@
         <v>1.25</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR34" t="n">
         <v>0.73</v>
@@ -8105,10 +8105,10 @@
         <v>2.25</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR35" t="n">
         <v>0.78</v>
@@ -8323,10 +8323,10 @@
         <v>2</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR36" t="n">
         <v>1.2</v>
@@ -8541,10 +8541,10 @@
         <v>0.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR37" t="n">
         <v>0.86</v>
@@ -8759,10 +8759,10 @@
         <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR38" t="n">
         <v>1.24</v>
@@ -8977,10 +8977,10 @@
         <v>1.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR39" t="n">
         <v>1.25</v>
@@ -9195,10 +9195,10 @@
         <v>1.6</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR40" t="n">
         <v>1.53</v>
@@ -9413,10 +9413,10 @@
         <v>1.8</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR41" t="n">
         <v>1.35</v>
@@ -9631,10 +9631,10 @@
         <v>0.8</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR42" t="n">
         <v>1.31</v>
@@ -9849,10 +9849,10 @@
         <v>0.2</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR43" t="n">
         <v>0.82</v>
@@ -10067,10 +10067,10 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR44" t="n">
         <v>1.31</v>
@@ -10285,10 +10285,10 @@
         <v>1.83</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR45" t="n">
         <v>1.2</v>
@@ -10503,10 +10503,10 @@
         <v>1.67</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR46" t="n">
         <v>1.29</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR47" t="n">
         <v>1.21</v>
@@ -10939,10 +10939,10 @@
         <v>0.67</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR48" t="n">
         <v>1.41</v>
@@ -11157,10 +11157,10 @@
         <v>2.17</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR49" t="n">
         <v>1.27</v>
@@ -11375,10 +11375,10 @@
         <v>0.17</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR50" t="n">
         <v>0.8100000000000001</v>
@@ -11593,10 +11593,10 @@
         <v>0.57</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR51" t="n">
         <v>1.07</v>
@@ -11811,10 +11811,10 @@
         <v>0.43</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR52" t="n">
         <v>1.44</v>
@@ -12029,10 +12029,10 @@
         <v>0.86</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR53" t="n">
         <v>1.56</v>
@@ -12247,10 +12247,10 @@
         <v>1.86</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR54" t="n">
         <v>0.89</v>
@@ -12465,10 +12465,10 @@
         <v>1.29</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR55" t="n">
         <v>1.05</v>
@@ -12683,10 +12683,10 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -12901,10 +12901,10 @@
         <v>1.29</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR57" t="n">
         <v>1.29</v>
@@ -13119,10 +13119,10 @@
         <v>1.38</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR58" t="n">
         <v>1.16</v>
@@ -13337,10 +13337,10 @@
         <v>0.88</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR59" t="n">
         <v>0.9399999999999999</v>
@@ -13555,10 +13555,10 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR60" t="n">
         <v>1.45</v>
@@ -13773,10 +13773,10 @@
         <v>2.38</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR61" t="n">
         <v>1.32</v>
@@ -13991,10 +13991,10 @@
         <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR62" t="n">
         <v>1.59</v>
@@ -14209,10 +14209,10 @@
         <v>1.88</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR63" t="n">
         <v>1.29</v>
@@ -14427,10 +14427,10 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR64" t="n">
         <v>1.28</v>
@@ -14645,10 +14645,10 @@
         <v>1.89</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR65" t="n">
         <v>0.92</v>
@@ -14863,10 +14863,10 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR66" t="n">
         <v>1.37</v>
@@ -15081,10 +15081,10 @@
         <v>1.22</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR67" t="n">
         <v>1.14</v>
@@ -15299,10 +15299,10 @@
         <v>1.89</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR68" t="n">
         <v>1.12</v>
@@ -15517,10 +15517,10 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR69" t="n">
         <v>1.36</v>
@@ -15735,10 +15735,10 @@
         <v>1.22</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR70" t="n">
         <v>1.36</v>
@@ -15953,10 +15953,10 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR71" t="n">
         <v>1.23</v>
@@ -16171,10 +16171,10 @@
         <v>0.9</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR72" t="n">
         <v>1.32</v>
@@ -16389,10 +16389,10 @@
         <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR73" t="n">
         <v>1.28</v>
@@ -16607,10 +16607,10 @@
         <v>2.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR74" t="n">
         <v>1.43</v>
@@ -16825,10 +16825,10 @@
         <v>0.7</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR75" t="n">
         <v>1.21</v>
@@ -17043,10 +17043,10 @@
         <v>1.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR76" t="n">
         <v>1.15</v>
@@ -17261,10 +17261,10 @@
         <v>1.8</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR77" t="n">
         <v>1.18</v>
@@ -17479,10 +17479,10 @@
         <v>0.3</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR78" t="n">
         <v>1.6</v>
@@ -17697,10 +17697,10 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR79" t="n">
         <v>1.28</v>
@@ -17915,10 +17915,10 @@
         <v>0.82</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR80" t="n">
         <v>1.33</v>
@@ -18133,10 +18133,10 @@
         <v>1.45</v>
       </c>
       <c r="AP81" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR81" t="n">
         <v>1.03</v>
@@ -18351,10 +18351,10 @@
         <v>1.91</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR82" t="n">
         <v>1.34</v>
@@ -18569,10 +18569,10 @@
         <v>2.55</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR83" t="n">
         <v>1.12</v>
@@ -18787,10 +18787,10 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR84" t="n">
         <v>1.13</v>
@@ -19005,10 +19005,10 @@
         <v>1.91</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR85" t="n">
         <v>1.32</v>
@@ -19223,10 +19223,10 @@
         <v>2</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR86" t="n">
         <v>1.13</v>
@@ -19441,10 +19441,10 @@
         <v>0.67</v>
       </c>
       <c r="AP87" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR87" t="n">
         <v>1.18</v>
@@ -19659,10 +19659,10 @@
         <v>1.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR88" t="n">
         <v>0.99</v>
@@ -19877,10 +19877,10 @@
         <v>0.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR89" t="n">
         <v>1.35</v>
@@ -20095,10 +20095,10 @@
         <v>1.75</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR90" t="n">
         <v>1.44</v>
@@ -20313,10 +20313,10 @@
         <v>2.08</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR91" t="n">
         <v>1.36</v>
@@ -20531,10 +20531,10 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR92" t="n">
         <v>1.65</v>
@@ -20749,10 +20749,10 @@
         <v>1.69</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR93" t="n">
         <v>1.15</v>
@@ -20967,10 +20967,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR94" t="n">
         <v>1.14</v>
@@ -21185,10 +21185,10 @@
         <v>1.08</v>
       </c>
       <c r="AP95" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR95" t="n">
         <v>1.19</v>
@@ -21403,10 +21403,10 @@
         <v>1.38</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR96" t="n">
         <v>1.09</v>
@@ -21621,10 +21621,10 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR97" t="n">
         <v>1.44</v>
@@ -21839,10 +21839,10 @@
         <v>1.69</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR98" t="n">
         <v>1.67</v>
@@ -22057,10 +22057,10 @@
         <v>2.62</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR99" t="n">
         <v>1.08</v>
@@ -22275,10 +22275,10 @@
         <v>2</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR100" t="n">
         <v>1.07</v>
@@ -22493,10 +22493,10 @@
         <v>1.29</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR101" t="n">
         <v>1.18</v>
@@ -22711,10 +22711,10 @@
         <v>0.64</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR102" t="n">
         <v>1.35</v>
@@ -22929,10 +22929,10 @@
         <v>0.86</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR103" t="n">
         <v>1.3</v>
@@ -23147,10 +23147,10 @@
         <v>1.93</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR104" t="n">
         <v>1.17</v>
@@ -23365,10 +23365,10 @@
         <v>1.57</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR105" t="n">
         <v>1.39</v>
@@ -23583,10 +23583,10 @@
         <v>0.36</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR106" t="n">
         <v>1.28</v>
@@ -23801,10 +23801,10 @@
         <v>0.33</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR107" t="n">
         <v>1.44</v>
@@ -24019,10 +24019,10 @@
         <v>1.87</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR108" t="n">
         <v>1.33</v>
@@ -24237,10 +24237,10 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR109" t="n">
         <v>1.17</v>
@@ -24455,10 +24455,10 @@
         <v>1.67</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR110" t="n">
         <v>1.17</v>
@@ -24673,10 +24673,10 @@
         <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR111" t="n">
         <v>1.13</v>
@@ -24891,10 +24891,10 @@
         <v>1.13</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR112" t="n">
         <v>1.28</v>
@@ -25109,10 +25109,10 @@
         <v>2.53</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ113" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR113" t="n">
         <v>1.67</v>
@@ -25327,10 +25327,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR114" t="n">
         <v>1.34</v>
@@ -25545,10 +25545,10 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR115" t="n">
         <v>1.02</v>
@@ -25763,10 +25763,10 @@
         <v>1.56</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR116" t="n">
         <v>1.04</v>
@@ -25981,10 +25981,10 @@
         <v>1.31</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR117" t="n">
         <v>1.11</v>
@@ -26199,10 +26199,10 @@
         <v>0.75</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR118" t="n">
         <v>1.33</v>
@@ -26417,10 +26417,10 @@
         <v>1.94</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR119" t="n">
         <v>1.31</v>
@@ -26635,10 +26635,10 @@
         <v>1.19</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR120" t="n">
         <v>1.23</v>
@@ -26853,10 +26853,10 @@
         <v>1.65</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR121" t="n">
         <v>1.46</v>
@@ -27071,10 +27071,10 @@
         <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR122" t="n">
         <v>1.34</v>
@@ -27289,10 +27289,10 @@
         <v>0.65</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR123" t="n">
         <v>1.04</v>
@@ -27507,10 +27507,10 @@
         <v>1.24</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR124" t="n">
         <v>1.05</v>
@@ -27725,10 +27725,10 @@
         <v>1.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR125" t="n">
         <v>1.66</v>
@@ -27943,10 +27943,10 @@
         <v>1.76</v>
       </c>
       <c r="AP126" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR126" t="n">
         <v>1.16</v>
@@ -28161,10 +28161,10 @@
         <v>2.59</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR127" t="n">
         <v>1.32</v>
@@ -28379,10 +28379,10 @@
         <v>1.94</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR128" t="n">
         <v>1.43</v>
@@ -28597,10 +28597,10 @@
         <v>2.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR129" t="n">
         <v>1.23</v>
@@ -28815,10 +28815,10 @@
         <v>1.61</v>
       </c>
       <c r="AP130" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR130" t="n">
         <v>1.19</v>
@@ -29033,10 +29033,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP131" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR131" t="n">
         <v>1.27</v>
@@ -29251,10 +29251,10 @@
         <v>1.72</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR132" t="n">
         <v>1.04</v>
@@ -29469,10 +29469,10 @@
         <v>1.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR133" t="n">
         <v>1.29</v>
@@ -29687,10 +29687,10 @@
         <v>0.67</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR134" t="n">
         <v>1.13</v>
@@ -29905,10 +29905,10 @@
         <v>0.89</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR135" t="n">
         <v>1.64</v>
@@ -30123,10 +30123,10 @@
         <v>0.84</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR136" t="n">
         <v>1.03</v>
@@ -30341,10 +30341,10 @@
         <v>0.95</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR137" t="n">
         <v>1.21</v>
@@ -30559,10 +30559,10 @@
         <v>1.16</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR138" t="n">
         <v>1.37</v>
@@ -30777,10 +30777,10 @@
         <v>1.32</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR139" t="n">
         <v>1.31</v>
@@ -30995,10 +30995,10 @@
         <v>1.26</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR140" t="n">
         <v>1.38</v>
@@ -31213,10 +31213,10 @@
         <v>1.53</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR141" t="n">
         <v>1.04</v>
@@ -31431,10 +31431,10 @@
         <v>2.05</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR142" t="n">
         <v>1.22</v>
@@ -31649,10 +31649,10 @@
         <v>0.95</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR143" t="n">
         <v>1.29</v>
@@ -31867,10 +31867,10 @@
         <v>1.15</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR144" t="n">
         <v>1.24</v>
@@ -32085,10 +32085,10 @@
         <v>1.55</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR145" t="n">
         <v>1.03</v>
@@ -32303,10 +32303,10 @@
         <v>1.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR146" t="n">
         <v>1.35</v>
@@ -32521,10 +32521,10 @@
         <v>0.65</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR147" t="n">
         <v>1.2</v>
@@ -32739,10 +32739,10 @@
         <v>2.4</v>
       </c>
       <c r="AP148" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ148" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR148" t="n">
         <v>1.26</v>
@@ -32957,10 +32957,10 @@
         <v>1.81</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR149" t="n">
         <v>1.36</v>
@@ -33175,10 +33175,10 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR150" t="n">
         <v>1.08</v>
@@ -33393,10 +33393,10 @@
         <v>1.24</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR151" t="n">
         <v>1.2</v>
@@ -33611,10 +33611,10 @@
         <v>1.05</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR152" t="n">
         <v>1.43</v>
@@ -33829,10 +33829,10 @@
         <v>1.76</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR153" t="n">
         <v>1.09</v>
@@ -34047,10 +34047,10 @@
         <v>1.43</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR154" t="n">
         <v>1.61</v>
@@ -34265,10 +34265,10 @@
         <v>0.95</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR155" t="n">
         <v>1.33</v>
@@ -34483,10 +34483,10 @@
         <v>1.23</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR156" t="n">
         <v>1.37</v>
@@ -34701,10 +34701,10 @@
         <v>2.45</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ157" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR157" t="n">
         <v>1.23</v>
@@ -34919,10 +34919,10 @@
         <v>1.18</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR158" t="n">
         <v>1.28</v>
@@ -35137,10 +35137,10 @@
         <v>1.32</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR159" t="n">
         <v>1</v>
@@ -35355,10 +35355,10 @@
         <v>0.91</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR160" t="n">
         <v>1.04</v>
@@ -35573,10 +35573,10 @@
         <v>1.55</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR161" t="n">
         <v>1.24</v>
@@ -35791,10 +35791,10 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR162" t="n">
         <v>1.14</v>
@@ -36009,10 +36009,10 @@
         <v>0.91</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR163" t="n">
         <v>1.41</v>
@@ -36227,10 +36227,10 @@
         <v>2.39</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ164" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR164" t="n">
         <v>1.39</v>
@@ -36445,10 +36445,10 @@
         <v>0.87</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR165" t="n">
         <v>1.62</v>
@@ -36663,10 +36663,10 @@
         <v>1.39</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR166" t="n">
         <v>1.14</v>
@@ -36881,10 +36881,10 @@
         <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR167" t="n">
         <v>1.23</v>
@@ -37099,10 +37099,10 @@
         <v>0.7</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR168" t="n">
         <v>1.27</v>
@@ -37317,10 +37317,10 @@
         <v>1.65</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR169" t="n">
         <v>1.2</v>
@@ -37535,10 +37535,10 @@
         <v>1.17</v>
       </c>
       <c r="AP170" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR170" t="n">
         <v>1.07</v>
@@ -37753,10 +37753,10 @@
         <v>1.71</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR171" t="n">
         <v>1.3</v>
@@ -37971,10 +37971,10 @@
         <v>2.08</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR172" t="n">
         <v>1.32</v>
@@ -38189,10 +38189,10 @@
         <v>1</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR173" t="n">
         <v>1.21</v>
@@ -38407,10 +38407,10 @@
         <v>1.46</v>
       </c>
       <c r="AP174" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR174" t="n">
         <v>1.2</v>
@@ -38625,10 +38625,10 @@
         <v>1.29</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR175" t="n">
         <v>1.26</v>
@@ -38843,10 +38843,10 @@
         <v>1.42</v>
       </c>
       <c r="AP176" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR176" t="n">
         <v>1.17</v>
@@ -39061,10 +39061,10 @@
         <v>1.44</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AR177" t="n">
         <v>1.22</v>
@@ -39279,10 +39279,10 @@
         <v>0.92</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR178" t="n">
         <v>1.16</v>
@@ -39497,10 +39497,10 @@
         <v>0.8</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR179" t="n">
         <v>1.3</v>
@@ -39715,10 +39715,10 @@
         <v>0.76</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ180" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR180" t="n">
         <v>1.34</v>
@@ -39933,10 +39933,10 @@
         <v>2.32</v>
       </c>
       <c r="AP181" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ181" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR181" t="n">
         <v>1.21</v>
@@ -40151,10 +40151,10 @@
         <v>1.48</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR182" t="n">
         <v>1.42</v>
@@ -40369,10 +40369,10 @@
         <v>2</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR183" t="n">
         <v>1</v>
@@ -40587,10 +40587,10 @@
         <v>1.19</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR184" t="n">
         <v>1.28</v>
@@ -40805,10 +40805,10 @@
         <v>1.42</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AR185" t="n">
         <v>1.61</v>
@@ -41023,10 +41023,10 @@
         <v>1</v>
       </c>
       <c r="AP186" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AR186" t="n">
         <v>1.07</v>
@@ -41241,10 +41241,10 @@
         <v>1.73</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AR187" t="n">
         <v>1.3</v>
@@ -41459,10 +41459,10 @@
         <v>0.92</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AR188" t="n">
         <v>1.37</v>
@@ -41677,10 +41677,10 @@
         <v>1.42</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR189" t="n">
         <v>1.17</v>
@@ -41895,10 +41895,10 @@
         <v>1.62</v>
       </c>
       <c r="AP190" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AR190" t="n">
         <v>1.2</v>
@@ -42113,10 +42113,10 @@
         <v>1.93</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AR191" t="n">
         <v>1.37</v>
@@ -42331,10 +42331,10 @@
         <v>1.48</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AR192" t="n">
         <v>1.29</v>
@@ -42549,10 +42549,10 @@
         <v>0.85</v>
       </c>
       <c r="AP193" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR193" t="n">
         <v>1.21</v>
@@ -42767,10 +42767,10 @@
         <v>0.74</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR194" t="n">
         <v>1.18</v>
@@ -42985,10 +42985,10 @@
         <v>0.74</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AR195" t="n">
         <v>1.31</v>
@@ -43203,10 +43203,10 @@
         <v>2.3</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AQ196" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AR196" t="n">
         <v>1.36</v>
@@ -43421,10 +43421,10 @@
         <v>1.19</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR197" t="n">
         <v>0.99</v>
@@ -43500,6 +43500,1532 @@
       </c>
       <c r="BP197" t="n">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>7814017</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>45913.1875</v>
+      </c>
+      <c r="F198" t="n">
+        <v>29</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Asan Mugunghwa</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>1</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>1</v>
+      </c>
+      <c r="L198" t="n">
+        <v>3</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>3</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>['28', '67', '71']</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R198" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S198" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U198" t="n">
+        <v>3</v>
+      </c>
+      <c r="V198" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X198" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF198" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="BN198" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BO198" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="BP198" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>7814018</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>45913.29166666666</v>
+      </c>
+      <c r="F199" t="n">
+        <v>29</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Gyeongnam</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>2</v>
+      </c>
+      <c r="N199" t="n">
+        <v>2</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>['83', '87']</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R199" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S199" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V199" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X199" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BN199" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO199" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BP199" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>7814019</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>45913.29166666666</v>
+      </c>
+      <c r="F200" t="n">
+        <v>29</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Suwon Bluewings</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="n">
+        <v>1</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>1</v>
+      </c>
+      <c r="N200" t="n">
+        <v>1</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R200" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S200" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U200" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V200" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W200" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X200" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO200" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="BP200" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>7814020</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>45913.29166666666</v>
+      </c>
+      <c r="F201" t="n">
+        <v>29</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="n">
+        <v>3</v>
+      </c>
+      <c r="L201" t="n">
+        <v>3</v>
+      </c>
+      <c r="M201" t="n">
+        <v>4</v>
+      </c>
+      <c r="N201" t="n">
+        <v>7</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>['68', '86', '90+10']</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>['27', '28', '31', '59']</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R201" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S201" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T201" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U201" t="n">
+        <v>3</v>
+      </c>
+      <c r="V201" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X201" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="BP201" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>7814021</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>45914.29166666666</v>
+      </c>
+      <c r="F202" t="n">
+        <v>29</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Jeonnam Dragons</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Hwaseong</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" t="n">
+        <v>2</v>
+      </c>
+      <c r="N202" t="n">
+        <v>3</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>['55', '66']</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R202" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S202" t="n">
+        <v>5</v>
+      </c>
+      <c r="T202" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U202" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V202" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W202" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X202" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>7814022</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>45914.29166666666</v>
+      </c>
+      <c r="F203" t="n">
+        <v>29</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Cheongju</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Seongnam</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" t="n">
+        <v>1</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>1</v>
+      </c>
+      <c r="N203" t="n">
+        <v>1</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="R203" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S203" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U203" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V203" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W203" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X203" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>7814023</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>45914.29166666666</v>
+      </c>
+      <c r="F204" t="n">
+        <v>29</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Busan I'Park</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" t="n">
+        <v>1</v>
+      </c>
+      <c r="L204" t="n">
+        <v>2</v>
+      </c>
+      <c r="M204" t="n">
+        <v>3</v>
+      </c>
+      <c r="N204" t="n">
+        <v>5</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>['71', '89']</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>['2', '57', '66']</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R204" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S204" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V204" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X204" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 2_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP204"/>
+  <dimension ref="A1:BP211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>3</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR9" t="n">
         <v>2.45</v>
@@ -2655,10 +2655,10 @@
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR10" t="n">
         <v>0.6899999999999999</v>
@@ -2873,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR11" t="n">
         <v>0.91</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR12" t="n">
         <v>0.67</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR13" t="n">
         <v>1.27</v>
@@ -3527,10 +3527,10 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR15" t="n">
         <v>0.6899999999999999</v>
@@ -3963,10 +3963,10 @@
         <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR16" t="n">
         <v>1.51</v>
@@ -4181,10 +4181,10 @@
         <v>1.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR17" t="n">
         <v>1.03</v>
@@ -4399,10 +4399,10 @@
         <v>2</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR18" t="n">
         <v>1.16</v>
@@ -4617,10 +4617,10 @@
         <v>0.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR19" t="n">
         <v>1.3</v>
@@ -4835,10 +4835,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR20" t="n">
         <v>0.93</v>
@@ -5053,10 +5053,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR21" t="n">
         <v>0.89</v>
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR22" t="n">
         <v>0.79</v>
@@ -5489,10 +5489,10 @@
         <v>2.33</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR23" t="n">
         <v>1.57</v>
@@ -5707,10 +5707,10 @@
         <v>1.33</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR24" t="n">
         <v>1.08</v>
@@ -5925,10 +5925,10 @@
         <v>2.33</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR25" t="n">
         <v>1.51</v>
@@ -6143,10 +6143,10 @@
         <v>0.33</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR26" t="n">
         <v>1.55</v>
@@ -6361,10 +6361,10 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR27" t="n">
         <v>1.14</v>
@@ -6579,10 +6579,10 @@
         <v>2.33</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR28" t="n">
         <v>0.9399999999999999</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR29" t="n">
         <v>1.24</v>
@@ -7015,10 +7015,10 @@
         <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR30" t="n">
         <v>0.99</v>
@@ -7233,10 +7233,10 @@
         <v>2</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR31" t="n">
         <v>1.42</v>
@@ -7451,10 +7451,10 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR32" t="n">
         <v>0.92</v>
@@ -7669,10 +7669,10 @@
         <v>1.75</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR33" t="n">
         <v>1.44</v>
@@ -7887,10 +7887,10 @@
         <v>1.25</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR34" t="n">
         <v>0.73</v>
@@ -8105,10 +8105,10 @@
         <v>2.25</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR35" t="n">
         <v>0.78</v>
@@ -8323,10 +8323,10 @@
         <v>2</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR36" t="n">
         <v>1.2</v>
@@ -8541,10 +8541,10 @@
         <v>0.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR37" t="n">
         <v>0.86</v>
@@ -8759,10 +8759,10 @@
         <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR38" t="n">
         <v>1.24</v>
@@ -8977,10 +8977,10 @@
         <v>1.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR39" t="n">
         <v>1.25</v>
@@ -9195,10 +9195,10 @@
         <v>1.6</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR40" t="n">
         <v>1.53</v>
@@ -9413,10 +9413,10 @@
         <v>1.8</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR41" t="n">
         <v>1.35</v>
@@ -9631,10 +9631,10 @@
         <v>0.8</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR42" t="n">
         <v>1.31</v>
@@ -9849,10 +9849,10 @@
         <v>0.2</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR43" t="n">
         <v>0.82</v>
@@ -10067,10 +10067,10 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR44" t="n">
         <v>1.31</v>
@@ -10285,10 +10285,10 @@
         <v>1.83</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR45" t="n">
         <v>1.2</v>
@@ -10503,10 +10503,10 @@
         <v>1.67</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR46" t="n">
         <v>1.29</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR47" t="n">
         <v>1.21</v>
@@ -10939,10 +10939,10 @@
         <v>0.67</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR48" t="n">
         <v>1.41</v>
@@ -11157,10 +11157,10 @@
         <v>2.17</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR49" t="n">
         <v>1.27</v>
@@ -11375,10 +11375,10 @@
         <v>0.17</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR50" t="n">
         <v>0.8100000000000001</v>
@@ -11593,10 +11593,10 @@
         <v>0.57</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR51" t="n">
         <v>1.07</v>
@@ -11811,10 +11811,10 @@
         <v>0.43</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR52" t="n">
         <v>1.44</v>
@@ -12029,10 +12029,10 @@
         <v>0.86</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR53" t="n">
         <v>1.56</v>
@@ -12247,10 +12247,10 @@
         <v>1.86</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR54" t="n">
         <v>0.89</v>
@@ -12465,10 +12465,10 @@
         <v>1.29</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR55" t="n">
         <v>1.05</v>
@@ -12683,10 +12683,10 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -12901,10 +12901,10 @@
         <v>1.29</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR57" t="n">
         <v>1.29</v>
@@ -13119,10 +13119,10 @@
         <v>1.38</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR58" t="n">
         <v>1.16</v>
@@ -13337,10 +13337,10 @@
         <v>0.88</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR59" t="n">
         <v>0.9399999999999999</v>
@@ -13555,10 +13555,10 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR60" t="n">
         <v>1.45</v>
@@ -13773,10 +13773,10 @@
         <v>2.38</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR61" t="n">
         <v>1.32</v>
@@ -13991,10 +13991,10 @@
         <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR62" t="n">
         <v>1.59</v>
@@ -14209,10 +14209,10 @@
         <v>1.88</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR63" t="n">
         <v>1.29</v>
@@ -14427,10 +14427,10 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR64" t="n">
         <v>1.28</v>
@@ -14645,10 +14645,10 @@
         <v>1.89</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR65" t="n">
         <v>0.92</v>
@@ -14863,10 +14863,10 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR66" t="n">
         <v>1.37</v>
@@ -15081,10 +15081,10 @@
         <v>1.22</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR67" t="n">
         <v>1.14</v>
@@ -15299,10 +15299,10 @@
         <v>1.89</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR68" t="n">
         <v>1.12</v>
@@ -15517,10 +15517,10 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR69" t="n">
         <v>1.36</v>
@@ -15735,10 +15735,10 @@
         <v>1.22</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR70" t="n">
         <v>1.36</v>
@@ -15953,10 +15953,10 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR71" t="n">
         <v>1.23</v>
@@ -16171,10 +16171,10 @@
         <v>0.9</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR72" t="n">
         <v>1.32</v>
@@ -16389,10 +16389,10 @@
         <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR73" t="n">
         <v>1.28</v>
@@ -16607,10 +16607,10 @@
         <v>2.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR74" t="n">
         <v>1.43</v>
@@ -16825,10 +16825,10 @@
         <v>0.7</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR75" t="n">
         <v>1.21</v>
@@ -17043,10 +17043,10 @@
         <v>1.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR76" t="n">
         <v>1.15</v>
@@ -17261,10 +17261,10 @@
         <v>1.8</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR77" t="n">
         <v>1.18</v>
@@ -17479,10 +17479,10 @@
         <v>0.3</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR78" t="n">
         <v>1.6</v>
@@ -17697,10 +17697,10 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR79" t="n">
         <v>1.28</v>
@@ -17915,10 +17915,10 @@
         <v>0.82</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR80" t="n">
         <v>1.33</v>
@@ -18133,10 +18133,10 @@
         <v>1.45</v>
       </c>
       <c r="AP81" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR81" t="n">
         <v>1.03</v>
@@ -18351,10 +18351,10 @@
         <v>1.91</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR82" t="n">
         <v>1.34</v>
@@ -18569,10 +18569,10 @@
         <v>2.55</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR83" t="n">
         <v>1.12</v>
@@ -18787,10 +18787,10 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR84" t="n">
         <v>1.13</v>
@@ -19005,10 +19005,10 @@
         <v>1.91</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR85" t="n">
         <v>1.32</v>
@@ -19223,10 +19223,10 @@
         <v>2</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR86" t="n">
         <v>1.13</v>
@@ -19441,10 +19441,10 @@
         <v>0.67</v>
       </c>
       <c r="AP87" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR87" t="n">
         <v>1.18</v>
@@ -19659,10 +19659,10 @@
         <v>1.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR88" t="n">
         <v>0.99</v>
@@ -19877,10 +19877,10 @@
         <v>0.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR89" t="n">
         <v>1.35</v>
@@ -20095,10 +20095,10 @@
         <v>1.75</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR90" t="n">
         <v>1.44</v>
@@ -20313,10 +20313,10 @@
         <v>2.08</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR91" t="n">
         <v>1.36</v>
@@ -20531,10 +20531,10 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR92" t="n">
         <v>1.65</v>
@@ -20749,10 +20749,10 @@
         <v>1.69</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR93" t="n">
         <v>1.15</v>
@@ -20967,10 +20967,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR94" t="n">
         <v>1.14</v>
@@ -21185,10 +21185,10 @@
         <v>1.08</v>
       </c>
       <c r="AP95" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR95" t="n">
         <v>1.19</v>
@@ -21403,10 +21403,10 @@
         <v>1.38</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR96" t="n">
         <v>1.09</v>
@@ -21621,10 +21621,10 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR97" t="n">
         <v>1.44</v>
@@ -21839,10 +21839,10 @@
         <v>1.69</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR98" t="n">
         <v>1.67</v>
@@ -22057,10 +22057,10 @@
         <v>2.62</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR99" t="n">
         <v>1.08</v>
@@ -22275,10 +22275,10 @@
         <v>2</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR100" t="n">
         <v>1.07</v>
@@ -22493,10 +22493,10 @@
         <v>1.29</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR101" t="n">
         <v>1.18</v>
@@ -22711,10 +22711,10 @@
         <v>0.64</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR102" t="n">
         <v>1.35</v>
@@ -22929,10 +22929,10 @@
         <v>0.86</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR103" t="n">
         <v>1.3</v>
@@ -23147,10 +23147,10 @@
         <v>1.93</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR104" t="n">
         <v>1.17</v>
@@ -23365,10 +23365,10 @@
         <v>1.57</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR105" t="n">
         <v>1.39</v>
@@ -23583,10 +23583,10 @@
         <v>0.36</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR106" t="n">
         <v>1.28</v>
@@ -23801,10 +23801,10 @@
         <v>0.33</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR107" t="n">
         <v>1.44</v>
@@ -24019,10 +24019,10 @@
         <v>1.87</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR108" t="n">
         <v>1.33</v>
@@ -24237,10 +24237,10 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR109" t="n">
         <v>1.17</v>
@@ -24455,10 +24455,10 @@
         <v>1.67</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR110" t="n">
         <v>1.17</v>
@@ -24673,10 +24673,10 @@
         <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR111" t="n">
         <v>1.13</v>
@@ -24891,10 +24891,10 @@
         <v>1.13</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR112" t="n">
         <v>1.28</v>
@@ -25109,10 +25109,10 @@
         <v>2.53</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ113" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR113" t="n">
         <v>1.67</v>
@@ -25327,10 +25327,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR114" t="n">
         <v>1.34</v>
@@ -25545,10 +25545,10 @@
         <v>1.75</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR115" t="n">
         <v>1.02</v>
@@ -25763,10 +25763,10 @@
         <v>1.56</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR116" t="n">
         <v>1.04</v>
@@ -25981,10 +25981,10 @@
         <v>1.31</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR117" t="n">
         <v>1.11</v>
@@ -26199,10 +26199,10 @@
         <v>0.75</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR118" t="n">
         <v>1.33</v>
@@ -26417,10 +26417,10 @@
         <v>1.94</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR119" t="n">
         <v>1.31</v>
@@ -26635,10 +26635,10 @@
         <v>1.19</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR120" t="n">
         <v>1.23</v>
@@ -26853,10 +26853,10 @@
         <v>1.65</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR121" t="n">
         <v>1.46</v>
@@ -27071,10 +27071,10 @@
         <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR122" t="n">
         <v>1.34</v>
@@ -27289,10 +27289,10 @@
         <v>0.65</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR123" t="n">
         <v>1.04</v>
@@ -27507,10 +27507,10 @@
         <v>1.24</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR124" t="n">
         <v>1.05</v>
@@ -27725,10 +27725,10 @@
         <v>1.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR125" t="n">
         <v>1.66</v>
@@ -27943,10 +27943,10 @@
         <v>1.76</v>
       </c>
       <c r="AP126" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR126" t="n">
         <v>1.16</v>
@@ -28161,10 +28161,10 @@
         <v>2.59</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR127" t="n">
         <v>1.32</v>
@@ -28379,10 +28379,10 @@
         <v>1.94</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR128" t="n">
         <v>1.43</v>
@@ -28597,10 +28597,10 @@
         <v>2.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR129" t="n">
         <v>1.23</v>
@@ -28815,10 +28815,10 @@
         <v>1.61</v>
       </c>
       <c r="AP130" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR130" t="n">
         <v>1.19</v>
@@ -29033,10 +29033,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP131" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR131" t="n">
         <v>1.27</v>
@@ -29251,10 +29251,10 @@
         <v>1.72</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR132" t="n">
         <v>1.04</v>
@@ -29469,10 +29469,10 @@
         <v>1.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR133" t="n">
         <v>1.29</v>
@@ -29687,10 +29687,10 @@
         <v>0.67</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR134" t="n">
         <v>1.13</v>
@@ -29905,10 +29905,10 @@
         <v>0.89</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR135" t="n">
         <v>1.64</v>
@@ -30123,10 +30123,10 @@
         <v>0.84</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR136" t="n">
         <v>1.03</v>
@@ -30341,10 +30341,10 @@
         <v>0.95</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR137" t="n">
         <v>1.21</v>
@@ -30559,10 +30559,10 @@
         <v>1.16</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR138" t="n">
         <v>1.37</v>
@@ -30777,10 +30777,10 @@
         <v>1.32</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR139" t="n">
         <v>1.31</v>
@@ -30995,10 +30995,10 @@
         <v>1.26</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR140" t="n">
         <v>1.38</v>
@@ -31213,10 +31213,10 @@
         <v>1.53</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR141" t="n">
         <v>1.04</v>
@@ -31431,10 +31431,10 @@
         <v>2.05</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR142" t="n">
         <v>1.22</v>
@@ -31649,10 +31649,10 @@
         <v>0.95</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR143" t="n">
         <v>1.29</v>
@@ -31867,10 +31867,10 @@
         <v>1.15</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR144" t="n">
         <v>1.24</v>
@@ -32085,10 +32085,10 @@
         <v>1.55</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR145" t="n">
         <v>1.03</v>
@@ -32303,10 +32303,10 @@
         <v>1.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR146" t="n">
         <v>1.35</v>
@@ -32521,10 +32521,10 @@
         <v>0.65</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR147" t="n">
         <v>1.2</v>
@@ -32739,10 +32739,10 @@
         <v>2.4</v>
       </c>
       <c r="AP148" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ148" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR148" t="n">
         <v>1.26</v>
@@ -32957,10 +32957,10 @@
         <v>1.81</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR149" t="n">
         <v>1.36</v>
@@ -33175,10 +33175,10 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR150" t="n">
         <v>1.08</v>
@@ -33393,10 +33393,10 @@
         <v>1.24</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR151" t="n">
         <v>1.2</v>
@@ -33611,10 +33611,10 @@
         <v>1.05</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR152" t="n">
         <v>1.43</v>
@@ -33829,10 +33829,10 @@
         <v>1.76</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR153" t="n">
         <v>1.09</v>
@@ -34047,10 +34047,10 @@
         <v>1.43</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR154" t="n">
         <v>1.61</v>
@@ -34265,10 +34265,10 @@
         <v>0.95</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR155" t="n">
         <v>1.33</v>
@@ -34483,10 +34483,10 @@
         <v>1.23</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR156" t="n">
         <v>1.37</v>
@@ -34701,10 +34701,10 @@
         <v>2.45</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ157" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR157" t="n">
         <v>1.23</v>
@@ -34919,10 +34919,10 @@
         <v>1.18</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR158" t="n">
         <v>1.28</v>
@@ -35137,10 +35137,10 @@
         <v>1.32</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR159" t="n">
         <v>1</v>
@@ -35355,10 +35355,10 @@
         <v>0.91</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR160" t="n">
         <v>1.04</v>
@@ -35573,10 +35573,10 @@
         <v>1.55</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR161" t="n">
         <v>1.24</v>
@@ -35791,10 +35791,10 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR162" t="n">
         <v>1.14</v>
@@ -36009,10 +36009,10 @@
         <v>0.91</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR163" t="n">
         <v>1.41</v>
@@ -36227,10 +36227,10 @@
         <v>2.39</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ164" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR164" t="n">
         <v>1.39</v>
@@ -36445,10 +36445,10 @@
         <v>0.87</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR165" t="n">
         <v>1.62</v>
@@ -36663,10 +36663,10 @@
         <v>1.39</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR166" t="n">
         <v>1.14</v>
@@ -36881,10 +36881,10 @@
         <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR167" t="n">
         <v>1.23</v>
@@ -37099,10 +37099,10 @@
         <v>0.7</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR168" t="n">
         <v>1.27</v>
@@ -37317,10 +37317,10 @@
         <v>1.65</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR169" t="n">
         <v>1.2</v>
@@ -37535,10 +37535,10 @@
         <v>1.17</v>
       </c>
       <c r="AP170" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR170" t="n">
         <v>1.07</v>
@@ -37753,10 +37753,10 @@
         <v>1.71</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR171" t="n">
         <v>1.3</v>
@@ -37971,10 +37971,10 @@
         <v>2.08</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR172" t="n">
         <v>1.32</v>
@@ -38189,10 +38189,10 @@
         <v>1</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR173" t="n">
         <v>1.21</v>
@@ -38407,10 +38407,10 @@
         <v>1.46</v>
       </c>
       <c r="AP174" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR174" t="n">
         <v>1.2</v>
@@ -38625,10 +38625,10 @@
         <v>1.29</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR175" t="n">
         <v>1.26</v>
@@ -38843,10 +38843,10 @@
         <v>1.42</v>
       </c>
       <c r="AP176" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR176" t="n">
         <v>1.17</v>
@@ -39061,10 +39061,10 @@
         <v>1.44</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR177" t="n">
         <v>1.22</v>
@@ -39279,10 +39279,10 @@
         <v>0.92</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR178" t="n">
         <v>1.16</v>
@@ -39497,10 +39497,10 @@
         <v>0.8</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR179" t="n">
         <v>1.3</v>
@@ -39715,10 +39715,10 @@
         <v>0.76</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ180" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR180" t="n">
         <v>1.34</v>
@@ -39933,10 +39933,10 @@
         <v>2.32</v>
       </c>
       <c r="AP181" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ181" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR181" t="n">
         <v>1.21</v>
@@ -40151,10 +40151,10 @@
         <v>1.48</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR182" t="n">
         <v>1.42</v>
@@ -40369,10 +40369,10 @@
         <v>2</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR183" t="n">
         <v>1</v>
@@ -40587,10 +40587,10 @@
         <v>1.19</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR184" t="n">
         <v>1.28</v>
@@ -40805,10 +40805,10 @@
         <v>1.42</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR185" t="n">
         <v>1.61</v>
@@ -41023,10 +41023,10 @@
         <v>1</v>
       </c>
       <c r="AP186" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR186" t="n">
         <v>1.07</v>
@@ -41241,10 +41241,10 @@
         <v>1.73</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR187" t="n">
         <v>1.3</v>
@@ -41459,10 +41459,10 @@
         <v>0.92</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR188" t="n">
         <v>1.37</v>
@@ -41677,10 +41677,10 @@
         <v>1.42</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR189" t="n">
         <v>1.17</v>
@@ -41895,10 +41895,10 @@
         <v>1.62</v>
       </c>
       <c r="AP190" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR190" t="n">
         <v>1.2</v>
@@ -42113,10 +42113,10 @@
         <v>1.93</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR191" t="n">
         <v>1.37</v>
@@ -42331,10 +42331,10 @@
         <v>1.48</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR192" t="n">
         <v>1.29</v>
@@ -42549,10 +42549,10 @@
         <v>0.85</v>
       </c>
       <c r="AP193" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AR193" t="n">
         <v>1.21</v>
@@ -42767,10 +42767,10 @@
         <v>0.74</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AR194" t="n">
         <v>1.18</v>
@@ -42985,10 +42985,10 @@
         <v>0.74</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR195" t="n">
         <v>1.31</v>
@@ -43203,10 +43203,10 @@
         <v>2.3</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AQ196" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR196" t="n">
         <v>1.36</v>
@@ -43421,10 +43421,10 @@
         <v>1.19</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AR197" t="n">
         <v>0.99</v>
@@ -43639,10 +43639,10 @@
         <v>1.71</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR198" t="n">
         <v>1.38</v>
@@ -43857,10 +43857,10 @@
         <v>1.43</v>
       </c>
       <c r="AP199" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AR199" t="n">
         <v>1.22</v>
@@ -44075,10 +44075,10 @@
         <v>1.86</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AR200" t="n">
         <v>1.24</v>
@@ -44293,10 +44293,10 @@
         <v>2.21</v>
       </c>
       <c r="AP201" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ201" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AR201" t="n">
         <v>1.2</v>
@@ -44511,10 +44511,10 @@
         <v>1.07</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR202" t="n">
         <v>1.32</v>
@@ -44729,10 +44729,10 @@
         <v>1.46</v>
       </c>
       <c r="AP203" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AR203" t="n">
         <v>1.2</v>
@@ -44947,10 +44947,10 @@
         <v>1.57</v>
       </c>
       <c r="AP204" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AR204" t="n">
         <v>1.09</v>
@@ -45026,6 +45026,1532 @@
       </c>
       <c r="BP204" t="n">
         <v>1.03</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>7814025</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>45920.1875</v>
+      </c>
+      <c r="F205" t="n">
+        <v>30</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Seoul E-Land</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="n">
+        <v>1</v>
+      </c>
+      <c r="L205" t="n">
+        <v>2</v>
+      </c>
+      <c r="M205" t="n">
+        <v>2</v>
+      </c>
+      <c r="N205" t="n">
+        <v>4</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>['90+2', '90+9']</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>['16', '58']</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R205" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S205" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V205" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X205" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BP205" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>7814024</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>45920.1875</v>
+      </c>
+      <c r="F206" t="n">
+        <v>30</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Suwon Bluewings</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Gyeongnam</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="n">
+        <v>1</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="n">
+        <v>2</v>
+      </c>
+      <c r="N206" t="n">
+        <v>3</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>['27', '77']</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R206" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S206" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U206" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="V206" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X206" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO206" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP206" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>7814026</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>45920.29166666666</v>
+      </c>
+      <c r="F207" t="n">
+        <v>30</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>1</v>
+      </c>
+      <c r="M207" t="n">
+        <v>2</v>
+      </c>
+      <c r="N207" t="n">
+        <v>3</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>['47', '63']</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R207" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S207" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T207" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U207" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V207" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X207" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY207" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB207" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE207" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BH207" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BI207" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ207" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BK207" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BL207" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BM207" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BN207" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BO207" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="BP207" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>7814027</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>45920.29166666666</v>
+      </c>
+      <c r="F208" t="n">
+        <v>30</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Seongnam</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Asan Mugunghwa</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" t="n">
+        <v>3</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>3</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>['40', '63', '66']</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R208" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S208" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U208" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V208" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W208" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X208" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB208" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE208" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="BF208" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG208" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BH208" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BI208" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ208" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BK208" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BL208" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BM208" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BN208" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO208" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BP208" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>7814028</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>45921.1875</v>
+      </c>
+      <c r="F209" t="n">
+        <v>30</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Cheongju</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R209" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S209" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T209" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U209" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V209" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="W209" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X209" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BH209" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BI209" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BJ209" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BK209" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BL209" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BM209" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BN209" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO209" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="BP209" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>7814029</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>45921.1875</v>
+      </c>
+      <c r="F210" t="n">
+        <v>30</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Cheonan City</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Hwaseong</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" t="n">
+        <v>2</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+      <c r="M210" t="n">
+        <v>2</v>
+      </c>
+      <c r="N210" t="n">
+        <v>4</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>['12', '71']</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>['40', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R210" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S210" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T210" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U210" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V210" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W210" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X210" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BI210" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BJ210" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BK210" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BL210" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BM210" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BN210" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BO210" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="BP210" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>7814030</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>South Korea K League 2</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>45921.29166666666</v>
+      </c>
+      <c r="F211" t="n">
+        <v>30</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Busan I'Park</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Jeonnam Dragons</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>1</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="n">
+        <v>2</v>
+      </c>
+      <c r="L211" t="n">
+        <v>1</v>
+      </c>
+      <c r="M211" t="n">
+        <v>1</v>
+      </c>
+      <c r="N211" t="n">
+        <v>2</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R211" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S211" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T211" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U211" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V211" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X211" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BI211" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BJ211" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BK211" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL211" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BM211" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="BN211" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BO211" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="BP211" t="n">
+        <v>1.07</v>
       </c>
     </row>
   </sheetData>
